--- a/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
+++ b/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
@@ -15484,10 +15484,20 @@
       <c r="G307" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H307" s="6" t="inlineStr"/>
-      <c r="I307" s="6" t="inlineStr"/>
-      <c r="J307" s="6" t="inlineStr"/>
-      <c r="K307" s="6" t="inlineStr"/>
+      <c r="H307" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I307" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K307" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -15523,10 +15533,20 @@
       <c r="G308" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H308" s="6" t="inlineStr"/>
-      <c r="I308" s="6" t="inlineStr"/>
-      <c r="J308" s="6" t="inlineStr"/>
-      <c r="K308" s="6" t="inlineStr"/>
+      <c r="H308" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K308" s="5" t="n">
+        <v>-260</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -15562,10 +15582,20 @@
       <c r="G309" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H309" s="6" t="inlineStr"/>
-      <c r="I309" s="6" t="inlineStr"/>
-      <c r="J309" s="6" t="inlineStr"/>
-      <c r="K309" s="6" t="inlineStr"/>
+      <c r="H309" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K309" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -20398,10 +20428,20 @@
       <c r="G433" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H433" s="6" t="inlineStr"/>
-      <c r="I433" s="6" t="inlineStr"/>
-      <c r="J433" s="6" t="inlineStr"/>
-      <c r="K433" s="6" t="inlineStr"/>
+      <c r="H433" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I433" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J433" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K433" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -20437,10 +20477,20 @@
       <c r="G434" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="H434" s="6" t="inlineStr"/>
-      <c r="I434" s="6" t="inlineStr"/>
-      <c r="J434" s="6" t="inlineStr"/>
-      <c r="K434" s="6" t="inlineStr"/>
+      <c r="H434" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I434" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J434" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K434" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -20476,10 +20526,20 @@
       <c r="G435" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="H435" s="6" t="inlineStr"/>
-      <c r="I435" s="6" t="inlineStr"/>
-      <c r="J435" s="6" t="inlineStr"/>
-      <c r="K435" s="6" t="inlineStr"/>
+      <c r="H435" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I435" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J435" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K435" s="4" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -20515,10 +20575,20 @@
       <c r="G436" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="H436" s="6" t="inlineStr"/>
-      <c r="I436" s="6" t="inlineStr"/>
-      <c r="J436" s="6" t="inlineStr"/>
-      <c r="K436" s="6" t="inlineStr"/>
+      <c r="H436" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I436" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J436" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K436" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -20632,10 +20702,20 @@
       <c r="G439" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H439" s="6" t="inlineStr"/>
-      <c r="I439" s="6" t="inlineStr"/>
-      <c r="J439" s="6" t="inlineStr"/>
-      <c r="K439" s="6" t="inlineStr"/>
+      <c r="H439" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I439" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K439" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -20671,10 +20751,20 @@
       <c r="G440" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H440" s="6" t="inlineStr"/>
-      <c r="I440" s="6" t="inlineStr"/>
-      <c r="J440" s="6" t="inlineStr"/>
-      <c r="K440" s="6" t="inlineStr"/>
+      <c r="H440" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I440" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K440" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -20710,10 +20800,20 @@
       <c r="G441" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H441" s="6" t="inlineStr"/>
-      <c r="I441" s="6" t="inlineStr"/>
-      <c r="J441" s="6" t="inlineStr"/>
-      <c r="K441" s="6" t="inlineStr"/>
+      <c r="H441" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I441" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K441" s="4" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -20749,10 +20849,20 @@
       <c r="G442" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H442" s="6" t="inlineStr"/>
-      <c r="I442" s="6" t="inlineStr"/>
-      <c r="J442" s="6" t="inlineStr"/>
-      <c r="K442" s="6" t="inlineStr"/>
+      <c r="H442" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J442" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K442" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -20788,10 +20898,20 @@
       <c r="G443" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H443" s="6" t="inlineStr"/>
-      <c r="I443" s="6" t="inlineStr"/>
-      <c r="J443" s="6" t="inlineStr"/>
-      <c r="K443" s="6" t="inlineStr"/>
+      <c r="H443" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K443" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -20827,10 +20947,20 @@
       <c r="G444" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H444" s="6" t="inlineStr"/>
-      <c r="I444" s="6" t="inlineStr"/>
-      <c r="J444" s="6" t="inlineStr"/>
-      <c r="K444" s="6" t="inlineStr"/>
+      <c r="H444" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I444" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K444" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -20866,10 +20996,20 @@
       <c r="G445" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H445" s="6" t="inlineStr"/>
-      <c r="I445" s="6" t="inlineStr"/>
-      <c r="J445" s="6" t="inlineStr"/>
-      <c r="K445" s="6" t="inlineStr"/>
+      <c r="H445" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I445" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K445" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -20905,10 +21045,20 @@
       <c r="G446" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H446" s="6" t="inlineStr"/>
-      <c r="I446" s="6" t="inlineStr"/>
-      <c r="J446" s="6" t="inlineStr"/>
-      <c r="K446" s="6" t="inlineStr"/>
+      <c r="H446" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I446" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K446" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -21334,10 +21484,20 @@
       <c r="G457" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H457" s="6" t="inlineStr"/>
-      <c r="I457" s="6" t="inlineStr"/>
-      <c r="J457" s="6" t="inlineStr"/>
-      <c r="K457" s="6" t="inlineStr"/>
+      <c r="H457" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I457" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J457" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K457" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -21373,10 +21533,20 @@
       <c r="G458" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H458" s="6" t="inlineStr"/>
-      <c r="I458" s="6" t="inlineStr"/>
-      <c r="J458" s="6" t="inlineStr"/>
-      <c r="K458" s="6" t="inlineStr"/>
+      <c r="H458" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I458" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J458" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K458" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -21412,10 +21582,20 @@
       <c r="G459" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H459" s="6" t="inlineStr"/>
-      <c r="I459" s="6" t="inlineStr"/>
-      <c r="J459" s="6" t="inlineStr"/>
-      <c r="K459" s="6" t="inlineStr"/>
+      <c r="H459" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I459" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J459" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K459" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -21451,10 +21631,20 @@
       <c r="G460" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H460" s="6" t="inlineStr"/>
-      <c r="I460" s="6" t="inlineStr"/>
-      <c r="J460" s="6" t="inlineStr"/>
-      <c r="K460" s="6" t="inlineStr"/>
+      <c r="H460" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I460" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J460" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K460" s="4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -21646,10 +21836,20 @@
       <c r="G465" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H465" s="6" t="inlineStr"/>
-      <c r="I465" s="6" t="inlineStr"/>
-      <c r="J465" s="6" t="inlineStr"/>
-      <c r="K465" s="6" t="inlineStr"/>
+      <c r="H465" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J465" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K465" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -21685,10 +21885,20 @@
       <c r="G466" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="H466" s="6" t="inlineStr"/>
-      <c r="I466" s="6" t="inlineStr"/>
-      <c r="J466" s="6" t="inlineStr"/>
-      <c r="K466" s="6" t="inlineStr"/>
+      <c r="H466" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I466" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J466" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K466" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -21724,10 +21934,20 @@
       <c r="G467" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H467" s="6" t="inlineStr"/>
-      <c r="I467" s="6" t="inlineStr"/>
-      <c r="J467" s="6" t="inlineStr"/>
-      <c r="K467" s="6" t="inlineStr"/>
+      <c r="H467" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I467" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J467" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K467" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -21841,10 +22061,20 @@
       <c r="G470" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H470" s="6" t="inlineStr"/>
-      <c r="I470" s="6" t="inlineStr"/>
-      <c r="J470" s="6" t="inlineStr"/>
-      <c r="K470" s="6" t="inlineStr"/>
+      <c r="H470" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I470" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J470" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K470" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -21880,10 +22110,20 @@
       <c r="G471" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H471" s="6" t="inlineStr"/>
-      <c r="I471" s="6" t="inlineStr"/>
-      <c r="J471" s="6" t="inlineStr"/>
-      <c r="K471" s="6" t="inlineStr"/>
+      <c r="H471" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I471" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K471" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -21997,10 +22237,20 @@
       <c r="G474" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H474" s="6" t="inlineStr"/>
-      <c r="I474" s="6" t="inlineStr"/>
-      <c r="J474" s="6" t="inlineStr"/>
-      <c r="K474" s="6" t="inlineStr"/>
+      <c r="H474" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K474" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -22114,10 +22364,20 @@
       <c r="G477" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H477" s="6" t="inlineStr"/>
-      <c r="I477" s="6" t="inlineStr"/>
-      <c r="J477" s="6" t="inlineStr"/>
-      <c r="K477" s="6" t="inlineStr"/>
+      <c r="H477" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I477" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J477" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K477" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -22153,10 +22413,20 @@
       <c r="G478" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H478" s="6" t="inlineStr"/>
-      <c r="I478" s="6" t="inlineStr"/>
-      <c r="J478" s="6" t="inlineStr"/>
-      <c r="K478" s="6" t="inlineStr"/>
+      <c r="H478" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I478" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J478" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K478" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -22426,10 +22696,20 @@
       <c r="G485" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H485" s="6" t="inlineStr"/>
-      <c r="I485" s="6" t="inlineStr"/>
-      <c r="J485" s="6" t="inlineStr"/>
-      <c r="K485" s="6" t="inlineStr"/>
+      <c r="H485" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I485" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J485" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K485" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -22465,10 +22745,20 @@
       <c r="G486" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H486" s="6" t="inlineStr"/>
-      <c r="I486" s="6" t="inlineStr"/>
-      <c r="J486" s="6" t="inlineStr"/>
-      <c r="K486" s="6" t="inlineStr"/>
+      <c r="H486" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I486" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J486" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K486" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -22504,10 +22794,20 @@
       <c r="G487" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H487" s="6" t="inlineStr"/>
-      <c r="I487" s="6" t="inlineStr"/>
-      <c r="J487" s="6" t="inlineStr"/>
-      <c r="K487" s="6" t="inlineStr"/>
+      <c r="H487" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I487" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J487" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K487" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -22543,10 +22843,20 @@
       <c r="G488" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H488" s="6" t="inlineStr"/>
-      <c r="I488" s="6" t="inlineStr"/>
-      <c r="J488" s="6" t="inlineStr"/>
-      <c r="K488" s="6" t="inlineStr"/>
+      <c r="H488" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I488" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J488" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K488" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -22582,10 +22892,20 @@
       <c r="G489" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H489" s="6" t="inlineStr"/>
-      <c r="I489" s="6" t="inlineStr"/>
-      <c r="J489" s="6" t="inlineStr"/>
-      <c r="K489" s="6" t="inlineStr"/>
+      <c r="H489" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I489" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K489" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -22621,10 +22941,20 @@
       <c r="G490" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H490" s="6" t="inlineStr"/>
-      <c r="I490" s="6" t="inlineStr"/>
-      <c r="J490" s="6" t="inlineStr"/>
-      <c r="K490" s="6" t="inlineStr"/>
+      <c r="H490" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I490" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K490" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -22660,10 +22990,20 @@
       <c r="G491" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H491" s="6" t="inlineStr"/>
-      <c r="I491" s="6" t="inlineStr"/>
-      <c r="J491" s="6" t="inlineStr"/>
-      <c r="K491" s="6" t="inlineStr"/>
+      <c r="H491" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I491" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J491" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K491" s="4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -22699,10 +23039,20 @@
       <c r="G492" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="H492" s="6" t="inlineStr"/>
-      <c r="I492" s="6" t="inlineStr"/>
-      <c r="J492" s="6" t="inlineStr"/>
-      <c r="K492" s="6" t="inlineStr"/>
+      <c r="H492" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I492" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J492" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K492" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -22738,10 +23088,20 @@
       <c r="G493" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H493" s="6" t="inlineStr"/>
-      <c r="I493" s="6" t="inlineStr"/>
-      <c r="J493" s="6" t="inlineStr"/>
-      <c r="K493" s="6" t="inlineStr"/>
+      <c r="H493" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I493" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J493" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K493" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -22777,10 +23137,20 @@
       <c r="G494" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H494" s="6" t="inlineStr"/>
-      <c r="I494" s="6" t="inlineStr"/>
-      <c r="J494" s="6" t="inlineStr"/>
-      <c r="K494" s="6" t="inlineStr"/>
+      <c r="H494" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I494" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J494" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K494" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -22855,10 +23225,20 @@
       <c r="G496" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H496" s="6" t="inlineStr"/>
-      <c r="I496" s="6" t="inlineStr"/>
-      <c r="J496" s="6" t="inlineStr"/>
-      <c r="K496" s="6" t="inlineStr"/>
+      <c r="H496" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I496" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J496" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K496" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -22894,10 +23274,20 @@
       <c r="G497" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H497" s="6" t="inlineStr"/>
-      <c r="I497" s="6" t="inlineStr"/>
-      <c r="J497" s="6" t="inlineStr"/>
-      <c r="K497" s="6" t="inlineStr"/>
+      <c r="H497" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I497" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K497" s="4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -22933,10 +23323,20 @@
       <c r="G498" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H498" s="6" t="inlineStr"/>
-      <c r="I498" s="6" t="inlineStr"/>
-      <c r="J498" s="6" t="inlineStr"/>
-      <c r="K498" s="6" t="inlineStr"/>
+      <c r="H498" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I498" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J498" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K498" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -22972,10 +23372,20 @@
       <c r="G499" s="2" t="n">
         <v>2.02</v>
       </c>
-      <c r="H499" s="6" t="inlineStr"/>
-      <c r="I499" s="6" t="inlineStr"/>
-      <c r="J499" s="6" t="inlineStr"/>
-      <c r="K499" s="6" t="inlineStr"/>
+      <c r="H499" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J499" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K499" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -23011,10 +23421,20 @@
       <c r="G500" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H500" s="6" t="inlineStr"/>
-      <c r="I500" s="6" t="inlineStr"/>
-      <c r="J500" s="6" t="inlineStr"/>
-      <c r="K500" s="6" t="inlineStr"/>
+      <c r="H500" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J500" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K500" s="5" t="n">
+        <v>-1000</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -23050,10 +23470,20 @@
       <c r="G501" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="H501" s="6" t="inlineStr"/>
-      <c r="I501" s="6" t="inlineStr"/>
-      <c r="J501" s="6" t="inlineStr"/>
-      <c r="K501" s="6" t="inlineStr"/>
+      <c r="H501" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I501" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J501" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K501" s="5" t="n">
+        <v>-240</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -23089,10 +23519,20 @@
       <c r="G502" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="H502" s="6" t="inlineStr"/>
-      <c r="I502" s="6" t="inlineStr"/>
-      <c r="J502" s="6" t="inlineStr"/>
-      <c r="K502" s="6" t="inlineStr"/>
+      <c r="H502" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K502" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -23128,10 +23568,20 @@
       <c r="G503" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H503" s="6" t="inlineStr"/>
-      <c r="I503" s="6" t="inlineStr"/>
-      <c r="J503" s="6" t="inlineStr"/>
-      <c r="K503" s="6" t="inlineStr"/>
+      <c r="H503" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I503" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J503" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K503" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -23167,10 +23617,20 @@
       <c r="G504" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H504" s="6" t="inlineStr"/>
-      <c r="I504" s="6" t="inlineStr"/>
-      <c r="J504" s="6" t="inlineStr"/>
-      <c r="K504" s="6" t="inlineStr"/>
+      <c r="H504" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K504" s="5" t="n">
+        <v>-285</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -23206,10 +23666,20 @@
       <c r="G505" s="2" t="n">
         <v>1.95</v>
       </c>
-      <c r="H505" s="6" t="inlineStr"/>
-      <c r="I505" s="6" t="inlineStr"/>
-      <c r="J505" s="6" t="inlineStr"/>
-      <c r="K505" s="6" t="inlineStr"/>
+      <c r="H505" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K505" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -23245,10 +23715,20 @@
       <c r="G506" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H506" s="6" t="inlineStr"/>
-      <c r="I506" s="6" t="inlineStr"/>
-      <c r="J506" s="6" t="inlineStr"/>
-      <c r="K506" s="6" t="inlineStr"/>
+      <c r="H506" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I506" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J506" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K506" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -23284,10 +23764,20 @@
       <c r="G507" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H507" s="6" t="inlineStr"/>
-      <c r="I507" s="6" t="inlineStr"/>
-      <c r="J507" s="6" t="inlineStr"/>
-      <c r="K507" s="6" t="inlineStr"/>
+      <c r="H507" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I507" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J507" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K507" s="4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -23362,10 +23852,20 @@
       <c r="G509" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="H509" s="6" t="inlineStr"/>
-      <c r="I509" s="6" t="inlineStr"/>
-      <c r="J509" s="6" t="inlineStr"/>
-      <c r="K509" s="6" t="inlineStr"/>
+      <c r="H509" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K509" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -23401,10 +23901,20 @@
       <c r="G510" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H510" s="6" t="inlineStr"/>
-      <c r="I510" s="6" t="inlineStr"/>
-      <c r="J510" s="6" t="inlineStr"/>
-      <c r="K510" s="6" t="inlineStr"/>
+      <c r="H510" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I510" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K510" s="5" t="n">
+        <v>-255</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -23440,10 +23950,20 @@
       <c r="G511" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H511" s="6" t="inlineStr"/>
-      <c r="I511" s="6" t="inlineStr"/>
-      <c r="J511" s="6" t="inlineStr"/>
-      <c r="K511" s="6" t="inlineStr"/>
+      <c r="H511" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I511" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K511" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -23479,10 +23999,20 @@
       <c r="G512" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H512" s="6" t="inlineStr"/>
-      <c r="I512" s="6" t="inlineStr"/>
-      <c r="J512" s="6" t="inlineStr"/>
-      <c r="K512" s="6" t="inlineStr"/>
+      <c r="H512" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I512" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J512" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K512" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -23518,10 +24048,20 @@
       <c r="G513" s="2" t="n">
         <v>1.85</v>
       </c>
-      <c r="H513" s="6" t="inlineStr"/>
-      <c r="I513" s="6" t="inlineStr"/>
-      <c r="J513" s="6" t="inlineStr"/>
-      <c r="K513" s="6" t="inlineStr"/>
+      <c r="H513" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I513" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J513" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K513" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -23557,10 +24097,20 @@
       <c r="G514" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="H514" s="6" t="inlineStr"/>
-      <c r="I514" s="6" t="inlineStr"/>
-      <c r="J514" s="6" t="inlineStr"/>
-      <c r="K514" s="6" t="inlineStr"/>
+      <c r="H514" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I514" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J514" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K514" s="4" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -23596,10 +24146,20 @@
       <c r="G515" s="2" t="n">
         <v>2.84</v>
       </c>
-      <c r="H515" s="6" t="inlineStr"/>
-      <c r="I515" s="6" t="inlineStr"/>
-      <c r="J515" s="6" t="inlineStr"/>
-      <c r="K515" s="6" t="inlineStr"/>
+      <c r="H515" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I515" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J515" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K515" s="5" t="n">
+        <v>-184</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -23635,10 +24195,20 @@
       <c r="G516" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H516" s="6" t="inlineStr"/>
-      <c r="I516" s="6" t="inlineStr"/>
-      <c r="J516" s="6" t="inlineStr"/>
-      <c r="K516" s="6" t="inlineStr"/>
+      <c r="H516" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I516" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J516" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K516" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -23674,10 +24244,20 @@
       <c r="G517" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H517" s="6" t="inlineStr"/>
-      <c r="I517" s="6" t="inlineStr"/>
-      <c r="J517" s="6" t="inlineStr"/>
-      <c r="K517" s="6" t="inlineStr"/>
+      <c r="H517" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I517" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J517" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K517" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -23713,10 +24293,20 @@
       <c r="G518" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H518" s="6" t="inlineStr"/>
-      <c r="I518" s="6" t="inlineStr"/>
-      <c r="J518" s="6" t="inlineStr"/>
-      <c r="K518" s="6" t="inlineStr"/>
+      <c r="H518" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I518" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J518" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K518" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -23752,10 +24342,20 @@
       <c r="G519" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H519" s="6" t="inlineStr"/>
-      <c r="I519" s="6" t="inlineStr"/>
-      <c r="J519" s="6" t="inlineStr"/>
-      <c r="K519" s="6" t="inlineStr"/>
+      <c r="H519" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I519" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J519" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K519" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -23791,10 +24391,20 @@
       <c r="G520" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="H520" s="6" t="inlineStr"/>
-      <c r="I520" s="6" t="inlineStr"/>
-      <c r="J520" s="6" t="inlineStr"/>
-      <c r="K520" s="6" t="inlineStr"/>
+      <c r="H520" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I520" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J520" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K520" s="4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -23869,10 +24479,20 @@
       <c r="G522" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H522" s="6" t="inlineStr"/>
-      <c r="I522" s="6" t="inlineStr"/>
-      <c r="J522" s="6" t="inlineStr"/>
-      <c r="K522" s="6" t="inlineStr"/>
+      <c r="H522" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J522" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K522" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -23986,10 +24606,20 @@
       <c r="G525" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="H525" s="6" t="inlineStr"/>
-      <c r="I525" s="6" t="inlineStr"/>
-      <c r="J525" s="6" t="inlineStr"/>
-      <c r="K525" s="6" t="inlineStr"/>
+      <c r="H525" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I525" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K525" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -24025,10 +24655,20 @@
       <c r="G526" s="2" t="n">
         <v>3.15</v>
       </c>
-      <c r="H526" s="6" t="inlineStr"/>
-      <c r="I526" s="6" t="inlineStr"/>
-      <c r="J526" s="6" t="inlineStr"/>
-      <c r="K526" s="6" t="inlineStr"/>
+      <c r="H526" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I526" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J526" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K526" s="5" t="n">
+        <v>-215</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -24064,10 +24704,20 @@
       <c r="G527" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H527" s="6" t="inlineStr"/>
-      <c r="I527" s="6" t="inlineStr"/>
-      <c r="J527" s="6" t="inlineStr"/>
-      <c r="K527" s="6" t="inlineStr"/>
+      <c r="H527" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I527" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J527" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K527" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -24259,10 +24909,20 @@
       <c r="G532" s="2" t="n">
         <v>9.6</v>
       </c>
-      <c r="H532" s="6" t="inlineStr"/>
-      <c r="I532" s="6" t="inlineStr"/>
-      <c r="J532" s="6" t="inlineStr"/>
-      <c r="K532" s="6" t="inlineStr"/>
+      <c r="H532" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I532" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J532" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K532" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -24298,10 +24958,20 @@
       <c r="G533" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H533" s="6" t="inlineStr"/>
-      <c r="I533" s="6" t="inlineStr"/>
-      <c r="J533" s="6" t="inlineStr"/>
-      <c r="K533" s="6" t="inlineStr"/>
+      <c r="H533" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I533" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J533" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K533" s="5" t="n">
+        <v>-235</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -24337,10 +25007,20 @@
       <c r="G534" s="2" t="n">
         <v>2.54</v>
       </c>
-      <c r="H534" s="6" t="inlineStr"/>
-      <c r="I534" s="6" t="inlineStr"/>
-      <c r="J534" s="6" t="inlineStr"/>
-      <c r="K534" s="6" t="inlineStr"/>
+      <c r="H534" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I534" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J534" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K534" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -24376,10 +25056,20 @@
       <c r="G535" s="2" t="n">
         <v>9.4</v>
       </c>
-      <c r="H535" s="6" t="inlineStr"/>
-      <c r="I535" s="6" t="inlineStr"/>
-      <c r="J535" s="6" t="inlineStr"/>
-      <c r="K535" s="6" t="inlineStr"/>
+      <c r="H535" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I535" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J535" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K535" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -24415,10 +25105,20 @@
       <c r="G536" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H536" s="6" t="inlineStr"/>
-      <c r="I536" s="6" t="inlineStr"/>
-      <c r="J536" s="6" t="inlineStr"/>
-      <c r="K536" s="6" t="inlineStr"/>
+      <c r="H536" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I536" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J536" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K536" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -24454,10 +25154,20 @@
       <c r="G537" s="2" t="n">
         <v>2.86</v>
       </c>
-      <c r="H537" s="6" t="inlineStr"/>
-      <c r="I537" s="6" t="inlineStr"/>
-      <c r="J537" s="6" t="inlineStr"/>
-      <c r="K537" s="6" t="inlineStr"/>
+      <c r="H537" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I537" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J537" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K537" s="5" t="n">
+        <v>-186</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -24493,10 +25203,20 @@
       <c r="G538" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H538" s="6" t="inlineStr"/>
-      <c r="I538" s="6" t="inlineStr"/>
-      <c r="J538" s="6" t="inlineStr"/>
-      <c r="K538" s="6" t="inlineStr"/>
+      <c r="H538" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I538" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J538" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K538" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -24532,10 +25252,20 @@
       <c r="G539" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H539" s="6" t="inlineStr"/>
-      <c r="I539" s="6" t="inlineStr"/>
-      <c r="J539" s="6" t="inlineStr"/>
-      <c r="K539" s="6" t="inlineStr"/>
+      <c r="H539" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I539" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J539" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K539" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -24571,10 +25301,20 @@
       <c r="G540" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H540" s="6" t="inlineStr"/>
-      <c r="I540" s="6" t="inlineStr"/>
-      <c r="J540" s="6" t="inlineStr"/>
-      <c r="K540" s="6" t="inlineStr"/>
+      <c r="H540" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I540" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J540" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K540" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -24727,10 +25467,20 @@
       <c r="G544" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H544" s="6" t="inlineStr"/>
-      <c r="I544" s="6" t="inlineStr"/>
-      <c r="J544" s="6" t="inlineStr"/>
-      <c r="K544" s="6" t="inlineStr"/>
+      <c r="H544" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I544" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K544" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -24766,10 +25516,20 @@
       <c r="G545" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="H545" s="6" t="inlineStr"/>
-      <c r="I545" s="6" t="inlineStr"/>
-      <c r="J545" s="6" t="inlineStr"/>
-      <c r="K545" s="6" t="inlineStr"/>
+      <c r="H545" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I545" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J545" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K545" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -24961,10 +25721,20 @@
       <c r="G550" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H550" s="6" t="inlineStr"/>
-      <c r="I550" s="6" t="inlineStr"/>
-      <c r="J550" s="6" t="inlineStr"/>
-      <c r="K550" s="6" t="inlineStr"/>
+      <c r="H550" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I550" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J550" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K550" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -25000,10 +25770,20 @@
       <c r="G551" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="H551" s="6" t="inlineStr"/>
-      <c r="I551" s="6" t="inlineStr"/>
-      <c r="J551" s="6" t="inlineStr"/>
-      <c r="K551" s="6" t="inlineStr"/>
+      <c r="H551" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J551" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K551" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -25039,10 +25819,20 @@
       <c r="G552" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H552" s="6" t="inlineStr"/>
-      <c r="I552" s="6" t="inlineStr"/>
-      <c r="J552" s="6" t="inlineStr"/>
-      <c r="K552" s="6" t="inlineStr"/>
+      <c r="H552" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I552" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J552" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K552" s="5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -25234,10 +26024,20 @@
       <c r="G557" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H557" s="6" t="inlineStr"/>
-      <c r="I557" s="6" t="inlineStr"/>
-      <c r="J557" s="6" t="inlineStr"/>
-      <c r="K557" s="6" t="inlineStr"/>
+      <c r="H557" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I557" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J557" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K557" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -25273,10 +26073,20 @@
       <c r="G558" s="2" t="n">
         <v>2.24</v>
       </c>
-      <c r="H558" s="6" t="inlineStr"/>
-      <c r="I558" s="6" t="inlineStr"/>
-      <c r="J558" s="6" t="inlineStr"/>
-      <c r="K558" s="6" t="inlineStr"/>
+      <c r="H558" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J558" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K558" s="4" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -26287,10 +27097,20 @@
       <c r="G584" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H584" s="6" t="inlineStr"/>
-      <c r="I584" s="6" t="inlineStr"/>
-      <c r="J584" s="6" t="inlineStr"/>
-      <c r="K584" s="6" t="inlineStr"/>
+      <c r="H584" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I584" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K584" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
@@ -26326,10 +27146,20 @@
       <c r="G585" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="6" t="inlineStr"/>
-      <c r="J585" s="6" t="inlineStr"/>
-      <c r="K585" s="6" t="inlineStr"/>
+      <c r="H585" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I585" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K585" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -26365,10 +27195,20 @@
       <c r="G586" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H586" s="6" t="inlineStr"/>
-      <c r="I586" s="6" t="inlineStr"/>
-      <c r="J586" s="6" t="inlineStr"/>
-      <c r="K586" s="6" t="inlineStr"/>
+      <c r="H586" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I586" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J586" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K586" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -26404,10 +27244,20 @@
       <c r="G587" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
-      <c r="K587" s="6" t="inlineStr"/>
+      <c r="H587" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I587" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J587" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K587" s="4" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -26677,10 +27527,20 @@
       <c r="G594" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H594" s="6" t="inlineStr"/>
-      <c r="I594" s="6" t="inlineStr"/>
-      <c r="J594" s="6" t="inlineStr"/>
-      <c r="K594" s="6" t="inlineStr"/>
+      <c r="H594" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I594" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J594" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K594" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -26716,10 +27576,20 @@
       <c r="G595" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
-      <c r="K595" s="6" t="inlineStr"/>
+      <c r="H595" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I595" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J595" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K595" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
@@ -26755,10 +27625,20 @@
       <c r="G596" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H596" s="6" t="inlineStr"/>
-      <c r="I596" s="6" t="inlineStr"/>
-      <c r="J596" s="6" t="inlineStr"/>
-      <c r="K596" s="6" t="inlineStr"/>
+      <c r="H596" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I596" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J596" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K596" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
@@ -26794,10 +27674,20 @@
       <c r="G597" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
-      <c r="K597" s="6" t="inlineStr"/>
+      <c r="H597" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J597" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K597" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -26833,10 +27723,20 @@
       <c r="G598" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H598" s="6" t="inlineStr"/>
-      <c r="I598" s="6" t="inlineStr"/>
-      <c r="J598" s="6" t="inlineStr"/>
-      <c r="K598" s="6" t="inlineStr"/>
+      <c r="H598" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I598" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J598" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K598" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -26872,10 +27772,20 @@
       <c r="G599" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="6" t="inlineStr"/>
-      <c r="K599" s="6" t="inlineStr"/>
+      <c r="H599" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I599" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J599" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K599" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -26911,10 +27821,20 @@
       <c r="G600" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H600" s="6" t="inlineStr"/>
-      <c r="I600" s="6" t="inlineStr"/>
-      <c r="J600" s="6" t="inlineStr"/>
-      <c r="K600" s="6" t="inlineStr"/>
+      <c r="H600" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I600" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J600" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K600" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
@@ -26950,10 +27870,20 @@
       <c r="G601" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="6" t="inlineStr"/>
-      <c r="J601" s="6" t="inlineStr"/>
-      <c r="K601" s="6" t="inlineStr"/>
+      <c r="H601" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I601" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J601" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K601" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -26989,10 +27919,20 @@
       <c r="G602" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H602" s="6" t="inlineStr"/>
-      <c r="I602" s="6" t="inlineStr"/>
-      <c r="J602" s="6" t="inlineStr"/>
-      <c r="K602" s="6" t="inlineStr"/>
+      <c r="H602" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J602" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K602" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
@@ -27028,10 +27968,20 @@
       <c r="G603" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
-      <c r="K603" s="6" t="inlineStr"/>
+      <c r="H603" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I603" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J603" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K603" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -27067,10 +28017,20 @@
       <c r="G604" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H604" s="6" t="inlineStr"/>
-      <c r="I604" s="6" t="inlineStr"/>
-      <c r="J604" s="6" t="inlineStr"/>
-      <c r="K604" s="6" t="inlineStr"/>
+      <c r="H604" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I604" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J604" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K604" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -27106,10 +28066,20 @@
       <c r="G605" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="6" t="inlineStr"/>
-      <c r="J605" s="6" t="inlineStr"/>
-      <c r="K605" s="6" t="inlineStr"/>
+      <c r="H605" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I605" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J605" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K605" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -27145,10 +28115,20 @@
       <c r="G606" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H606" s="6" t="inlineStr"/>
-      <c r="I606" s="6" t="inlineStr"/>
-      <c r="J606" s="6" t="inlineStr"/>
-      <c r="K606" s="6" t="inlineStr"/>
+      <c r="H606" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J606" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K606" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -27184,10 +28164,20 @@
       <c r="G607" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
-      <c r="K607" s="6" t="inlineStr"/>
+      <c r="H607" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I607" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J607" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K607" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
@@ -27223,10 +28213,20 @@
       <c r="G608" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H608" s="6" t="inlineStr"/>
-      <c r="I608" s="6" t="inlineStr"/>
-      <c r="J608" s="6" t="inlineStr"/>
-      <c r="K608" s="6" t="inlineStr"/>
+      <c r="H608" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I608" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J608" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K608" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
@@ -27262,10 +28262,20 @@
       <c r="G609" s="2" t="n">
         <v>2.24</v>
       </c>
-      <c r="H609" s="6" t="inlineStr"/>
-      <c r="I609" s="6" t="inlineStr"/>
-      <c r="J609" s="6" t="inlineStr"/>
-      <c r="K609" s="6" t="inlineStr"/>
+      <c r="H609" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I609" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J609" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K609" s="4" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -27613,10 +28623,20 @@
       <c r="G618" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H618" s="6" t="inlineStr"/>
-      <c r="I618" s="6" t="inlineStr"/>
-      <c r="J618" s="6" t="inlineStr"/>
-      <c r="K618" s="6" t="inlineStr"/>
+      <c r="H618" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J618" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K618" s="5" t="n">
+        <v>-1000</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -27652,10 +28672,20 @@
       <c r="G619" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H619" s="6" t="inlineStr"/>
-      <c r="I619" s="6" t="inlineStr"/>
-      <c r="J619" s="6" t="inlineStr"/>
-      <c r="K619" s="6" t="inlineStr"/>
+      <c r="H619" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I619" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J619" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K619" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -27691,10 +28721,20 @@
       <c r="G620" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H620" s="6" t="inlineStr"/>
-      <c r="I620" s="6" t="inlineStr"/>
-      <c r="J620" s="6" t="inlineStr"/>
-      <c r="K620" s="6" t="inlineStr"/>
+      <c r="H620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J620" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K620" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
@@ -27847,10 +28887,20 @@
       <c r="G624" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H624" s="6" t="inlineStr"/>
-      <c r="I624" s="6" t="inlineStr"/>
-      <c r="J624" s="6" t="inlineStr"/>
-      <c r="K624" s="6" t="inlineStr"/>
+      <c r="H624" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I624" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J624" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K624" s="5" t="n">
+        <v>-285</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
@@ -27886,10 +28936,20 @@
       <c r="G625" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H625" s="6" t="inlineStr"/>
-      <c r="I625" s="6" t="inlineStr"/>
-      <c r="J625" s="6" t="inlineStr"/>
-      <c r="K625" s="6" t="inlineStr"/>
+      <c r="H625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K625" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -28003,10 +29063,20 @@
       <c r="G628" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H628" s="6" t="inlineStr"/>
-      <c r="I628" s="6" t="inlineStr"/>
-      <c r="J628" s="6" t="inlineStr"/>
-      <c r="K628" s="6" t="inlineStr"/>
+      <c r="H628" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J628" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K628" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -28042,10 +29112,20 @@
       <c r="G629" s="2" t="n">
         <v>2.02</v>
       </c>
-      <c r="H629" s="6" t="inlineStr"/>
-      <c r="I629" s="6" t="inlineStr"/>
-      <c r="J629" s="6" t="inlineStr"/>
-      <c r="K629" s="6" t="inlineStr"/>
+      <c r="H629" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I629" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J629" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K629" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -28081,10 +29161,20 @@
       <c r="G630" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H630" s="6" t="inlineStr"/>
-      <c r="I630" s="6" t="inlineStr"/>
-      <c r="J630" s="6" t="inlineStr"/>
-      <c r="K630" s="6" t="inlineStr"/>
+      <c r="H630" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I630" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J630" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K630" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -28120,10 +29210,20 @@
       <c r="G631" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H631" s="6" t="inlineStr"/>
-      <c r="I631" s="6" t="inlineStr"/>
-      <c r="J631" s="6" t="inlineStr"/>
-      <c r="K631" s="6" t="inlineStr"/>
+      <c r="H631" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I631" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J631" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K631" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -28159,10 +29259,20 @@
       <c r="G632" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H632" s="6" t="inlineStr"/>
-      <c r="I632" s="6" t="inlineStr"/>
-      <c r="J632" s="6" t="inlineStr"/>
-      <c r="K632" s="6" t="inlineStr"/>
+      <c r="H632" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I632" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J632" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K632" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
@@ -28198,10 +29308,20 @@
       <c r="G633" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H633" s="6" t="inlineStr"/>
-      <c r="I633" s="6" t="inlineStr"/>
-      <c r="J633" s="6" t="inlineStr"/>
-      <c r="K633" s="6" t="inlineStr"/>
+      <c r="H633" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I633" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J633" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K633" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -28237,10 +29357,20 @@
       <c r="G634" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H634" s="6" t="inlineStr"/>
-      <c r="I634" s="6" t="inlineStr"/>
-      <c r="J634" s="6" t="inlineStr"/>
-      <c r="K634" s="6" t="inlineStr"/>
+      <c r="H634" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I634" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J634" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K634" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -28354,10 +29484,20 @@
       <c r="G637" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H637" s="6" t="inlineStr"/>
-      <c r="I637" s="6" t="inlineStr"/>
-      <c r="J637" s="6" t="inlineStr"/>
-      <c r="K637" s="6" t="inlineStr"/>
+      <c r="H637" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I637" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J637" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K637" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
@@ -28510,10 +29650,20 @@
       <c r="G641" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H641" s="6" t="inlineStr"/>
-      <c r="I641" s="6" t="inlineStr"/>
-      <c r="J641" s="6" t="inlineStr"/>
-      <c r="K641" s="6" t="inlineStr"/>
+      <c r="H641" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I641" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J641" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K641" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
@@ -28549,10 +29699,20 @@
       <c r="G642" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H642" s="6" t="inlineStr"/>
-      <c r="I642" s="6" t="inlineStr"/>
-      <c r="J642" s="6" t="inlineStr"/>
-      <c r="K642" s="6" t="inlineStr"/>
+      <c r="H642" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I642" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J642" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K642" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -28588,10 +29748,20 @@
       <c r="G643" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H643" s="6" t="inlineStr"/>
-      <c r="I643" s="6" t="inlineStr"/>
-      <c r="J643" s="6" t="inlineStr"/>
-      <c r="K643" s="6" t="inlineStr"/>
+      <c r="H643" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I643" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J643" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K643" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -28627,10 +29797,20 @@
       <c r="G644" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H644" s="6" t="inlineStr"/>
-      <c r="I644" s="6" t="inlineStr"/>
-      <c r="J644" s="6" t="inlineStr"/>
-      <c r="K644" s="6" t="inlineStr"/>
+      <c r="H644" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I644" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J644" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K644" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
@@ -28666,10 +29846,20 @@
       <c r="G645" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H645" s="6" t="inlineStr"/>
-      <c r="I645" s="6" t="inlineStr"/>
-      <c r="J645" s="6" t="inlineStr"/>
-      <c r="K645" s="6" t="inlineStr"/>
+      <c r="H645" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I645" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J645" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K645" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
@@ -28705,10 +29895,20 @@
       <c r="G646" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H646" s="6" t="inlineStr"/>
-      <c r="I646" s="6" t="inlineStr"/>
-      <c r="J646" s="6" t="inlineStr"/>
-      <c r="K646" s="6" t="inlineStr"/>
+      <c r="H646" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I646" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J646" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K646" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -28744,10 +29944,20 @@
       <c r="G647" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H647" s="6" t="inlineStr"/>
-      <c r="I647" s="6" t="inlineStr"/>
-      <c r="J647" s="6" t="inlineStr"/>
-      <c r="K647" s="6" t="inlineStr"/>
+      <c r="H647" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I647" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J647" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K647" s="5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -28783,10 +29993,20 @@
       <c r="G648" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="H648" s="6" t="inlineStr"/>
-      <c r="I648" s="6" t="inlineStr"/>
-      <c r="J648" s="6" t="inlineStr"/>
-      <c r="K648" s="6" t="inlineStr"/>
+      <c r="H648" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I648" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J648" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K648" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -28822,10 +30042,20 @@
       <c r="G649" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H649" s="6" t="inlineStr"/>
-      <c r="I649" s="6" t="inlineStr"/>
-      <c r="J649" s="6" t="inlineStr"/>
-      <c r="K649" s="6" t="inlineStr"/>
+      <c r="H649" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I649" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J649" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K649" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
@@ -28861,10 +30091,20 @@
       <c r="G650" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H650" s="6" t="inlineStr"/>
-      <c r="I650" s="6" t="inlineStr"/>
-      <c r="J650" s="6" t="inlineStr"/>
-      <c r="K650" s="6" t="inlineStr"/>
+      <c r="H650" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I650" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J650" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K650" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
@@ -28900,10 +30140,20 @@
       <c r="G651" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H651" s="6" t="inlineStr"/>
-      <c r="I651" s="6" t="inlineStr"/>
-      <c r="J651" s="6" t="inlineStr"/>
-      <c r="K651" s="6" t="inlineStr"/>
+      <c r="H651" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I651" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J651" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K651" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="2" t="inlineStr">
@@ -28978,10 +30228,20 @@
       <c r="G653" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H653" s="6" t="inlineStr"/>
-      <c r="I653" s="6" t="inlineStr"/>
-      <c r="J653" s="6" t="inlineStr"/>
-      <c r="K653" s="6" t="inlineStr"/>
+      <c r="H653" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I653" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J653" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K653" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
@@ -29017,10 +30277,20 @@
       <c r="G654" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H654" s="6" t="inlineStr"/>
-      <c r="I654" s="6" t="inlineStr"/>
-      <c r="J654" s="6" t="inlineStr"/>
-      <c r="K654" s="6" t="inlineStr"/>
+      <c r="H654" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I654" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J654" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K654" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
@@ -29056,10 +30326,20 @@
       <c r="G655" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H655" s="6" t="inlineStr"/>
-      <c r="I655" s="6" t="inlineStr"/>
-      <c r="J655" s="6" t="inlineStr"/>
-      <c r="K655" s="6" t="inlineStr"/>
+      <c r="H655" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I655" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J655" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K655" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -29095,10 +30375,20 @@
       <c r="G656" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H656" s="6" t="inlineStr"/>
-      <c r="I656" s="6" t="inlineStr"/>
-      <c r="J656" s="6" t="inlineStr"/>
-      <c r="K656" s="6" t="inlineStr"/>
+      <c r="H656" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I656" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J656" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K656" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
@@ -29134,10 +30424,20 @@
       <c r="G657" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H657" s="6" t="inlineStr"/>
-      <c r="I657" s="6" t="inlineStr"/>
-      <c r="J657" s="6" t="inlineStr"/>
-      <c r="K657" s="6" t="inlineStr"/>
+      <c r="H657" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I657" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J657" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K657" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -29212,10 +30512,20 @@
       <c r="G659" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H659" s="6" t="inlineStr"/>
-      <c r="I659" s="6" t="inlineStr"/>
-      <c r="J659" s="6" t="inlineStr"/>
-      <c r="K659" s="6" t="inlineStr"/>
+      <c r="H659" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I659" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J659" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K659" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -29251,10 +30561,20 @@
       <c r="G660" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H660" s="6" t="inlineStr"/>
-      <c r="I660" s="6" t="inlineStr"/>
-      <c r="J660" s="6" t="inlineStr"/>
-      <c r="K660" s="6" t="inlineStr"/>
+      <c r="H660" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I660" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J660" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K660" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
@@ -29290,10 +30610,20 @@
       <c r="G661" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H661" s="6" t="inlineStr"/>
-      <c r="I661" s="6" t="inlineStr"/>
-      <c r="J661" s="6" t="inlineStr"/>
-      <c r="K661" s="6" t="inlineStr"/>
+      <c r="H661" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I661" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J661" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K661" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
@@ -29329,10 +30659,20 @@
       <c r="G662" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H662" s="6" t="inlineStr"/>
-      <c r="I662" s="6" t="inlineStr"/>
-      <c r="J662" s="6" t="inlineStr"/>
-      <c r="K662" s="6" t="inlineStr"/>
+      <c r="H662" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I662" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J662" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K662" s="4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="2" t="inlineStr">
@@ -29368,10 +30708,20 @@
       <c r="G663" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H663" s="6" t="inlineStr"/>
-      <c r="I663" s="6" t="inlineStr"/>
-      <c r="J663" s="6" t="inlineStr"/>
-      <c r="K663" s="6" t="inlineStr"/>
+      <c r="H663" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I663" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J663" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K663" s="5" t="n">
+        <v>-260</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
@@ -29407,10 +30757,20 @@
       <c r="G664" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H664" s="6" t="inlineStr"/>
-      <c r="I664" s="6" t="inlineStr"/>
-      <c r="J664" s="6" t="inlineStr"/>
-      <c r="K664" s="6" t="inlineStr"/>
+      <c r="H664" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I664" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J664" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K664" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
@@ -29446,10 +30806,20 @@
       <c r="G665" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H665" s="6" t="inlineStr"/>
-      <c r="I665" s="6" t="inlineStr"/>
-      <c r="J665" s="6" t="inlineStr"/>
-      <c r="K665" s="6" t="inlineStr"/>
+      <c r="H665" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I665" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J665" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K665" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
@@ -29485,10 +30855,20 @@
       <c r="G666" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H666" s="6" t="inlineStr"/>
-      <c r="I666" s="6" t="inlineStr"/>
-      <c r="J666" s="6" t="inlineStr"/>
-      <c r="K666" s="6" t="inlineStr"/>
+      <c r="H666" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I666" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J666" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K666" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
@@ -29524,10 +30904,20 @@
       <c r="G667" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H667" s="6" t="inlineStr"/>
-      <c r="I667" s="6" t="inlineStr"/>
-      <c r="J667" s="6" t="inlineStr"/>
-      <c r="K667" s="6" t="inlineStr"/>
+      <c r="H667" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I667" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J667" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K667" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="2" t="inlineStr">
@@ -29563,10 +30953,20 @@
       <c r="G668" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H668" s="6" t="inlineStr"/>
-      <c r="I668" s="6" t="inlineStr"/>
-      <c r="J668" s="6" t="inlineStr"/>
-      <c r="K668" s="6" t="inlineStr"/>
+      <c r="H668" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I668" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J668" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K668" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="2" t="inlineStr">
@@ -29641,10 +31041,20 @@
       <c r="G670" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H670" s="6" t="inlineStr"/>
-      <c r="I670" s="6" t="inlineStr"/>
-      <c r="J670" s="6" t="inlineStr"/>
-      <c r="K670" s="6" t="inlineStr"/>
+      <c r="H670" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I670" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J670" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K670" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -29680,10 +31090,20 @@
       <c r="G671" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H671" s="6" t="inlineStr"/>
-      <c r="I671" s="6" t="inlineStr"/>
-      <c r="J671" s="6" t="inlineStr"/>
-      <c r="K671" s="6" t="inlineStr"/>
+      <c r="H671" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I671" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J671" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K671" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
@@ -29719,10 +31139,20 @@
       <c r="G672" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H672" s="6" t="inlineStr"/>
-      <c r="I672" s="6" t="inlineStr"/>
-      <c r="J672" s="6" t="inlineStr"/>
-      <c r="K672" s="6" t="inlineStr"/>
+      <c r="H672" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I672" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J672" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K672" s="4" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
@@ -29797,10 +31227,20 @@
       <c r="G674" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H674" s="6" t="inlineStr"/>
-      <c r="I674" s="6" t="inlineStr"/>
-      <c r="J674" s="6" t="inlineStr"/>
-      <c r="K674" s="6" t="inlineStr"/>
+      <c r="H674" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I674" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J674" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K674" s="5" t="n">
+        <v>-330</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="inlineStr">
@@ -29836,10 +31276,20 @@
       <c r="G675" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H675" s="6" t="inlineStr"/>
-      <c r="I675" s="6" t="inlineStr"/>
-      <c r="J675" s="6" t="inlineStr"/>
-      <c r="K675" s="6" t="inlineStr"/>
+      <c r="H675" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I675" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J675" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K675" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="2" t="inlineStr">
@@ -29875,10 +31325,20 @@
       <c r="G676" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H676" s="6" t="inlineStr"/>
-      <c r="I676" s="6" t="inlineStr"/>
-      <c r="J676" s="6" t="inlineStr"/>
-      <c r="K676" s="6" t="inlineStr"/>
+      <c r="H676" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I676" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J676" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K676" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
@@ -29914,10 +31374,20 @@
       <c r="G677" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="H677" s="6" t="inlineStr"/>
-      <c r="I677" s="6" t="inlineStr"/>
-      <c r="J677" s="6" t="inlineStr"/>
-      <c r="K677" s="6" t="inlineStr"/>
+      <c r="H677" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I677" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J677" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K677" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="2" t="inlineStr">
@@ -29953,10 +31423,20 @@
       <c r="G678" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H678" s="6" t="inlineStr"/>
-      <c r="I678" s="6" t="inlineStr"/>
-      <c r="J678" s="6" t="inlineStr"/>
-      <c r="K678" s="6" t="inlineStr"/>
+      <c r="H678" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I678" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J678" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K678" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" s="2" t="inlineStr">
@@ -29992,10 +31472,20 @@
       <c r="G679" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H679" s="6" t="inlineStr"/>
-      <c r="I679" s="6" t="inlineStr"/>
-      <c r="J679" s="6" t="inlineStr"/>
-      <c r="K679" s="6" t="inlineStr"/>
+      <c r="H679" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I679" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J679" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K679" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="2" t="inlineStr">
@@ -30031,10 +31521,20 @@
       <c r="G680" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H680" s="6" t="inlineStr"/>
-      <c r="I680" s="6" t="inlineStr"/>
-      <c r="J680" s="6" t="inlineStr"/>
-      <c r="K680" s="6" t="inlineStr"/>
+      <c r="H680" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I680" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J680" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K680" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
@@ -30070,10 +31570,20 @@
       <c r="G681" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H681" s="6" t="inlineStr"/>
-      <c r="I681" s="6" t="inlineStr"/>
-      <c r="J681" s="6" t="inlineStr"/>
-      <c r="K681" s="6" t="inlineStr"/>
+      <c r="H681" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I681" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J681" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K681" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
@@ -30109,10 +31619,20 @@
       <c r="G682" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H682" s="6" t="inlineStr"/>
-      <c r="I682" s="6" t="inlineStr"/>
-      <c r="J682" s="6" t="inlineStr"/>
-      <c r="K682" s="6" t="inlineStr"/>
+      <c r="H682" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I682" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J682" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K682" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
@@ -30148,10 +31668,20 @@
       <c r="G683" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H683" s="6" t="inlineStr"/>
-      <c r="I683" s="6" t="inlineStr"/>
-      <c r="J683" s="6" t="inlineStr"/>
-      <c r="K683" s="6" t="inlineStr"/>
+      <c r="H683" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I683" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J683" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K683" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -30187,10 +31717,20 @@
       <c r="G684" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H684" s="6" t="inlineStr"/>
-      <c r="I684" s="6" t="inlineStr"/>
-      <c r="J684" s="6" t="inlineStr"/>
-      <c r="K684" s="6" t="inlineStr"/>
+      <c r="H684" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I684" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J684" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K684" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" s="2" t="inlineStr">
@@ -30226,10 +31766,20 @@
       <c r="G685" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H685" s="6" t="inlineStr"/>
-      <c r="I685" s="6" t="inlineStr"/>
-      <c r="J685" s="6" t="inlineStr"/>
-      <c r="K685" s="6" t="inlineStr"/>
+      <c r="H685" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I685" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J685" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K685" s="4" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -30265,10 +31815,20 @@
       <c r="G686" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="H686" s="6" t="inlineStr"/>
-      <c r="I686" s="6" t="inlineStr"/>
-      <c r="J686" s="6" t="inlineStr"/>
-      <c r="K686" s="6" t="inlineStr"/>
+      <c r="H686" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I686" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J686" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K686" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
@@ -30304,10 +31864,20 @@
       <c r="G687" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H687" s="6" t="inlineStr"/>
-      <c r="I687" s="6" t="inlineStr"/>
-      <c r="J687" s="6" t="inlineStr"/>
-      <c r="K687" s="6" t="inlineStr"/>
+      <c r="H687" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I687" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J687" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K687" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
@@ -30343,10 +31913,20 @@
       <c r="G688" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H688" s="6" t="inlineStr"/>
-      <c r="I688" s="6" t="inlineStr"/>
-      <c r="J688" s="6" t="inlineStr"/>
-      <c r="K688" s="6" t="inlineStr"/>
+      <c r="H688" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I688" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J688" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K688" s="4" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" s="2" t="inlineStr">
@@ -30382,10 +31962,20 @@
       <c r="G689" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H689" s="6" t="inlineStr"/>
-      <c r="I689" s="6" t="inlineStr"/>
-      <c r="J689" s="6" t="inlineStr"/>
-      <c r="K689" s="6" t="inlineStr"/>
+      <c r="H689" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I689" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J689" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K689" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -30421,10 +32011,20 @@
       <c r="G690" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H690" s="6" t="inlineStr"/>
-      <c r="I690" s="6" t="inlineStr"/>
-      <c r="J690" s="6" t="inlineStr"/>
-      <c r="K690" s="6" t="inlineStr"/>
+      <c r="H690" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I690" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J690" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K690" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" s="2" t="inlineStr">
@@ -30460,10 +32060,20 @@
       <c r="G691" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H691" s="6" t="inlineStr"/>
-      <c r="I691" s="6" t="inlineStr"/>
-      <c r="J691" s="6" t="inlineStr"/>
-      <c r="K691" s="6" t="inlineStr"/>
+      <c r="H691" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I691" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J691" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K691" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="inlineStr">
@@ -30499,10 +32109,20 @@
       <c r="G692" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H692" s="6" t="inlineStr"/>
-      <c r="I692" s="6" t="inlineStr"/>
-      <c r="J692" s="6" t="inlineStr"/>
-      <c r="K692" s="6" t="inlineStr"/>
+      <c r="H692" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I692" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J692" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K692" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
@@ -30538,10 +32158,20 @@
       <c r="G693" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H693" s="6" t="inlineStr"/>
-      <c r="I693" s="6" t="inlineStr"/>
-      <c r="J693" s="6" t="inlineStr"/>
-      <c r="K693" s="6" t="inlineStr"/>
+      <c r="H693" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I693" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J693" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K693" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
@@ -30577,10 +32207,20 @@
       <c r="G694" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="H694" s="6" t="inlineStr"/>
-      <c r="I694" s="6" t="inlineStr"/>
-      <c r="J694" s="6" t="inlineStr"/>
-      <c r="K694" s="6" t="inlineStr"/>
+      <c r="H694" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I694" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J694" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K694" s="4" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
@@ -30616,10 +32256,20 @@
       <c r="G695" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H695" s="6" t="inlineStr"/>
-      <c r="I695" s="6" t="inlineStr"/>
-      <c r="J695" s="6" t="inlineStr"/>
-      <c r="K695" s="6" t="inlineStr"/>
+      <c r="H695" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I695" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J695" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K695" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
@@ -30655,10 +32305,20 @@
       <c r="G696" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H696" s="6" t="inlineStr"/>
-      <c r="I696" s="6" t="inlineStr"/>
-      <c r="J696" s="6" t="inlineStr"/>
-      <c r="K696" s="6" t="inlineStr"/>
+      <c r="H696" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I696" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J696" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K696" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
@@ -30694,10 +32354,20 @@
       <c r="G697" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H697" s="6" t="inlineStr"/>
-      <c r="I697" s="6" t="inlineStr"/>
-      <c r="J697" s="6" t="inlineStr"/>
-      <c r="K697" s="6" t="inlineStr"/>
+      <c r="H697" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I697" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J697" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K697" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="2" t="inlineStr">
@@ -30733,10 +32403,20 @@
       <c r="G698" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H698" s="6" t="inlineStr"/>
-      <c r="I698" s="6" t="inlineStr"/>
-      <c r="J698" s="6" t="inlineStr"/>
-      <c r="K698" s="6" t="inlineStr"/>
+      <c r="H698" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I698" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J698" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K698" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="2" t="inlineStr">
@@ -30772,10 +32452,20 @@
       <c r="G699" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H699" s="6" t="inlineStr"/>
-      <c r="I699" s="6" t="inlineStr"/>
-      <c r="J699" s="6" t="inlineStr"/>
-      <c r="K699" s="6" t="inlineStr"/>
+      <c r="H699" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I699" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J699" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K699" s="5" t="n">
+        <v>-290</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
@@ -30811,10 +32501,20 @@
       <c r="G700" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H700" s="6" t="inlineStr"/>
-      <c r="I700" s="6" t="inlineStr"/>
-      <c r="J700" s="6" t="inlineStr"/>
-      <c r="K700" s="6" t="inlineStr"/>
+      <c r="H700" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I700" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J700" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K700" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
@@ -30850,10 +32550,20 @@
       <c r="G701" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H701" s="6" t="inlineStr"/>
-      <c r="I701" s="6" t="inlineStr"/>
-      <c r="J701" s="6" t="inlineStr"/>
-      <c r="K701" s="6" t="inlineStr"/>
+      <c r="H701" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I701" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J701" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K701" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="inlineStr">
@@ -30889,10 +32599,20 @@
       <c r="G702" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H702" s="6" t="inlineStr"/>
-      <c r="I702" s="6" t="inlineStr"/>
-      <c r="J702" s="6" t="inlineStr"/>
-      <c r="K702" s="6" t="inlineStr"/>
+      <c r="H702" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I702" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J702" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K702" s="5" t="n">
+        <v>-340</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
@@ -30928,10 +32648,20 @@
       <c r="G703" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H703" s="6" t="inlineStr"/>
-      <c r="I703" s="6" t="inlineStr"/>
-      <c r="J703" s="6" t="inlineStr"/>
-      <c r="K703" s="6" t="inlineStr"/>
+      <c r="H703" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I703" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J703" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K703" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="inlineStr">
@@ -30967,10 +32697,20 @@
       <c r="G704" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H704" s="6" t="inlineStr"/>
-      <c r="I704" s="6" t="inlineStr"/>
-      <c r="J704" s="6" t="inlineStr"/>
-      <c r="K704" s="6" t="inlineStr"/>
+      <c r="H704" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I704" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J704" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K704" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="inlineStr">
@@ -31006,10 +32746,20 @@
       <c r="G705" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H705" s="6" t="inlineStr"/>
-      <c r="I705" s="6" t="inlineStr"/>
-      <c r="J705" s="6" t="inlineStr"/>
-      <c r="K705" s="6" t="inlineStr"/>
+      <c r="H705" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I705" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J705" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K705" s="5" t="n">
+        <v>-300</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="inlineStr">
@@ -31045,10 +32795,20 @@
       <c r="G706" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H706" s="6" t="inlineStr"/>
-      <c r="I706" s="6" t="inlineStr"/>
-      <c r="J706" s="6" t="inlineStr"/>
-      <c r="K706" s="6" t="inlineStr"/>
+      <c r="H706" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I706" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J706" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K706" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="inlineStr">
@@ -31084,10 +32844,20 @@
       <c r="G707" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H707" s="6" t="inlineStr"/>
-      <c r="I707" s="6" t="inlineStr"/>
-      <c r="J707" s="6" t="inlineStr"/>
-      <c r="K707" s="6" t="inlineStr"/>
+      <c r="H707" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I707" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J707" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K707" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="inlineStr">
@@ -31123,10 +32893,20 @@
       <c r="G708" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H708" s="6" t="inlineStr"/>
-      <c r="I708" s="6" t="inlineStr"/>
-      <c r="J708" s="6" t="inlineStr"/>
-      <c r="K708" s="6" t="inlineStr"/>
+      <c r="H708" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I708" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J708" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K708" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -31162,10 +32942,20 @@
       <c r="G709" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H709" s="6" t="inlineStr"/>
-      <c r="I709" s="6" t="inlineStr"/>
-      <c r="J709" s="6" t="inlineStr"/>
-      <c r="K709" s="6" t="inlineStr"/>
+      <c r="H709" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I709" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J709" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K709" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -31201,10 +32991,20 @@
       <c r="G710" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H710" s="6" t="inlineStr"/>
-      <c r="I710" s="6" t="inlineStr"/>
-      <c r="J710" s="6" t="inlineStr"/>
-      <c r="K710" s="6" t="inlineStr"/>
+      <c r="H710" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I710" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J710" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K710" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="2" t="inlineStr">
@@ -31240,10 +33040,20 @@
       <c r="G711" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H711" s="6" t="inlineStr"/>
-      <c r="I711" s="6" t="inlineStr"/>
-      <c r="J711" s="6" t="inlineStr"/>
-      <c r="K711" s="6" t="inlineStr"/>
+      <c r="H711" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I711" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J711" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K711" s="4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="2" t="inlineStr">
@@ -31279,10 +33089,20 @@
       <c r="G712" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H712" s="6" t="inlineStr"/>
-      <c r="I712" s="6" t="inlineStr"/>
-      <c r="J712" s="6" t="inlineStr"/>
-      <c r="K712" s="6" t="inlineStr"/>
+      <c r="H712" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I712" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J712" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K712" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -31318,10 +33138,20 @@
       <c r="G713" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H713" s="6" t="inlineStr"/>
-      <c r="I713" s="6" t="inlineStr"/>
-      <c r="J713" s="6" t="inlineStr"/>
-      <c r="K713" s="6" t="inlineStr"/>
+      <c r="H713" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I713" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J713" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K713" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -31357,10 +33187,20 @@
       <c r="G714" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H714" s="6" t="inlineStr"/>
-      <c r="I714" s="6" t="inlineStr"/>
-      <c r="J714" s="6" t="inlineStr"/>
-      <c r="K714" s="6" t="inlineStr"/>
+      <c r="H714" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I714" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J714" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K714" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" s="2" t="inlineStr">
@@ -31396,10 +33236,20 @@
       <c r="G715" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H715" s="6" t="inlineStr"/>
-      <c r="I715" s="6" t="inlineStr"/>
-      <c r="J715" s="6" t="inlineStr"/>
-      <c r="K715" s="6" t="inlineStr"/>
+      <c r="H715" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I715" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J715" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K715" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
@@ -31591,10 +33441,20 @@
       <c r="G720" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H720" s="6" t="inlineStr"/>
-      <c r="I720" s="6" t="inlineStr"/>
-      <c r="J720" s="6" t="inlineStr"/>
-      <c r="K720" s="6" t="inlineStr"/>
+      <c r="H720" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I720" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J720" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K720" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="inlineStr">
@@ -31630,10 +33490,20 @@
       <c r="G721" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H721" s="6" t="inlineStr"/>
-      <c r="I721" s="6" t="inlineStr"/>
-      <c r="J721" s="6" t="inlineStr"/>
-      <c r="K721" s="6" t="inlineStr"/>
+      <c r="H721" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I721" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J721" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K721" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" s="2" t="inlineStr">
@@ -31825,10 +33695,20 @@
       <c r="G726" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H726" s="6" t="inlineStr"/>
-      <c r="I726" s="6" t="inlineStr"/>
-      <c r="J726" s="6" t="inlineStr"/>
-      <c r="K726" s="6" t="inlineStr"/>
+      <c r="H726" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I726" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J726" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K726" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" s="2" t="inlineStr">
@@ -31864,10 +33744,20 @@
       <c r="G727" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H727" s="6" t="inlineStr"/>
-      <c r="I727" s="6" t="inlineStr"/>
-      <c r="J727" s="6" t="inlineStr"/>
-      <c r="K727" s="6" t="inlineStr"/>
+      <c r="H727" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I727" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J727" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K727" s="4" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="2" t="inlineStr">
@@ -32020,10 +33910,20 @@
       <c r="G731" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H731" s="6" t="inlineStr"/>
-      <c r="I731" s="6" t="inlineStr"/>
-      <c r="J731" s="6" t="inlineStr"/>
-      <c r="K731" s="6" t="inlineStr"/>
+      <c r="H731" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I731" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J731" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K731" s="5" t="n">
+        <v>-295</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="inlineStr">
@@ -32059,10 +33959,20 @@
       <c r="G732" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H732" s="6" t="inlineStr"/>
-      <c r="I732" s="6" t="inlineStr"/>
-      <c r="J732" s="6" t="inlineStr"/>
-      <c r="K732" s="6" t="inlineStr"/>
+      <c r="H732" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I732" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J732" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K732" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="inlineStr">
@@ -32176,10 +34086,20 @@
       <c r="G735" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H735" s="6" t="inlineStr"/>
-      <c r="I735" s="6" t="inlineStr"/>
-      <c r="J735" s="6" t="inlineStr"/>
-      <c r="K735" s="6" t="inlineStr"/>
+      <c r="H735" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I735" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J735" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K735" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="inlineStr">
@@ -32293,10 +34213,20 @@
       <c r="G738" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H738" s="6" t="inlineStr"/>
-      <c r="I738" s="6" t="inlineStr"/>
-      <c r="J738" s="6" t="inlineStr"/>
-      <c r="K738" s="6" t="inlineStr"/>
+      <c r="H738" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I738" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J738" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K738" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="inlineStr">
@@ -32332,10 +34262,20 @@
       <c r="G739" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H739" s="6" t="inlineStr"/>
-      <c r="I739" s="6" t="inlineStr"/>
-      <c r="J739" s="6" t="inlineStr"/>
-      <c r="K739" s="6" t="inlineStr"/>
+      <c r="H739" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I739" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J739" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K739" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="inlineStr">
@@ -32371,10 +34311,20 @@
       <c r="G740" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H740" s="6" t="inlineStr"/>
-      <c r="I740" s="6" t="inlineStr"/>
-      <c r="J740" s="6" t="inlineStr"/>
-      <c r="K740" s="6" t="inlineStr"/>
+      <c r="H740" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I740" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J740" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K740" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="inlineStr">
@@ -32410,10 +34360,20 @@
       <c r="G741" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H741" s="6" t="inlineStr"/>
-      <c r="I741" s="6" t="inlineStr"/>
-      <c r="J741" s="6" t="inlineStr"/>
-      <c r="K741" s="6" t="inlineStr"/>
+      <c r="H741" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I741" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J741" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K741" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="inlineStr">
@@ -32488,10 +34448,20 @@
       <c r="G743" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H743" s="6" t="inlineStr"/>
-      <c r="I743" s="6" t="inlineStr"/>
-      <c r="J743" s="6" t="inlineStr"/>
-      <c r="K743" s="6" t="inlineStr"/>
+      <c r="H743" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I743" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J743" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K743" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
@@ -32527,10 +34497,20 @@
       <c r="G744" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H744" s="6" t="inlineStr"/>
-      <c r="I744" s="6" t="inlineStr"/>
-      <c r="J744" s="6" t="inlineStr"/>
-      <c r="K744" s="6" t="inlineStr"/>
+      <c r="H744" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I744" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J744" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K744" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="inlineStr">
@@ -32566,10 +34546,20 @@
       <c r="G745" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H745" s="6" t="inlineStr"/>
-      <c r="I745" s="6" t="inlineStr"/>
-      <c r="J745" s="6" t="inlineStr"/>
-      <c r="K745" s="6" t="inlineStr"/>
+      <c r="H745" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I745" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J745" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K745" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="inlineStr">
@@ -32605,10 +34595,20 @@
       <c r="G746" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H746" s="6" t="inlineStr"/>
-      <c r="I746" s="6" t="inlineStr"/>
-      <c r="J746" s="6" t="inlineStr"/>
-      <c r="K746" s="6" t="inlineStr"/>
+      <c r="H746" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I746" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J746" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K746" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="inlineStr">
@@ -32839,10 +34839,20 @@
       <c r="G752" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H752" s="6" t="inlineStr"/>
-      <c r="I752" s="6" t="inlineStr"/>
-      <c r="J752" s="6" t="inlineStr"/>
-      <c r="K752" s="6" t="inlineStr"/>
+      <c r="H752" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I752" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J752" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K752" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="inlineStr">
@@ -32878,10 +34888,20 @@
       <c r="G753" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H753" s="6" t="inlineStr"/>
-      <c r="I753" s="6" t="inlineStr"/>
-      <c r="J753" s="6" t="inlineStr"/>
-      <c r="K753" s="6" t="inlineStr"/>
+      <c r="H753" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I753" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J753" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K753" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="inlineStr">
@@ -32917,10 +34937,20 @@
       <c r="G754" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H754" s="6" t="inlineStr"/>
-      <c r="I754" s="6" t="inlineStr"/>
-      <c r="J754" s="6" t="inlineStr"/>
-      <c r="K754" s="6" t="inlineStr"/>
+      <c r="H754" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I754" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J754" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K754" s="4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="inlineStr">
@@ -32995,10 +35025,20 @@
       <c r="G756" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H756" s="6" t="inlineStr"/>
-      <c r="I756" s="6" t="inlineStr"/>
-      <c r="J756" s="6" t="inlineStr"/>
-      <c r="K756" s="6" t="inlineStr"/>
+      <c r="H756" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I756" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J756" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K756" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="2" t="inlineStr">
@@ -33034,10 +35074,20 @@
       <c r="G757" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H757" s="6" t="inlineStr"/>
-      <c r="I757" s="6" t="inlineStr"/>
-      <c r="J757" s="6" t="inlineStr"/>
-      <c r="K757" s="6" t="inlineStr"/>
+      <c r="H757" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I757" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J757" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K757" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="inlineStr">
@@ -33112,10 +35162,20 @@
       <c r="G759" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H759" s="6" t="inlineStr"/>
-      <c r="I759" s="6" t="inlineStr"/>
-      <c r="J759" s="6" t="inlineStr"/>
-      <c r="K759" s="6" t="inlineStr"/>
+      <c r="H759" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I759" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J759" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K759" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" s="2" t="inlineStr">
@@ -33151,10 +35211,20 @@
       <c r="G760" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H760" s="6" t="inlineStr"/>
-      <c r="I760" s="6" t="inlineStr"/>
-      <c r="J760" s="6" t="inlineStr"/>
-      <c r="K760" s="6" t="inlineStr"/>
+      <c r="H760" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I760" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J760" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K760" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="inlineStr">
@@ -33190,10 +35260,20 @@
       <c r="G761" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H761" s="6" t="inlineStr"/>
-      <c r="I761" s="6" t="inlineStr"/>
-      <c r="J761" s="6" t="inlineStr"/>
-      <c r="K761" s="6" t="inlineStr"/>
+      <c r="H761" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I761" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J761" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K761" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="inlineStr">
@@ -33385,10 +35465,20 @@
       <c r="G766" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H766" s="6" t="inlineStr"/>
-      <c r="I766" s="6" t="inlineStr"/>
-      <c r="J766" s="6" t="inlineStr"/>
-      <c r="K766" s="6" t="inlineStr"/>
+      <c r="H766" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I766" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J766" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K766" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="2" t="inlineStr">
@@ -33424,10 +35514,20 @@
       <c r="G767" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H767" s="6" t="inlineStr"/>
-      <c r="I767" s="6" t="inlineStr"/>
-      <c r="J767" s="6" t="inlineStr"/>
-      <c r="K767" s="6" t="inlineStr"/>
+      <c r="H767" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I767" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J767" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K767" s="4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="2" t="inlineStr">
@@ -33463,10 +35563,20 @@
       <c r="G768" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H768" s="6" t="inlineStr"/>
-      <c r="I768" s="6" t="inlineStr"/>
-      <c r="J768" s="6" t="inlineStr"/>
-      <c r="K768" s="6" t="inlineStr"/>
+      <c r="H768" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I768" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J768" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K768" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" s="2" t="inlineStr">
@@ -33502,10 +35612,20 @@
       <c r="G769" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H769" s="6" t="inlineStr"/>
-      <c r="I769" s="6" t="inlineStr"/>
-      <c r="J769" s="6" t="inlineStr"/>
-      <c r="K769" s="6" t="inlineStr"/>
+      <c r="H769" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I769" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J769" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K769" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="2" t="inlineStr">
@@ -33541,10 +35661,20 @@
       <c r="G770" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H770" s="6" t="inlineStr"/>
-      <c r="I770" s="6" t="inlineStr"/>
-      <c r="J770" s="6" t="inlineStr"/>
-      <c r="K770" s="6" t="inlineStr"/>
+      <c r="H770" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I770" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J770" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K770" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="inlineStr">
@@ -33580,10 +35710,20 @@
       <c r="G771" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H771" s="6" t="inlineStr"/>
-      <c r="I771" s="6" t="inlineStr"/>
-      <c r="J771" s="6" t="inlineStr"/>
-      <c r="K771" s="6" t="inlineStr"/>
+      <c r="H771" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I771" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J771" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K771" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="2" t="inlineStr">
@@ -33697,10 +35837,20 @@
       <c r="G774" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H774" s="6" t="inlineStr"/>
-      <c r="I774" s="6" t="inlineStr"/>
-      <c r="J774" s="6" t="inlineStr"/>
-      <c r="K774" s="6" t="inlineStr"/>
+      <c r="H774" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I774" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J774" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K774" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" s="2" t="inlineStr">
@@ -33736,10 +35886,20 @@
       <c r="G775" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H775" s="6" t="inlineStr"/>
-      <c r="I775" s="6" t="inlineStr"/>
-      <c r="J775" s="6" t="inlineStr"/>
-      <c r="K775" s="6" t="inlineStr"/>
+      <c r="H775" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I775" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J775" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K775" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="2" t="inlineStr">
@@ -33775,10 +35935,20 @@
       <c r="G776" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H776" s="6" t="inlineStr"/>
-      <c r="I776" s="6" t="inlineStr"/>
-      <c r="J776" s="6" t="inlineStr"/>
-      <c r="K776" s="6" t="inlineStr"/>
+      <c r="H776" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I776" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J776" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K776" s="5" t="n">
+        <v>-300</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" s="2" t="inlineStr">
@@ -33814,10 +35984,20 @@
       <c r="G777" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H777" s="6" t="inlineStr"/>
-      <c r="I777" s="6" t="inlineStr"/>
-      <c r="J777" s="6" t="inlineStr"/>
-      <c r="K777" s="6" t="inlineStr"/>
+      <c r="H777" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I777" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J777" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K777" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" s="2" t="inlineStr">
@@ -33853,10 +36033,20 @@
       <c r="G778" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H778" s="6" t="inlineStr"/>
-      <c r="I778" s="6" t="inlineStr"/>
-      <c r="J778" s="6" t="inlineStr"/>
-      <c r="K778" s="6" t="inlineStr"/>
+      <c r="H778" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I778" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J778" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K778" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" s="2" t="inlineStr">
@@ -33892,10 +36082,20 @@
       <c r="G779" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H779" s="6" t="inlineStr"/>
-      <c r="I779" s="6" t="inlineStr"/>
-      <c r="J779" s="6" t="inlineStr"/>
-      <c r="K779" s="6" t="inlineStr"/>
+      <c r="H779" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I779" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J779" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K779" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="2" t="inlineStr">
@@ -33931,10 +36131,20 @@
       <c r="G780" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H780" s="6" t="inlineStr"/>
-      <c r="I780" s="6" t="inlineStr"/>
-      <c r="J780" s="6" t="inlineStr"/>
-      <c r="K780" s="6" t="inlineStr"/>
+      <c r="H780" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I780" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J780" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K780" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="2" t="inlineStr">
@@ -34087,10 +36297,20 @@
       <c r="G784" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H784" s="6" t="inlineStr"/>
-      <c r="I784" s="6" t="inlineStr"/>
-      <c r="J784" s="6" t="inlineStr"/>
-      <c r="K784" s="6" t="inlineStr"/>
+      <c r="H784" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I784" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J784" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K784" s="5" t="n">
+        <v>-950</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785" s="2" t="inlineStr">
@@ -34126,10 +36346,20 @@
       <c r="G785" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H785" s="6" t="inlineStr"/>
-      <c r="I785" s="6" t="inlineStr"/>
-      <c r="J785" s="6" t="inlineStr"/>
-      <c r="K785" s="6" t="inlineStr"/>
+      <c r="H785" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I785" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J785" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K785" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="2" t="inlineStr">
@@ -34165,10 +36395,20 @@
       <c r="G786" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H786" s="6" t="inlineStr"/>
-      <c r="I786" s="6" t="inlineStr"/>
-      <c r="J786" s="6" t="inlineStr"/>
-      <c r="K786" s="6" t="inlineStr"/>
+      <c r="H786" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I786" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J786" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K786" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" s="2" t="inlineStr">
@@ -34204,10 +36444,20 @@
       <c r="G787" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H787" s="6" t="inlineStr"/>
-      <c r="I787" s="6" t="inlineStr"/>
-      <c r="J787" s="6" t="inlineStr"/>
-      <c r="K787" s="6" t="inlineStr"/>
+      <c r="H787" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I787" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J787" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K787" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="2" t="inlineStr">
@@ -34243,10 +36493,20 @@
       <c r="G788" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H788" s="6" t="inlineStr"/>
-      <c r="I788" s="6" t="inlineStr"/>
-      <c r="J788" s="6" t="inlineStr"/>
-      <c r="K788" s="6" t="inlineStr"/>
+      <c r="H788" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I788" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J788" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K788" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="2" t="inlineStr">
@@ -34321,10 +36581,20 @@
       <c r="G790" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H790" s="6" t="inlineStr"/>
-      <c r="I790" s="6" t="inlineStr"/>
-      <c r="J790" s="6" t="inlineStr"/>
-      <c r="K790" s="6" t="inlineStr"/>
+      <c r="H790" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I790" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J790" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K790" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" s="2" t="inlineStr">
@@ -34711,10 +36981,20 @@
       <c r="G800" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H800" s="6" t="inlineStr"/>
-      <c r="I800" s="6" t="inlineStr"/>
-      <c r="J800" s="6" t="inlineStr"/>
-      <c r="K800" s="6" t="inlineStr"/>
+      <c r="H800" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I800" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J800" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K800" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" s="2" t="inlineStr">
@@ -34750,10 +37030,20 @@
       <c r="G801" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H801" s="6" t="inlineStr"/>
-      <c r="I801" s="6" t="inlineStr"/>
-      <c r="J801" s="6" t="inlineStr"/>
-      <c r="K801" s="6" t="inlineStr"/>
+      <c r="H801" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I801" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J801" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K801" s="4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="inlineStr">
@@ -34789,10 +37079,20 @@
       <c r="G802" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H802" s="6" t="inlineStr"/>
-      <c r="I802" s="6" t="inlineStr"/>
-      <c r="J802" s="6" t="inlineStr"/>
-      <c r="K802" s="6" t="inlineStr"/>
+      <c r="H802" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I802" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J802" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K802" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="inlineStr">
@@ -34828,10 +37128,20 @@
       <c r="G803" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H803" s="6" t="inlineStr"/>
-      <c r="I803" s="6" t="inlineStr"/>
-      <c r="J803" s="6" t="inlineStr"/>
-      <c r="K803" s="6" t="inlineStr"/>
+      <c r="H803" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J803" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K803" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="inlineStr">
@@ -34867,10 +37177,20 @@
       <c r="G804" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H804" s="6" t="inlineStr"/>
-      <c r="I804" s="6" t="inlineStr"/>
-      <c r="J804" s="6" t="inlineStr"/>
-      <c r="K804" s="6" t="inlineStr"/>
+      <c r="H804" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I804" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J804" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K804" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="inlineStr">
@@ -35413,10 +37733,20 @@
       <c r="G818" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H818" s="6" t="inlineStr"/>
-      <c r="I818" s="6" t="inlineStr"/>
-      <c r="J818" s="6" t="inlineStr"/>
-      <c r="K818" s="6" t="inlineStr"/>
+      <c r="H818" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I818" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J818" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K818" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="inlineStr">
@@ -35452,10 +37782,20 @@
       <c r="G819" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H819" s="6" t="inlineStr"/>
-      <c r="I819" s="6" t="inlineStr"/>
-      <c r="J819" s="6" t="inlineStr"/>
-      <c r="K819" s="6" t="inlineStr"/>
+      <c r="H819" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I819" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J819" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K819" s="4" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="2" t="inlineStr">
@@ -35491,10 +37831,20 @@
       <c r="G820" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="H820" s="6" t="inlineStr"/>
-      <c r="I820" s="6" t="inlineStr"/>
-      <c r="J820" s="6" t="inlineStr"/>
-      <c r="K820" s="6" t="inlineStr"/>
+      <c r="H820" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I820" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J820" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K820" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821" s="2" t="inlineStr">
@@ -35647,10 +37997,20 @@
       <c r="G824" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H824" s="6" t="inlineStr"/>
-      <c r="I824" s="6" t="inlineStr"/>
-      <c r="J824" s="6" t="inlineStr"/>
-      <c r="K824" s="6" t="inlineStr"/>
+      <c r="H824" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I824" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J824" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K824" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825" s="2" t="inlineStr">
@@ -35686,10 +38046,20 @@
       <c r="G825" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H825" s="6" t="inlineStr"/>
-      <c r="I825" s="6" t="inlineStr"/>
-      <c r="J825" s="6" t="inlineStr"/>
-      <c r="K825" s="6" t="inlineStr"/>
+      <c r="H825" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I825" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J825" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K825" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826" s="2" t="inlineStr">
@@ -35725,10 +38095,20 @@
       <c r="G826" s="2" t="n">
         <v>2.14</v>
       </c>
-      <c r="H826" s="6" t="inlineStr"/>
-      <c r="I826" s="6" t="inlineStr"/>
-      <c r="J826" s="6" t="inlineStr"/>
-      <c r="K826" s="6" t="inlineStr"/>
+      <c r="H826" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I826" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J826" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K826" s="4" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827" s="2" t="inlineStr">
@@ -35764,10 +38144,20 @@
       <c r="G827" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="H827" s="6" t="inlineStr"/>
-      <c r="I827" s="6" t="inlineStr"/>
-      <c r="J827" s="6" t="inlineStr"/>
-      <c r="K827" s="6" t="inlineStr"/>
+      <c r="H827" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I827" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J827" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K827" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828" s="2" t="inlineStr">
@@ -35881,10 +38271,20 @@
       <c r="G830" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H830" s="6" t="inlineStr"/>
-      <c r="I830" s="6" t="inlineStr"/>
-      <c r="J830" s="6" t="inlineStr"/>
-      <c r="K830" s="6" t="inlineStr"/>
+      <c r="H830" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I830" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J830" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K830" s="5" t="n">
+        <v>-295</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="inlineStr">
@@ -35920,10 +38320,20 @@
       <c r="G831" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H831" s="6" t="inlineStr"/>
-      <c r="I831" s="6" t="inlineStr"/>
-      <c r="J831" s="6" t="inlineStr"/>
-      <c r="K831" s="6" t="inlineStr"/>
+      <c r="H831" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I831" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J831" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K831" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -36037,10 +38447,20 @@
       <c r="G834" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H834" s="6" t="inlineStr"/>
-      <c r="I834" s="6" t="inlineStr"/>
-      <c r="J834" s="6" t="inlineStr"/>
-      <c r="K834" s="6" t="inlineStr"/>
+      <c r="H834" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I834" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J834" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K834" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" s="2" t="inlineStr">
@@ -36076,10 +38496,20 @@
       <c r="G835" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H835" s="6" t="inlineStr"/>
-      <c r="I835" s="6" t="inlineStr"/>
-      <c r="J835" s="6" t="inlineStr"/>
-      <c r="K835" s="6" t="inlineStr"/>
+      <c r="H835" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I835" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J835" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K835" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836" s="2" t="inlineStr">
@@ -36115,10 +38545,20 @@
       <c r="G836" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H836" s="6" t="inlineStr"/>
-      <c r="I836" s="6" t="inlineStr"/>
-      <c r="J836" s="6" t="inlineStr"/>
-      <c r="K836" s="6" t="inlineStr"/>
+      <c r="H836" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I836" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J836" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K836" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" s="2" t="inlineStr">
@@ -36154,10 +38594,20 @@
       <c r="G837" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H837" s="6" t="inlineStr"/>
-      <c r="I837" s="6" t="inlineStr"/>
-      <c r="J837" s="6" t="inlineStr"/>
-      <c r="K837" s="6" t="inlineStr"/>
+      <c r="H837" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I837" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J837" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K837" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838" s="2" t="inlineStr">
@@ -36193,10 +38643,20 @@
       <c r="G838" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H838" s="6" t="inlineStr"/>
-      <c r="I838" s="6" t="inlineStr"/>
-      <c r="J838" s="6" t="inlineStr"/>
-      <c r="K838" s="6" t="inlineStr"/>
+      <c r="H838" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I838" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J838" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K838" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" s="2" t="inlineStr">
@@ -36505,10 +38965,20 @@
       <c r="G846" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H846" s="6" t="inlineStr"/>
-      <c r="I846" s="6" t="inlineStr"/>
-      <c r="J846" s="6" t="inlineStr"/>
-      <c r="K846" s="6" t="inlineStr"/>
+      <c r="H846" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I846" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J846" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K846" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847" s="2" t="inlineStr">
@@ -36544,10 +39014,20 @@
       <c r="G847" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H847" s="6" t="inlineStr"/>
-      <c r="I847" s="6" t="inlineStr"/>
-      <c r="J847" s="6" t="inlineStr"/>
-      <c r="K847" s="6" t="inlineStr"/>
+      <c r="H847" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I847" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J847" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K847" s="4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" s="2" t="inlineStr">
@@ -36583,10 +39063,20 @@
       <c r="G848" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H848" s="6" t="inlineStr"/>
-      <c r="I848" s="6" t="inlineStr"/>
-      <c r="J848" s="6" t="inlineStr"/>
-      <c r="K848" s="6" t="inlineStr"/>
+      <c r="H848" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I848" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J848" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K848" s="5" t="n">
+        <v>-255</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" s="2" t="inlineStr">
@@ -36622,10 +39112,20 @@
       <c r="G849" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H849" s="6" t="inlineStr"/>
-      <c r="I849" s="6" t="inlineStr"/>
-      <c r="J849" s="6" t="inlineStr"/>
-      <c r="K849" s="6" t="inlineStr"/>
+      <c r="H849" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I849" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J849" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K849" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="inlineStr">
@@ -36700,10 +39200,20 @@
       <c r="G851" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H851" s="6" t="inlineStr"/>
-      <c r="I851" s="6" t="inlineStr"/>
-      <c r="J851" s="6" t="inlineStr"/>
-      <c r="K851" s="6" t="inlineStr"/>
+      <c r="H851" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I851" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J851" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K851" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
@@ -36739,10 +39249,20 @@
       <c r="G852" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H852" s="6" t="inlineStr"/>
-      <c r="I852" s="6" t="inlineStr"/>
-      <c r="J852" s="6" t="inlineStr"/>
-      <c r="K852" s="6" t="inlineStr"/>
+      <c r="H852" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I852" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J852" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K852" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="inlineStr">
@@ -36778,10 +39298,20 @@
       <c r="G853" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H853" s="6" t="inlineStr"/>
-      <c r="I853" s="6" t="inlineStr"/>
-      <c r="J853" s="6" t="inlineStr"/>
-      <c r="K853" s="6" t="inlineStr"/>
+      <c r="H853" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I853" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J853" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K853" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="inlineStr">
@@ -36817,10 +39347,20 @@
       <c r="G854" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H854" s="6" t="inlineStr"/>
-      <c r="I854" s="6" t="inlineStr"/>
-      <c r="J854" s="6" t="inlineStr"/>
-      <c r="K854" s="6" t="inlineStr"/>
+      <c r="H854" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I854" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J854" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K854" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="inlineStr">
@@ -36856,10 +39396,20 @@
       <c r="G855" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H855" s="6" t="inlineStr"/>
-      <c r="I855" s="6" t="inlineStr"/>
-      <c r="J855" s="6" t="inlineStr"/>
-      <c r="K855" s="6" t="inlineStr"/>
+      <c r="H855" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I855" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J855" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K855" s="5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
@@ -37090,10 +39640,20 @@
       <c r="G861" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H861" s="6" t="inlineStr"/>
-      <c r="I861" s="6" t="inlineStr"/>
-      <c r="J861" s="6" t="inlineStr"/>
-      <c r="K861" s="6" t="inlineStr"/>
+      <c r="H861" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I861" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J861" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K861" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862" s="2" t="inlineStr">
@@ -37129,10 +39689,20 @@
       <c r="G862" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H862" s="6" t="inlineStr"/>
-      <c r="I862" s="6" t="inlineStr"/>
-      <c r="J862" s="6" t="inlineStr"/>
-      <c r="K862" s="6" t="inlineStr"/>
+      <c r="H862" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I862" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J862" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K862" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="863">
       <c r="A863" s="2" t="inlineStr">
@@ -37168,10 +39738,20 @@
       <c r="G863" s="2" t="n">
         <v>2.46</v>
       </c>
-      <c r="H863" s="6" t="inlineStr"/>
-      <c r="I863" s="6" t="inlineStr"/>
-      <c r="J863" s="6" t="inlineStr"/>
-      <c r="K863" s="6" t="inlineStr"/>
+      <c r="H863" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I863" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J863" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K863" s="4" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="inlineStr">
@@ -37207,10 +39787,20 @@
       <c r="G864" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H864" s="6" t="inlineStr"/>
-      <c r="I864" s="6" t="inlineStr"/>
-      <c r="J864" s="6" t="inlineStr"/>
-      <c r="K864" s="6" t="inlineStr"/>
+      <c r="H864" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I864" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J864" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K864" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
@@ -37363,10 +39953,20 @@
       <c r="G868" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H868" s="6" t="inlineStr"/>
-      <c r="I868" s="6" t="inlineStr"/>
-      <c r="J868" s="6" t="inlineStr"/>
-      <c r="K868" s="6" t="inlineStr"/>
+      <c r="H868" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I868" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J868" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K868" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="inlineStr">
@@ -37402,10 +40002,20 @@
       <c r="G869" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H869" s="6" t="inlineStr"/>
-      <c r="I869" s="6" t="inlineStr"/>
-      <c r="J869" s="6" t="inlineStr"/>
-      <c r="K869" s="6" t="inlineStr"/>
+      <c r="H869" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I869" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J869" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K869" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
@@ -37519,10 +40129,20 @@
       <c r="G872" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H872" s="6" t="inlineStr"/>
-      <c r="I872" s="6" t="inlineStr"/>
-      <c r="J872" s="6" t="inlineStr"/>
-      <c r="K872" s="6" t="inlineStr"/>
+      <c r="H872" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I872" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J872" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K872" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="inlineStr">
@@ -37558,10 +40178,20 @@
       <c r="G873" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H873" s="6" t="inlineStr"/>
-      <c r="I873" s="6" t="inlineStr"/>
-      <c r="J873" s="6" t="inlineStr"/>
-      <c r="K873" s="6" t="inlineStr"/>
+      <c r="H873" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I873" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J873" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K873" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
@@ -37792,10 +40422,20 @@
       <c r="G879" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H879" s="6" t="inlineStr"/>
-      <c r="I879" s="6" t="inlineStr"/>
-      <c r="J879" s="6" t="inlineStr"/>
-      <c r="K879" s="6" t="inlineStr"/>
+      <c r="H879" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I879" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J879" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K879" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="inlineStr">
@@ -37831,10 +40471,20 @@
       <c r="G880" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H880" s="6" t="inlineStr"/>
-      <c r="I880" s="6" t="inlineStr"/>
-      <c r="J880" s="6" t="inlineStr"/>
-      <c r="K880" s="6" t="inlineStr"/>
+      <c r="H880" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I880" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J880" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K880" s="4" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" s="2" t="inlineStr">
@@ -38026,10 +40676,20 @@
       <c r="G885" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H885" s="6" t="inlineStr"/>
-      <c r="I885" s="6" t="inlineStr"/>
-      <c r="J885" s="6" t="inlineStr"/>
-      <c r="K885" s="6" t="inlineStr"/>
+      <c r="H885" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I885" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J885" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K885" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886" s="2" t="inlineStr">
@@ -38065,10 +40725,20 @@
       <c r="G886" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H886" s="6" t="inlineStr"/>
-      <c r="I886" s="6" t="inlineStr"/>
-      <c r="J886" s="6" t="inlineStr"/>
-      <c r="K886" s="6" t="inlineStr"/>
+      <c r="H886" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I886" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J886" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K886" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" s="2" t="inlineStr">
@@ -38104,10 +40774,20 @@
       <c r="G887" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H887" s="6" t="inlineStr"/>
-      <c r="I887" s="6" t="inlineStr"/>
-      <c r="J887" s="6" t="inlineStr"/>
-      <c r="K887" s="6" t="inlineStr"/>
+      <c r="H887" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I887" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J887" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K887" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="inlineStr">
@@ -38143,10 +40823,20 @@
       <c r="G888" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H888" s="6" t="inlineStr"/>
-      <c r="I888" s="6" t="inlineStr"/>
-      <c r="J888" s="6" t="inlineStr"/>
-      <c r="K888" s="6" t="inlineStr"/>
+      <c r="H888" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I888" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J888" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K888" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
@@ -38182,10 +40872,20 @@
       <c r="G889" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="H889" s="6" t="inlineStr"/>
-      <c r="I889" s="6" t="inlineStr"/>
-      <c r="J889" s="6" t="inlineStr"/>
-      <c r="K889" s="6" t="inlineStr"/>
+      <c r="H889" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I889" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J889" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K889" s="4" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="inlineStr">
@@ -38338,10 +41038,20 @@
       <c r="G893" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H893" s="6" t="inlineStr"/>
-      <c r="I893" s="6" t="inlineStr"/>
-      <c r="J893" s="6" t="inlineStr"/>
-      <c r="K893" s="6" t="inlineStr"/>
+      <c r="H893" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I893" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J893" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K893" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894" s="2" t="inlineStr">
@@ -38377,10 +41087,20 @@
       <c r="G894" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H894" s="6" t="inlineStr"/>
-      <c r="I894" s="6" t="inlineStr"/>
-      <c r="J894" s="6" t="inlineStr"/>
-      <c r="K894" s="6" t="inlineStr"/>
+      <c r="H894" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I894" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J894" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K894" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" s="2" t="inlineStr">
@@ -38494,10 +41214,20 @@
       <c r="G897" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H897" s="6" t="inlineStr"/>
-      <c r="I897" s="6" t="inlineStr"/>
-      <c r="J897" s="6" t="inlineStr"/>
-      <c r="K897" s="6" t="inlineStr"/>
+      <c r="H897" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I897" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J897" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K897" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898" s="2" t="inlineStr">
@@ -38533,10 +41263,20 @@
       <c r="G898" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H898" s="6" t="inlineStr"/>
-      <c r="I898" s="6" t="inlineStr"/>
-      <c r="J898" s="6" t="inlineStr"/>
-      <c r="K898" s="6" t="inlineStr"/>
+      <c r="H898" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I898" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J898" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K898" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899" s="2" t="inlineStr">
@@ -38572,10 +41312,20 @@
       <c r="G899" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H899" s="6" t="inlineStr"/>
-      <c r="I899" s="6" t="inlineStr"/>
-      <c r="J899" s="6" t="inlineStr"/>
-      <c r="K899" s="6" t="inlineStr"/>
+      <c r="H899" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I899" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J899" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K899" s="4" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">
@@ -38611,10 +41361,20 @@
       <c r="G900" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H900" s="6" t="inlineStr"/>
-      <c r="I900" s="6" t="inlineStr"/>
-      <c r="J900" s="6" t="inlineStr"/>
-      <c r="K900" s="6" t="inlineStr"/>
+      <c r="H900" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I900" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J900" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K900" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="inlineStr">
@@ -38728,10 +41488,20 @@
       <c r="G903" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H903" s="6" t="inlineStr"/>
-      <c r="I903" s="6" t="inlineStr"/>
-      <c r="J903" s="6" t="inlineStr"/>
-      <c r="K903" s="6" t="inlineStr"/>
+      <c r="H903" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I903" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K903" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904" s="2" t="inlineStr">
@@ -38767,10 +41537,20 @@
       <c r="G904" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H904" s="6" t="inlineStr"/>
-      <c r="I904" s="6" t="inlineStr"/>
-      <c r="J904" s="6" t="inlineStr"/>
-      <c r="K904" s="6" t="inlineStr"/>
+      <c r="H904" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I904" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J904" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K904" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905" s="2" t="inlineStr">
@@ -38806,10 +41586,20 @@
       <c r="G905" s="2" t="n">
         <v>2.44</v>
       </c>
-      <c r="H905" s="6" t="inlineStr"/>
-      <c r="I905" s="6" t="inlineStr"/>
-      <c r="J905" s="6" t="inlineStr"/>
-      <c r="K905" s="6" t="inlineStr"/>
+      <c r="H905" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I905" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J905" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K905" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="2" t="inlineStr">
@@ -38845,10 +41635,20 @@
       <c r="G906" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H906" s="6" t="inlineStr"/>
-      <c r="I906" s="6" t="inlineStr"/>
-      <c r="J906" s="6" t="inlineStr"/>
-      <c r="K906" s="6" t="inlineStr"/>
+      <c r="H906" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I906" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J906" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K906" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
@@ -39001,10 +41801,20 @@
       <c r="G910" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H910" s="6" t="inlineStr"/>
-      <c r="I910" s="6" t="inlineStr"/>
-      <c r="J910" s="6" t="inlineStr"/>
-      <c r="K910" s="6" t="inlineStr"/>
+      <c r="H910" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I910" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J910" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K910" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
@@ -39040,10 +41850,20 @@
       <c r="G911" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H911" s="6" t="inlineStr"/>
-      <c r="I911" s="6" t="inlineStr"/>
-      <c r="J911" s="6" t="inlineStr"/>
-      <c r="K911" s="6" t="inlineStr"/>
+      <c r="H911" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I911" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J911" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K911" s="4" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
@@ -39079,10 +41899,20 @@
       <c r="G912" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="H912" s="6" t="inlineStr"/>
-      <c r="I912" s="6" t="inlineStr"/>
-      <c r="J912" s="6" t="inlineStr"/>
-      <c r="K912" s="6" t="inlineStr"/>
+      <c r="H912" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I912" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J912" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K912" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913" s="2" t="inlineStr">
@@ -39118,10 +41948,20 @@
       <c r="G913" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H913" s="6" t="inlineStr"/>
-      <c r="I913" s="6" t="inlineStr"/>
-      <c r="J913" s="6" t="inlineStr"/>
-      <c r="K913" s="6" t="inlineStr"/>
+      <c r="H913" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I913" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J913" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K913" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
@@ -39157,10 +41997,20 @@
       <c r="G914" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H914" s="6" t="inlineStr"/>
-      <c r="I914" s="6" t="inlineStr"/>
-      <c r="J914" s="6" t="inlineStr"/>
-      <c r="K914" s="6" t="inlineStr"/>
+      <c r="H914" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I914" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J914" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K914" s="4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="2" t="inlineStr">
@@ -39430,10 +42280,20 @@
       <c r="G921" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H921" s="6" t="inlineStr"/>
-      <c r="I921" s="6" t="inlineStr"/>
-      <c r="J921" s="6" t="inlineStr"/>
-      <c r="K921" s="6" t="inlineStr"/>
+      <c r="H921" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I921" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J921" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K921" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
@@ -39469,10 +42329,20 @@
       <c r="G922" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H922" s="6" t="inlineStr"/>
-      <c r="I922" s="6" t="inlineStr"/>
-      <c r="J922" s="6" t="inlineStr"/>
-      <c r="K922" s="6" t="inlineStr"/>
+      <c r="H922" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I922" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J922" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K922" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923" s="2" t="inlineStr">
@@ -39508,10 +42378,20 @@
       <c r="G923" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H923" s="6" t="inlineStr"/>
-      <c r="I923" s="6" t="inlineStr"/>
-      <c r="J923" s="6" t="inlineStr"/>
-      <c r="K923" s="6" t="inlineStr"/>
+      <c r="H923" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I923" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J923" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K923" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="924">
       <c r="A924" s="2" t="inlineStr">
@@ -39547,10 +42427,20 @@
       <c r="G924" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H924" s="6" t="inlineStr"/>
-      <c r="I924" s="6" t="inlineStr"/>
-      <c r="J924" s="6" t="inlineStr"/>
-      <c r="K924" s="6" t="inlineStr"/>
+      <c r="H924" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I924" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J924" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K924" s="5" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925" s="2" t="inlineStr">
@@ -39820,10 +42710,20 @@
       <c r="G931" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H931" s="6" t="inlineStr"/>
-      <c r="I931" s="6" t="inlineStr"/>
-      <c r="J931" s="6" t="inlineStr"/>
-      <c r="K931" s="6" t="inlineStr"/>
+      <c r="H931" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I931" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J931" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K931" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932" s="2" t="inlineStr">
@@ -39859,10 +42759,20 @@
       <c r="G932" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H932" s="6" t="inlineStr"/>
-      <c r="I932" s="6" t="inlineStr"/>
-      <c r="J932" s="6" t="inlineStr"/>
-      <c r="K932" s="6" t="inlineStr"/>
+      <c r="H932" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I932" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J932" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K932" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933" s="2" t="inlineStr">
@@ -39898,10 +42808,20 @@
       <c r="G933" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="H933" s="6" t="inlineStr"/>
-      <c r="I933" s="6" t="inlineStr"/>
-      <c r="J933" s="6" t="inlineStr"/>
-      <c r="K933" s="6" t="inlineStr"/>
+      <c r="H933" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I933" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J933" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K933" s="5" t="n">
+        <v>-148</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934" s="2" t="inlineStr">
@@ -39937,10 +42857,20 @@
       <c r="G934" s="2" t="n">
         <v>2.64</v>
       </c>
-      <c r="H934" s="6" t="inlineStr"/>
-      <c r="I934" s="6" t="inlineStr"/>
-      <c r="J934" s="6" t="inlineStr"/>
-      <c r="K934" s="6" t="inlineStr"/>
+      <c r="H934" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I934" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J934" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K934" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935" s="2" t="inlineStr">
@@ -39976,10 +42906,20 @@
       <c r="G935" s="2" t="n">
         <v>2.68</v>
       </c>
-      <c r="H935" s="6" t="inlineStr"/>
-      <c r="I935" s="6" t="inlineStr"/>
-      <c r="J935" s="6" t="inlineStr"/>
-      <c r="K935" s="6" t="inlineStr"/>
+      <c r="H935" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I935" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J935" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K935" s="5" t="n">
+        <v>-168</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936" s="2" t="inlineStr">
@@ -40015,10 +42955,20 @@
       <c r="G936" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H936" s="6" t="inlineStr"/>
-      <c r="I936" s="6" t="inlineStr"/>
-      <c r="J936" s="6" t="inlineStr"/>
-      <c r="K936" s="6" t="inlineStr"/>
+      <c r="H936" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I936" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J936" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K936" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="2" t="inlineStr">
@@ -40054,10 +43004,20 @@
       <c r="G937" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H937" s="6" t="inlineStr"/>
-      <c r="I937" s="6" t="inlineStr"/>
-      <c r="J937" s="6" t="inlineStr"/>
-      <c r="K937" s="6" t="inlineStr"/>
+      <c r="H937" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I937" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J937" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K937" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
@@ -40093,10 +43053,20 @@
       <c r="G938" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H938" s="6" t="inlineStr"/>
-      <c r="I938" s="6" t="inlineStr"/>
-      <c r="J938" s="6" t="inlineStr"/>
-      <c r="K938" s="6" t="inlineStr"/>
+      <c r="H938" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I938" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J938" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K938" s="5" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
@@ -40210,10 +43180,20 @@
       <c r="G941" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H941" s="6" t="inlineStr"/>
-      <c r="I941" s="6" t="inlineStr"/>
-      <c r="J941" s="6" t="inlineStr"/>
-      <c r="K941" s="6" t="inlineStr"/>
+      <c r="H941" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I941" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J941" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K941" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" s="2" t="inlineStr">
@@ -40249,10 +43229,20 @@
       <c r="G942" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H942" s="6" t="inlineStr"/>
-      <c r="I942" s="6" t="inlineStr"/>
-      <c r="J942" s="6" t="inlineStr"/>
-      <c r="K942" s="6" t="inlineStr"/>
+      <c r="H942" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I942" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J942" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K942" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="943">
       <c r="A943" s="2" t="inlineStr">
@@ -40288,10 +43278,20 @@
       <c r="G943" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H943" s="6" t="inlineStr"/>
-      <c r="I943" s="6" t="inlineStr"/>
-      <c r="J943" s="6" t="inlineStr"/>
-      <c r="K943" s="6" t="inlineStr"/>
+      <c r="H943" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I943" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J943" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K943" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944" s="2" t="inlineStr">
@@ -40327,10 +43327,20 @@
       <c r="G944" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H944" s="6" t="inlineStr"/>
-      <c r="I944" s="6" t="inlineStr"/>
-      <c r="J944" s="6" t="inlineStr"/>
-      <c r="K944" s="6" t="inlineStr"/>
+      <c r="H944" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I944" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J944" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K944" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" s="2" t="inlineStr">
@@ -40366,10 +43376,20 @@
       <c r="G945" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H945" s="6" t="inlineStr"/>
-      <c r="I945" s="6" t="inlineStr"/>
-      <c r="J945" s="6" t="inlineStr"/>
-      <c r="K945" s="6" t="inlineStr"/>
+      <c r="H945" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I945" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J945" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K945" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946" s="2" t="inlineStr">
@@ -40795,10 +43815,20 @@
       <c r="G956" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H956" s="6" t="inlineStr"/>
-      <c r="I956" s="6" t="inlineStr"/>
-      <c r="J956" s="6" t="inlineStr"/>
-      <c r="K956" s="6" t="inlineStr"/>
+      <c r="H956" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I956" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J956" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K956" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957" s="2" t="inlineStr">
@@ -40834,10 +43864,20 @@
       <c r="G957" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H957" s="6" t="inlineStr"/>
-      <c r="I957" s="6" t="inlineStr"/>
-      <c r="J957" s="6" t="inlineStr"/>
-      <c r="K957" s="6" t="inlineStr"/>
+      <c r="H957" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I957" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J957" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K957" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958" s="2" t="inlineStr">
@@ -41380,10 +44420,20 @@
       <c r="G971" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H971" s="6" t="inlineStr"/>
-      <c r="I971" s="6" t="inlineStr"/>
-      <c r="J971" s="6" t="inlineStr"/>
-      <c r="K971" s="6" t="inlineStr"/>
+      <c r="H971" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I971" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J971" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K971" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" s="2" t="inlineStr">
@@ -41614,10 +44664,20 @@
       <c r="G977" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H977" s="6" t="inlineStr"/>
-      <c r="I977" s="6" t="inlineStr"/>
-      <c r="J977" s="6" t="inlineStr"/>
-      <c r="K977" s="6" t="inlineStr"/>
+      <c r="H977" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I977" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J977" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K977" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978" s="2" t="inlineStr">
@@ -41653,10 +44713,20 @@
       <c r="G978" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H978" s="6" t="inlineStr"/>
-      <c r="I978" s="6" t="inlineStr"/>
-      <c r="J978" s="6" t="inlineStr"/>
-      <c r="K978" s="6" t="inlineStr"/>
+      <c r="H978" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I978" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J978" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K978" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="979">
       <c r="A979" s="2" t="inlineStr">
@@ -41926,10 +44996,20 @@
       <c r="G985" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H985" s="6" t="inlineStr"/>
-      <c r="I985" s="6" t="inlineStr"/>
-      <c r="J985" s="6" t="inlineStr"/>
-      <c r="K985" s="6" t="inlineStr"/>
+      <c r="H985" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I985" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J985" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K985" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="986">
       <c r="A986" s="2" t="inlineStr">
@@ -41965,10 +45045,20 @@
       <c r="G986" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H986" s="6" t="inlineStr"/>
-      <c r="I986" s="6" t="inlineStr"/>
-      <c r="J986" s="6" t="inlineStr"/>
-      <c r="K986" s="6" t="inlineStr"/>
+      <c r="H986" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I986" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J986" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K986" s="4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="987">
       <c r="A987" s="2" t="inlineStr">
@@ -42121,10 +45211,20 @@
       <c r="G990" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H990" s="6" t="inlineStr"/>
-      <c r="I990" s="6" t="inlineStr"/>
-      <c r="J990" s="6" t="inlineStr"/>
-      <c r="K990" s="6" t="inlineStr"/>
+      <c r="H990" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I990" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J990" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K990" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="991">
       <c r="A991" s="2" t="inlineStr">
@@ -42160,10 +45260,20 @@
       <c r="G991" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H991" s="6" t="inlineStr"/>
-      <c r="I991" s="6" t="inlineStr"/>
-      <c r="J991" s="6" t="inlineStr"/>
-      <c r="K991" s="6" t="inlineStr"/>
+      <c r="H991" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I991" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J991" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K991" s="5" t="n">
+        <v>-320</v>
+      </c>
     </row>
     <row r="992">
       <c r="A992" s="2" t="inlineStr">
@@ -42199,10 +45309,20 @@
       <c r="G992" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H992" s="6" t="inlineStr"/>
-      <c r="I992" s="6" t="inlineStr"/>
-      <c r="J992" s="6" t="inlineStr"/>
-      <c r="K992" s="6" t="inlineStr"/>
+      <c r="H992" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I992" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J992" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K992" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="993">
       <c r="A993" s="2" t="inlineStr">
@@ -42238,10 +45358,20 @@
       <c r="G993" s="2" t="n">
         <v>2.54</v>
       </c>
-      <c r="H993" s="6" t="inlineStr"/>
-      <c r="I993" s="6" t="inlineStr"/>
-      <c r="J993" s="6" t="inlineStr"/>
-      <c r="K993" s="6" t="inlineStr"/>
+      <c r="H993" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I993" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J993" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K993" s="5" t="n">
+        <v>-154</v>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="2" t="inlineStr">
@@ -42277,10 +45407,20 @@
       <c r="G994" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="H994" s="6" t="inlineStr"/>
-      <c r="I994" s="6" t="inlineStr"/>
-      <c r="J994" s="6" t="inlineStr"/>
-      <c r="K994" s="6" t="inlineStr"/>
+      <c r="H994" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I994" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J994" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K994" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="995">
       <c r="A995" s="2" t="inlineStr">
@@ -42316,10 +45456,20 @@
       <c r="G995" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H995" s="6" t="inlineStr"/>
-      <c r="I995" s="6" t="inlineStr"/>
-      <c r="J995" s="6" t="inlineStr"/>
-      <c r="K995" s="6" t="inlineStr"/>
+      <c r="H995" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I995" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J995" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K995" s="5" t="n">
+        <v>-700</v>
+      </c>
     </row>
     <row r="996">
       <c r="A996" s="2" t="inlineStr">
@@ -42355,10 +45505,20 @@
       <c r="G996" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="H996" s="6" t="inlineStr"/>
-      <c r="I996" s="6" t="inlineStr"/>
-      <c r="J996" s="6" t="inlineStr"/>
-      <c r="K996" s="6" t="inlineStr"/>
+      <c r="H996" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I996" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J996" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K996" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="997">
       <c r="A997" s="2" t="inlineStr">
@@ -42394,10 +45554,20 @@
       <c r="G997" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="H997" s="6" t="inlineStr"/>
-      <c r="I997" s="6" t="inlineStr"/>
-      <c r="J997" s="6" t="inlineStr"/>
-      <c r="K997" s="6" t="inlineStr"/>
+      <c r="H997" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I997" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J997" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K997" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="998">
       <c r="A998" s="2" t="inlineStr">
@@ -42433,10 +45603,20 @@
       <c r="G998" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H998" s="6" t="inlineStr"/>
-      <c r="I998" s="6" t="inlineStr"/>
-      <c r="J998" s="6" t="inlineStr"/>
-      <c r="K998" s="6" t="inlineStr"/>
+      <c r="H998" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I998" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J998" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K998" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="999">
       <c r="A999" s="2" t="inlineStr">
@@ -42472,10 +45652,20 @@
       <c r="G999" s="2" t="n">
         <v>2.52</v>
       </c>
-      <c r="H999" s="6" t="inlineStr"/>
-      <c r="I999" s="6" t="inlineStr"/>
-      <c r="J999" s="6" t="inlineStr"/>
-      <c r="K999" s="6" t="inlineStr"/>
+      <c r="H999" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I999" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J999" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K999" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="inlineStr">
@@ -42511,10 +45701,20 @@
       <c r="G1000" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H1000" s="6" t="inlineStr"/>
-      <c r="I1000" s="6" t="inlineStr"/>
-      <c r="J1000" s="6" t="inlineStr"/>
-      <c r="K1000" s="6" t="inlineStr"/>
+      <c r="H1000" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1000" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1000" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1000" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="inlineStr">
@@ -42550,10 +45750,20 @@
       <c r="G1001" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H1001" s="6" t="inlineStr"/>
-      <c r="I1001" s="6" t="inlineStr"/>
-      <c r="J1001" s="6" t="inlineStr"/>
-      <c r="K1001" s="6" t="inlineStr"/>
+      <c r="H1001" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1001" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1001" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1001" s="5" t="n">
+        <v>-300</v>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" s="2" t="inlineStr">
@@ -43291,10 +46501,20 @@
       <c r="G1020" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H1020" s="6" t="inlineStr"/>
-      <c r="I1020" s="6" t="inlineStr"/>
-      <c r="J1020" s="6" t="inlineStr"/>
-      <c r="K1020" s="6" t="inlineStr"/>
+      <c r="H1020" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1020" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1020" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1020" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1021">
       <c r="A1021" s="2" t="inlineStr">
@@ -43330,10 +46550,20 @@
       <c r="G1021" s="2" t="n">
         <v>2.54</v>
       </c>
-      <c r="H1021" s="6" t="inlineStr"/>
-      <c r="I1021" s="6" t="inlineStr"/>
-      <c r="J1021" s="6" t="inlineStr"/>
-      <c r="K1021" s="6" t="inlineStr"/>
+      <c r="H1021" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1021" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1021" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1021" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" s="2" t="inlineStr">
@@ -43447,10 +46677,20 @@
       <c r="G1024" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H1024" s="6" t="inlineStr"/>
-      <c r="I1024" s="6" t="inlineStr"/>
-      <c r="J1024" s="6" t="inlineStr"/>
-      <c r="K1024" s="6" t="inlineStr"/>
+      <c r="H1024" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1024" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1024" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1024" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" s="2" t="inlineStr">
@@ -43486,10 +46726,20 @@
       <c r="G1025" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H1025" s="6" t="inlineStr"/>
-      <c r="I1025" s="6" t="inlineStr"/>
-      <c r="J1025" s="6" t="inlineStr"/>
-      <c r="K1025" s="6" t="inlineStr"/>
+      <c r="H1025" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1025" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1025" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1025" s="4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" s="2" t="inlineStr">
@@ -43525,10 +46775,20 @@
       <c r="G1026" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H1026" s="6" t="inlineStr"/>
-      <c r="I1026" s="6" t="inlineStr"/>
-      <c r="J1026" s="6" t="inlineStr"/>
-      <c r="K1026" s="6" t="inlineStr"/>
+      <c r="H1026" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1026" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1026" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1026" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" s="2" t="inlineStr">
@@ -43564,10 +46824,20 @@
       <c r="G1027" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H1027" s="6" t="inlineStr"/>
-      <c r="I1027" s="6" t="inlineStr"/>
-      <c r="J1027" s="6" t="inlineStr"/>
-      <c r="K1027" s="6" t="inlineStr"/>
+      <c r="H1027" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1027" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1027" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1027" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" s="2" t="inlineStr">
@@ -43603,10 +46873,20 @@
       <c r="G1028" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H1028" s="6" t="inlineStr"/>
-      <c r="I1028" s="6" t="inlineStr"/>
-      <c r="J1028" s="6" t="inlineStr"/>
-      <c r="K1028" s="6" t="inlineStr"/>
+      <c r="H1028" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1028" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1028" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1028" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" s="2" t="inlineStr">
@@ -43798,10 +47078,20 @@
       <c r="G1033" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H1033" s="6" t="inlineStr"/>
-      <c r="I1033" s="6" t="inlineStr"/>
-      <c r="J1033" s="6" t="inlineStr"/>
-      <c r="K1033" s="6" t="inlineStr"/>
+      <c r="H1033" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1033" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1033" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1033" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
@@ -43837,10 +47127,20 @@
       <c r="G1034" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H1034" s="6" t="inlineStr"/>
-      <c r="I1034" s="6" t="inlineStr"/>
-      <c r="J1034" s="6" t="inlineStr"/>
-      <c r="K1034" s="6" t="inlineStr"/>
+      <c r="H1034" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1034" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1034" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1034" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="inlineStr">
@@ -44110,10 +47410,20 @@
       <c r="G1041" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H1041" s="6" t="inlineStr"/>
-      <c r="I1041" s="6" t="inlineStr"/>
-      <c r="J1041" s="6" t="inlineStr"/>
-      <c r="K1041" s="6" t="inlineStr"/>
+      <c r="H1041" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1041" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1041" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1041" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="inlineStr">
@@ -44149,10 +47459,20 @@
       <c r="G1042" s="2" t="n">
         <v>1.85</v>
       </c>
-      <c r="H1042" s="6" t="inlineStr"/>
-      <c r="I1042" s="6" t="inlineStr"/>
-      <c r="J1042" s="6" t="inlineStr"/>
-      <c r="K1042" s="6" t="inlineStr"/>
+      <c r="H1042" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1042" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1042" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1042" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" s="2" t="inlineStr">
@@ -44188,10 +47508,20 @@
       <c r="G1043" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H1043" s="6" t="inlineStr"/>
-      <c r="I1043" s="6" t="inlineStr"/>
-      <c r="J1043" s="6" t="inlineStr"/>
-      <c r="K1043" s="6" t="inlineStr"/>
+      <c r="H1043" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1043" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1043" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1043" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" s="2" t="inlineStr">
@@ -44227,10 +47557,20 @@
       <c r="G1044" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H1044" s="6" t="inlineStr"/>
-      <c r="I1044" s="6" t="inlineStr"/>
-      <c r="J1044" s="6" t="inlineStr"/>
-      <c r="K1044" s="6" t="inlineStr"/>
+      <c r="H1044" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1044" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1044" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1044" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="inlineStr">
@@ -44266,10 +47606,20 @@
       <c r="G1045" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="H1045" s="6" t="inlineStr"/>
-      <c r="I1045" s="6" t="inlineStr"/>
-      <c r="J1045" s="6" t="inlineStr"/>
-      <c r="K1045" s="6" t="inlineStr"/>
+      <c r="H1045" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1045" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1045" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1045" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" s="2" t="inlineStr">
@@ -44305,10 +47655,20 @@
       <c r="G1046" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H1046" s="6" t="inlineStr"/>
-      <c r="I1046" s="6" t="inlineStr"/>
-      <c r="J1046" s="6" t="inlineStr"/>
-      <c r="K1046" s="6" t="inlineStr"/>
+      <c r="H1046" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1046" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1046" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1046" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" s="2" t="inlineStr">
@@ -44344,10 +47704,20 @@
       <c r="G1047" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H1047" s="6" t="inlineStr"/>
-      <c r="I1047" s="6" t="inlineStr"/>
-      <c r="J1047" s="6" t="inlineStr"/>
-      <c r="K1047" s="6" t="inlineStr"/>
+      <c r="H1047" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1047" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1047" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1047" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="inlineStr">
@@ -44383,10 +47753,20 @@
       <c r="G1048" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H1048" s="6" t="inlineStr"/>
-      <c r="I1048" s="6" t="inlineStr"/>
-      <c r="J1048" s="6" t="inlineStr"/>
-      <c r="K1048" s="6" t="inlineStr"/>
+      <c r="H1048" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1048" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1048" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1048" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" s="2" t="inlineStr">
@@ -44461,10 +47841,20 @@
       <c r="G1050" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H1050" s="6" t="inlineStr"/>
-      <c r="I1050" s="6" t="inlineStr"/>
-      <c r="J1050" s="6" t="inlineStr"/>
-      <c r="K1050" s="6" t="inlineStr"/>
+      <c r="H1050" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1050" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1050" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1050" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" s="2" t="inlineStr">
@@ -44500,10 +47890,20 @@
       <c r="G1051" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H1051" s="6" t="inlineStr"/>
-      <c r="I1051" s="6" t="inlineStr"/>
-      <c r="J1051" s="6" t="inlineStr"/>
-      <c r="K1051" s="6" t="inlineStr"/>
+      <c r="H1051" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1051" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1051" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1051" s="5" t="n">
+        <v>-136</v>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" s="2" t="inlineStr">
@@ -44578,10 +47978,20 @@
       <c r="G1053" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H1053" s="6" t="inlineStr"/>
-      <c r="I1053" s="6" t="inlineStr"/>
-      <c r="J1053" s="6" t="inlineStr"/>
-      <c r="K1053" s="6" t="inlineStr"/>
+      <c r="H1053" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1053" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1053" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1053" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" s="2" t="inlineStr">
@@ -44695,10 +48105,20 @@
       <c r="G1056" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H1056" s="6" t="inlineStr"/>
-      <c r="I1056" s="6" t="inlineStr"/>
-      <c r="J1056" s="6" t="inlineStr"/>
-      <c r="K1056" s="6" t="inlineStr"/>
+      <c r="H1056" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1056" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1056" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1056" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="inlineStr">
@@ -44734,10 +48154,20 @@
       <c r="G1057" s="2" t="n">
         <v>1.89</v>
       </c>
-      <c r="H1057" s="6" t="inlineStr"/>
-      <c r="I1057" s="6" t="inlineStr"/>
-      <c r="J1057" s="6" t="inlineStr"/>
-      <c r="K1057" s="6" t="inlineStr"/>
+      <c r="H1057" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1057" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1057" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1057" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
@@ -44773,10 +48203,20 @@
       <c r="G1058" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H1058" s="6" t="inlineStr"/>
-      <c r="I1058" s="6" t="inlineStr"/>
-      <c r="J1058" s="6" t="inlineStr"/>
-      <c r="K1058" s="6" t="inlineStr"/>
+      <c r="H1058" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1058" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1058" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1058" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="inlineStr">
@@ -44812,10 +48252,20 @@
       <c r="G1059" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="H1059" s="6" t="inlineStr"/>
-      <c r="I1059" s="6" t="inlineStr"/>
-      <c r="J1059" s="6" t="inlineStr"/>
-      <c r="K1059" s="6" t="inlineStr"/>
+      <c r="H1059" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1059" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1059" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1059" s="4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
@@ -44890,10 +48340,20 @@
       <c r="G1061" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H1061" s="6" t="inlineStr"/>
-      <c r="I1061" s="6" t="inlineStr"/>
-      <c r="J1061" s="6" t="inlineStr"/>
-      <c r="K1061" s="6" t="inlineStr"/>
+      <c r="H1061" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1061" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1061" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1061" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
@@ -45124,10 +48584,20 @@
       <c r="G1067" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H1067" s="6" t="inlineStr"/>
-      <c r="I1067" s="6" t="inlineStr"/>
-      <c r="J1067" s="6" t="inlineStr"/>
-      <c r="K1067" s="6" t="inlineStr"/>
+      <c r="H1067" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1067" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1067" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1067" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
@@ -45163,10 +48633,20 @@
       <c r="G1068" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H1068" s="6" t="inlineStr"/>
-      <c r="I1068" s="6" t="inlineStr"/>
-      <c r="J1068" s="6" t="inlineStr"/>
-      <c r="K1068" s="6" t="inlineStr"/>
+      <c r="H1068" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1068" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1068" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1068" s="4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
@@ -45280,10 +48760,20 @@
       <c r="G1071" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H1071" s="6" t="inlineStr"/>
-      <c r="I1071" s="6" t="inlineStr"/>
-      <c r="J1071" s="6" t="inlineStr"/>
-      <c r="K1071" s="6" t="inlineStr"/>
+      <c r="H1071" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1071" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1071" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1071" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
@@ -45319,10 +48809,20 @@
       <c r="G1072" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H1072" s="6" t="inlineStr"/>
-      <c r="I1072" s="6" t="inlineStr"/>
-      <c r="J1072" s="6" t="inlineStr"/>
-      <c r="K1072" s="6" t="inlineStr"/>
+      <c r="H1072" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1072" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1072" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1072" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
@@ -45358,10 +48858,20 @@
       <c r="G1073" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H1073" s="6" t="inlineStr"/>
-      <c r="I1073" s="6" t="inlineStr"/>
-      <c r="J1073" s="6" t="inlineStr"/>
-      <c r="K1073" s="6" t="inlineStr"/>
+      <c r="H1073" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1073" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1073" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1073" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="inlineStr">
@@ -45397,10 +48907,20 @@
       <c r="G1074" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H1074" s="6" t="inlineStr"/>
-      <c r="I1074" s="6" t="inlineStr"/>
-      <c r="J1074" s="6" t="inlineStr"/>
-      <c r="K1074" s="6" t="inlineStr"/>
+      <c r="H1074" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1074" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1074" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1074" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="inlineStr">
@@ -45436,10 +48956,20 @@
       <c r="G1075" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H1075" s="6" t="inlineStr"/>
-      <c r="I1075" s="6" t="inlineStr"/>
-      <c r="J1075" s="6" t="inlineStr"/>
-      <c r="K1075" s="6" t="inlineStr"/>
+      <c r="H1075" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1075" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1075" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1075" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="inlineStr">
@@ -45475,10 +49005,20 @@
       <c r="G1076" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H1076" s="6" t="inlineStr"/>
-      <c r="I1076" s="6" t="inlineStr"/>
-      <c r="J1076" s="6" t="inlineStr"/>
-      <c r="K1076" s="6" t="inlineStr"/>
+      <c r="H1076" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1076" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1076" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1076" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="inlineStr">
@@ -45670,10 +49210,20 @@
       <c r="G1081" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="H1081" s="6" t="inlineStr"/>
-      <c r="I1081" s="6" t="inlineStr"/>
-      <c r="J1081" s="6" t="inlineStr"/>
-      <c r="K1081" s="6" t="inlineStr"/>
+      <c r="H1081" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1081" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1081" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1081" s="4" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="1082">
       <c r="A1082" s="2" t="inlineStr">
@@ -45709,10 +49259,20 @@
       <c r="G1082" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H1082" s="6" t="inlineStr"/>
-      <c r="I1082" s="6" t="inlineStr"/>
-      <c r="J1082" s="6" t="inlineStr"/>
-      <c r="K1082" s="6" t="inlineStr"/>
+      <c r="H1082" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1082" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1082" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1082" s="5" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" s="2" t="inlineStr">
@@ -45748,10 +49308,20 @@
       <c r="G1083" s="2" t="n">
         <v>9.4</v>
       </c>
-      <c r="H1083" s="6" t="inlineStr"/>
-      <c r="I1083" s="6" t="inlineStr"/>
-      <c r="J1083" s="6" t="inlineStr"/>
-      <c r="K1083" s="6" t="inlineStr"/>
+      <c r="H1083" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1083" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1083" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1083" s="5" t="n">
+        <v>-840</v>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
@@ -45787,10 +49357,20 @@
       <c r="G1084" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H1084" s="6" t="inlineStr"/>
-      <c r="I1084" s="6" t="inlineStr"/>
-      <c r="J1084" s="6" t="inlineStr"/>
-      <c r="K1084" s="6" t="inlineStr"/>
+      <c r="H1084" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1084" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1084" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1084" s="5" t="n">
+        <v>-265</v>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
@@ -45826,10 +49406,20 @@
       <c r="G1085" s="2" t="n">
         <v>2.58</v>
       </c>
-      <c r="H1085" s="6" t="inlineStr"/>
-      <c r="I1085" s="6" t="inlineStr"/>
-      <c r="J1085" s="6" t="inlineStr"/>
-      <c r="K1085" s="6" t="inlineStr"/>
+      <c r="H1085" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1085" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1085" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1085" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
@@ -45865,10 +49455,20 @@
       <c r="G1086" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="H1086" s="6" t="inlineStr"/>
-      <c r="I1086" s="6" t="inlineStr"/>
-      <c r="J1086" s="6" t="inlineStr"/>
-      <c r="K1086" s="6" t="inlineStr"/>
+      <c r="H1086" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1086" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1086" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1086" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="inlineStr">
@@ -46060,10 +49660,20 @@
       <c r="G1091" s="2" t="n">
         <v>2.8</v>
       </c>
-      <c r="H1091" s="6" t="inlineStr"/>
-      <c r="I1091" s="6" t="inlineStr"/>
-      <c r="J1091" s="6" t="inlineStr"/>
-      <c r="K1091" s="6" t="inlineStr"/>
+      <c r="H1091" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1091" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1091" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1091" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1092">
       <c r="A1092" s="2" t="inlineStr">
@@ -46099,10 +49709,20 @@
       <c r="G1092" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H1092" s="6" t="inlineStr"/>
-      <c r="I1092" s="6" t="inlineStr"/>
-      <c r="J1092" s="6" t="inlineStr"/>
-      <c r="K1092" s="6" t="inlineStr"/>
+      <c r="H1092" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1092" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1092" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1092" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" s="2" t="inlineStr">
@@ -46138,10 +49758,20 @@
       <c r="G1093" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H1093" s="6" t="inlineStr"/>
-      <c r="I1093" s="6" t="inlineStr"/>
-      <c r="J1093" s="6" t="inlineStr"/>
-      <c r="K1093" s="6" t="inlineStr"/>
+      <c r="H1093" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1093" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1093" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1093" s="4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="inlineStr">

--- a/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
+++ b/Sinais_Arsenal_Completo_Paper_Trading_01_a_17_Ago.xlsx
@@ -20624,10 +20624,20 @@
       <c r="G437" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H437" s="6" t="inlineStr"/>
-      <c r="I437" s="6" t="inlineStr"/>
-      <c r="J437" s="6" t="inlineStr"/>
-      <c r="K437" s="6" t="inlineStr"/>
+      <c r="H437" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I437" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J437" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K437" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -20663,10 +20673,20 @@
       <c r="G438" s="2" t="n">
         <v>2.14</v>
       </c>
-      <c r="H438" s="6" t="inlineStr"/>
-      <c r="I438" s="6" t="inlineStr"/>
-      <c r="J438" s="6" t="inlineStr"/>
-      <c r="K438" s="6" t="inlineStr"/>
+      <c r="H438" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I438" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J438" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K438" s="4" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -21094,10 +21114,20 @@
       <c r="G447" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H447" s="6" t="inlineStr"/>
-      <c r="I447" s="6" t="inlineStr"/>
-      <c r="J447" s="6" t="inlineStr"/>
-      <c r="K447" s="6" t="inlineStr"/>
+      <c r="H447" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I447" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J447" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K447" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -21133,10 +21163,20 @@
       <c r="G448" s="2" t="n">
         <v>2.24</v>
       </c>
-      <c r="H448" s="6" t="inlineStr"/>
-      <c r="I448" s="6" t="inlineStr"/>
-      <c r="J448" s="6" t="inlineStr"/>
-      <c r="K448" s="6" t="inlineStr"/>
+      <c r="H448" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I448" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J448" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K448" s="4" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -21172,10 +21212,20 @@
       <c r="G449" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H449" s="6" t="inlineStr"/>
-      <c r="I449" s="6" t="inlineStr"/>
-      <c r="J449" s="6" t="inlineStr"/>
-      <c r="K449" s="6" t="inlineStr"/>
+      <c r="H449" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I449" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J449" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K449" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -21211,10 +21261,20 @@
       <c r="G450" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H450" s="6" t="inlineStr"/>
-      <c r="I450" s="6" t="inlineStr"/>
-      <c r="J450" s="6" t="inlineStr"/>
-      <c r="K450" s="6" t="inlineStr"/>
+      <c r="H450" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I450" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J450" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K450" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -21250,10 +21310,20 @@
       <c r="G451" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H451" s="6" t="inlineStr"/>
-      <c r="I451" s="6" t="inlineStr"/>
-      <c r="J451" s="6" t="inlineStr"/>
-      <c r="K451" s="6" t="inlineStr"/>
+      <c r="H451" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I451" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J451" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K451" s="4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -21289,10 +21359,20 @@
       <c r="G452" s="2" t="n">
         <v>1.89</v>
       </c>
-      <c r="H452" s="6" t="inlineStr"/>
-      <c r="I452" s="6" t="inlineStr"/>
-      <c r="J452" s="6" t="inlineStr"/>
-      <c r="K452" s="6" t="inlineStr"/>
+      <c r="H452" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I452" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J452" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K452" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -21367,10 +21447,20 @@
       <c r="G454" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H454" s="6" t="inlineStr"/>
-      <c r="I454" s="6" t="inlineStr"/>
-      <c r="J454" s="6" t="inlineStr"/>
-      <c r="K454" s="6" t="inlineStr"/>
+      <c r="H454" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I454" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J454" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K454" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -21406,10 +21496,20 @@
       <c r="G455" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H455" s="6" t="inlineStr"/>
-      <c r="I455" s="6" t="inlineStr"/>
-      <c r="J455" s="6" t="inlineStr"/>
-      <c r="K455" s="6" t="inlineStr"/>
+      <c r="H455" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I455" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J455" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K455" s="4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -21445,10 +21545,20 @@
       <c r="G456" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H456" s="6" t="inlineStr"/>
-      <c r="I456" s="6" t="inlineStr"/>
-      <c r="J456" s="6" t="inlineStr"/>
-      <c r="K456" s="6" t="inlineStr"/>
+      <c r="H456" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I456" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J456" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K456" s="5" t="n">
+        <v>-340</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -21680,10 +21790,20 @@
       <c r="G461" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H461" s="6" t="inlineStr"/>
-      <c r="I461" s="6" t="inlineStr"/>
-      <c r="J461" s="6" t="inlineStr"/>
-      <c r="K461" s="6" t="inlineStr"/>
+      <c r="H461" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I461" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J461" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K461" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -21797,10 +21917,20 @@
       <c r="G464" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H464" s="6" t="inlineStr"/>
-      <c r="I464" s="6" t="inlineStr"/>
-      <c r="J464" s="6" t="inlineStr"/>
-      <c r="K464" s="6" t="inlineStr"/>
+      <c r="H464" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I464" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J464" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K464" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -22159,10 +22289,20 @@
       <c r="G472" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H472" s="6" t="inlineStr"/>
-      <c r="I472" s="6" t="inlineStr"/>
-      <c r="J472" s="6" t="inlineStr"/>
-      <c r="K472" s="6" t="inlineStr"/>
+      <c r="H472" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I472" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J472" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K472" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -22198,10 +22338,20 @@
       <c r="G473" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H473" s="6" t="inlineStr"/>
-      <c r="I473" s="6" t="inlineStr"/>
-      <c r="J473" s="6" t="inlineStr"/>
-      <c r="K473" s="6" t="inlineStr"/>
+      <c r="H473" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I473" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J473" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K473" s="4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -22286,10 +22436,20 @@
       <c r="G475" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H475" s="6" t="inlineStr"/>
-      <c r="I475" s="6" t="inlineStr"/>
-      <c r="J475" s="6" t="inlineStr"/>
-      <c r="K475" s="6" t="inlineStr"/>
+      <c r="H475" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I475" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J475" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K475" s="5" t="n">
+        <v>-310</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -22325,10 +22485,20 @@
       <c r="G476" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H476" s="6" t="inlineStr"/>
-      <c r="I476" s="6" t="inlineStr"/>
-      <c r="J476" s="6" t="inlineStr"/>
-      <c r="K476" s="6" t="inlineStr"/>
+      <c r="H476" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I476" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J476" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K476" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -22462,10 +22632,20 @@
       <c r="G479" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H479" s="6" t="inlineStr"/>
-      <c r="I479" s="6" t="inlineStr"/>
-      <c r="J479" s="6" t="inlineStr"/>
-      <c r="K479" s="6" t="inlineStr"/>
+      <c r="H479" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I479" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J479" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K479" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -22501,10 +22681,20 @@
       <c r="G480" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="H480" s="6" t="inlineStr"/>
-      <c r="I480" s="6" t="inlineStr"/>
-      <c r="J480" s="6" t="inlineStr"/>
-      <c r="K480" s="6" t="inlineStr"/>
+      <c r="H480" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I480" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K480" s="5" t="n">
+        <v>-240</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -22540,10 +22730,20 @@
       <c r="G481" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H481" s="6" t="inlineStr"/>
-      <c r="I481" s="6" t="inlineStr"/>
-      <c r="J481" s="6" t="inlineStr"/>
-      <c r="K481" s="6" t="inlineStr"/>
+      <c r="H481" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I481" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J481" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K481" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -22579,10 +22779,20 @@
       <c r="G482" s="2" t="n">
         <v>1.95</v>
       </c>
-      <c r="H482" s="6" t="inlineStr"/>
-      <c r="I482" s="6" t="inlineStr"/>
-      <c r="J482" s="6" t="inlineStr"/>
-      <c r="K482" s="6" t="inlineStr"/>
+      <c r="H482" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I482" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K482" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -22618,10 +22828,20 @@
       <c r="G483" s="2" t="n">
         <v>2.46</v>
       </c>
-      <c r="H483" s="6" t="inlineStr"/>
-      <c r="I483" s="6" t="inlineStr"/>
-      <c r="J483" s="6" t="inlineStr"/>
-      <c r="K483" s="6" t="inlineStr"/>
+      <c r="H483" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I483" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J483" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K483" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -22657,10 +22877,20 @@
       <c r="G484" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H484" s="6" t="inlineStr"/>
-      <c r="I484" s="6" t="inlineStr"/>
-      <c r="J484" s="6" t="inlineStr"/>
-      <c r="K484" s="6" t="inlineStr"/>
+      <c r="H484" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J484" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K484" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -23186,10 +23416,20 @@
       <c r="G495" s="2" t="n">
         <v>1.97</v>
       </c>
-      <c r="H495" s="6" t="inlineStr"/>
-      <c r="I495" s="6" t="inlineStr"/>
-      <c r="J495" s="6" t="inlineStr"/>
-      <c r="K495" s="6" t="inlineStr"/>
+      <c r="H495" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I495" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J495" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K495" s="4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -23813,10 +24053,20 @@
       <c r="G508" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H508" s="6" t="inlineStr"/>
-      <c r="I508" s="6" t="inlineStr"/>
-      <c r="J508" s="6" t="inlineStr"/>
-      <c r="K508" s="6" t="inlineStr"/>
+      <c r="H508" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I508" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J508" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K508" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -24528,10 +24778,20 @@
       <c r="G523" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="H523" s="6" t="inlineStr"/>
-      <c r="I523" s="6" t="inlineStr"/>
-      <c r="J523" s="6" t="inlineStr"/>
-      <c r="K523" s="6" t="inlineStr"/>
+      <c r="H523" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I523" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J523" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K523" s="4" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -24567,10 +24827,20 @@
       <c r="G524" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H524" s="6" t="inlineStr"/>
-      <c r="I524" s="6" t="inlineStr"/>
-      <c r="J524" s="6" t="inlineStr"/>
-      <c r="K524" s="6" t="inlineStr"/>
+      <c r="H524" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I524" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J524" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K524" s="5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -24753,10 +25023,20 @@
       <c r="G528" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H528" s="6" t="inlineStr"/>
-      <c r="I528" s="6" t="inlineStr"/>
-      <c r="J528" s="6" t="inlineStr"/>
-      <c r="K528" s="6" t="inlineStr"/>
+      <c r="H528" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I528" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J528" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K528" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -24792,10 +25072,20 @@
       <c r="G529" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="H529" s="6" t="inlineStr"/>
-      <c r="I529" s="6" t="inlineStr"/>
-      <c r="J529" s="6" t="inlineStr"/>
-      <c r="K529" s="6" t="inlineStr"/>
+      <c r="H529" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I529" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J529" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K529" s="4" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -24831,10 +25121,20 @@
       <c r="G530" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H530" s="6" t="inlineStr"/>
-      <c r="I530" s="6" t="inlineStr"/>
-      <c r="J530" s="6" t="inlineStr"/>
-      <c r="K530" s="6" t="inlineStr"/>
+      <c r="H530" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I530" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K530" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -24870,10 +25170,20 @@
       <c r="G531" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H531" s="6" t="inlineStr"/>
-      <c r="I531" s="6" t="inlineStr"/>
-      <c r="J531" s="6" t="inlineStr"/>
-      <c r="K531" s="6" t="inlineStr"/>
+      <c r="H531" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I531" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K531" s="4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -25643,10 +25953,20 @@
       <c r="G548" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H548" s="6" t="inlineStr"/>
-      <c r="I548" s="6" t="inlineStr"/>
-      <c r="J548" s="6" t="inlineStr"/>
-      <c r="K548" s="6" t="inlineStr"/>
+      <c r="H548" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I548" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K548" s="5" t="n">
+        <v>-255</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -25682,10 +26002,20 @@
       <c r="G549" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H549" s="6" t="inlineStr"/>
-      <c r="I549" s="6" t="inlineStr"/>
-      <c r="J549" s="6" t="inlineStr"/>
-      <c r="K549" s="6" t="inlineStr"/>
+      <c r="H549" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J549" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K549" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -25868,10 +26198,20 @@
       <c r="G553" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H553" s="6" t="inlineStr"/>
-      <c r="I553" s="6" t="inlineStr"/>
-      <c r="J553" s="6" t="inlineStr"/>
-      <c r="K553" s="6" t="inlineStr"/>
+      <c r="H553" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I553" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J553" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K553" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -25907,10 +26247,20 @@
       <c r="G554" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H554" s="6" t="inlineStr"/>
-      <c r="I554" s="6" t="inlineStr"/>
-      <c r="J554" s="6" t="inlineStr"/>
-      <c r="K554" s="6" t="inlineStr"/>
+      <c r="H554" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I554" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J554" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K554" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -25946,10 +26296,20 @@
       <c r="G555" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="H555" s="6" t="inlineStr"/>
-      <c r="I555" s="6" t="inlineStr"/>
-      <c r="J555" s="6" t="inlineStr"/>
-      <c r="K555" s="6" t="inlineStr"/>
+      <c r="H555" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I555" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J555" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K555" s="4" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -25985,10 +26345,20 @@
       <c r="G556" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H556" s="6" t="inlineStr"/>
-      <c r="I556" s="6" t="inlineStr"/>
-      <c r="J556" s="6" t="inlineStr"/>
-      <c r="K556" s="6" t="inlineStr"/>
+      <c r="H556" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I556" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J556" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K556" s="5" t="n">
+        <v>-160</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -26122,10 +26492,20 @@
       <c r="G559" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H559" s="6" t="inlineStr"/>
-      <c r="I559" s="6" t="inlineStr"/>
-      <c r="J559" s="6" t="inlineStr"/>
-      <c r="K559" s="6" t="inlineStr"/>
+      <c r="H559" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J559" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K559" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -26161,10 +26541,20 @@
       <c r="G560" s="2" t="n">
         <v>1.83</v>
       </c>
-      <c r="H560" s="6" t="inlineStr"/>
-      <c r="I560" s="6" t="inlineStr"/>
-      <c r="J560" s="6" t="inlineStr"/>
-      <c r="K560" s="6" t="inlineStr"/>
+      <c r="H560" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J560" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K560" s="4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -26200,10 +26590,20 @@
       <c r="G561" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H561" s="6" t="inlineStr"/>
-      <c r="I561" s="6" t="inlineStr"/>
-      <c r="J561" s="6" t="inlineStr"/>
-      <c r="K561" s="6" t="inlineStr"/>
+      <c r="H561" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I561" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J561" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K561" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -26239,10 +26639,20 @@
       <c r="G562" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H562" s="6" t="inlineStr"/>
-      <c r="I562" s="6" t="inlineStr"/>
-      <c r="J562" s="6" t="inlineStr"/>
-      <c r="K562" s="6" t="inlineStr"/>
+      <c r="H562" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I562" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J562" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K562" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -26278,10 +26688,20 @@
       <c r="G563" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H563" s="6" t="inlineStr"/>
-      <c r="I563" s="6" t="inlineStr"/>
-      <c r="J563" s="6" t="inlineStr"/>
-      <c r="K563" s="6" t="inlineStr"/>
+      <c r="H563" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I563" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K563" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -26317,10 +26737,20 @@
       <c r="G564" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="H564" s="6" t="inlineStr"/>
-      <c r="I564" s="6" t="inlineStr"/>
-      <c r="J564" s="6" t="inlineStr"/>
-      <c r="K564" s="6" t="inlineStr"/>
+      <c r="H564" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I564" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J564" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K564" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
@@ -26356,10 +26786,20 @@
       <c r="G565" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H565" s="6" t="inlineStr"/>
-      <c r="I565" s="6" t="inlineStr"/>
-      <c r="J565" s="6" t="inlineStr"/>
-      <c r="K565" s="6" t="inlineStr"/>
+      <c r="H565" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I565" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K565" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -26395,10 +26835,20 @@
       <c r="G566" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H566" s="6" t="inlineStr"/>
-      <c r="I566" s="6" t="inlineStr"/>
-      <c r="J566" s="6" t="inlineStr"/>
-      <c r="K566" s="6" t="inlineStr"/>
+      <c r="H566" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I566" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K566" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -26434,10 +26884,20 @@
       <c r="G567" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H567" s="6" t="inlineStr"/>
-      <c r="I567" s="6" t="inlineStr"/>
-      <c r="J567" s="6" t="inlineStr"/>
-      <c r="K567" s="6" t="inlineStr"/>
+      <c r="H567" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I567" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J567" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K567" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -26473,10 +26933,20 @@
       <c r="G568" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H568" s="6" t="inlineStr"/>
-      <c r="I568" s="6" t="inlineStr"/>
-      <c r="J568" s="6" t="inlineStr"/>
-      <c r="K568" s="6" t="inlineStr"/>
+      <c r="H568" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I568" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J568" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K568" s="5" t="n">
+        <v>-320</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -26512,10 +26982,20 @@
       <c r="G569" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H569" s="6" t="inlineStr"/>
-      <c r="I569" s="6" t="inlineStr"/>
-      <c r="J569" s="6" t="inlineStr"/>
-      <c r="K569" s="6" t="inlineStr"/>
+      <c r="H569" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J569" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K569" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -26551,10 +27031,20 @@
       <c r="G570" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H570" s="6" t="inlineStr"/>
-      <c r="I570" s="6" t="inlineStr"/>
-      <c r="J570" s="6" t="inlineStr"/>
-      <c r="K570" s="6" t="inlineStr"/>
+      <c r="H570" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J570" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K570" s="5" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -26590,10 +27080,20 @@
       <c r="G571" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H571" s="6" t="inlineStr"/>
-      <c r="I571" s="6" t="inlineStr"/>
-      <c r="J571" s="6" t="inlineStr"/>
-      <c r="K571" s="6" t="inlineStr"/>
+      <c r="H571" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I571" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J571" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K571" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -26629,10 +27129,20 @@
       <c r="G572" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H572" s="6" t="inlineStr"/>
-      <c r="I572" s="6" t="inlineStr"/>
-      <c r="J572" s="6" t="inlineStr"/>
-      <c r="K572" s="6" t="inlineStr"/>
+      <c r="H572" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I572" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J572" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K572" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -26668,10 +27178,20 @@
       <c r="G573" s="2" t="n">
         <v>1.93</v>
       </c>
-      <c r="H573" s="6" t="inlineStr"/>
-      <c r="I573" s="6" t="inlineStr"/>
-      <c r="J573" s="6" t="inlineStr"/>
-      <c r="K573" s="6" t="inlineStr"/>
+      <c r="H573" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I573" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K573" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -26707,10 +27227,20 @@
       <c r="G574" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H574" s="6" t="inlineStr"/>
-      <c r="I574" s="6" t="inlineStr"/>
-      <c r="J574" s="6" t="inlineStr"/>
-      <c r="K574" s="6" t="inlineStr"/>
+      <c r="H574" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I574" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J574" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K574" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -26746,10 +27276,20 @@
       <c r="G575" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="H575" s="6" t="inlineStr"/>
-      <c r="I575" s="6" t="inlineStr"/>
-      <c r="J575" s="6" t="inlineStr"/>
-      <c r="K575" s="6" t="inlineStr"/>
+      <c r="H575" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I575" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J575" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K575" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -26785,10 +27325,20 @@
       <c r="G576" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="H576" s="6" t="inlineStr"/>
-      <c r="I576" s="6" t="inlineStr"/>
-      <c r="J576" s="6" t="inlineStr"/>
-      <c r="K576" s="6" t="inlineStr"/>
+      <c r="H576" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I576" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J576" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K576" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -26824,10 +27374,20 @@
       <c r="G577" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H577" s="6" t="inlineStr"/>
-      <c r="I577" s="6" t="inlineStr"/>
-      <c r="J577" s="6" t="inlineStr"/>
-      <c r="K577" s="6" t="inlineStr"/>
+      <c r="H577" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I577" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J577" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K577" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -26863,10 +27423,20 @@
       <c r="G578" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H578" s="6" t="inlineStr"/>
-      <c r="I578" s="6" t="inlineStr"/>
-      <c r="J578" s="6" t="inlineStr"/>
-      <c r="K578" s="6" t="inlineStr"/>
+      <c r="H578" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I578" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J578" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K578" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -26902,10 +27472,20 @@
       <c r="G579" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H579" s="6" t="inlineStr"/>
-      <c r="I579" s="6" t="inlineStr"/>
-      <c r="J579" s="6" t="inlineStr"/>
-      <c r="K579" s="6" t="inlineStr"/>
+      <c r="H579" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I579" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J579" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K579" s="4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
@@ -26941,10 +27521,20 @@
       <c r="G580" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="H580" s="6" t="inlineStr"/>
-      <c r="I580" s="6" t="inlineStr"/>
-      <c r="J580" s="6" t="inlineStr"/>
-      <c r="K580" s="6" t="inlineStr"/>
+      <c r="H580" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I580" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J580" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K580" s="4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -26980,10 +27570,20 @@
       <c r="G581" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H581" s="6" t="inlineStr"/>
-      <c r="I581" s="6" t="inlineStr"/>
-      <c r="J581" s="6" t="inlineStr"/>
-      <c r="K581" s="6" t="inlineStr"/>
+      <c r="H581" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I581" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K581" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
@@ -27019,10 +27619,20 @@
       <c r="G582" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H582" s="6" t="inlineStr"/>
-      <c r="I582" s="6" t="inlineStr"/>
-      <c r="J582" s="6" t="inlineStr"/>
-      <c r="K582" s="6" t="inlineStr"/>
+      <c r="H582" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I582" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K582" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
@@ -27058,10 +27668,20 @@
       <c r="G583" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="6" t="inlineStr"/>
-      <c r="J583" s="6" t="inlineStr"/>
-      <c r="K583" s="6" t="inlineStr"/>
+      <c r="H583" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I583" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J583" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K583" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
@@ -27293,10 +27913,20 @@
       <c r="G588" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H588" s="6" t="inlineStr"/>
-      <c r="I588" s="6" t="inlineStr"/>
-      <c r="J588" s="6" t="inlineStr"/>
-      <c r="K588" s="6" t="inlineStr"/>
+      <c r="H588" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I588" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J588" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K588" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -27332,10 +27962,20 @@
       <c r="G589" s="2" t="n">
         <v>2.36</v>
       </c>
-      <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="6" t="inlineStr"/>
-      <c r="J589" s="6" t="inlineStr"/>
-      <c r="K589" s="6" t="inlineStr"/>
+      <c r="H589" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I589" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J589" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K589" s="4" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
@@ -27371,10 +28011,20 @@
       <c r="G590" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H590" s="6" t="inlineStr"/>
-      <c r="I590" s="6" t="inlineStr"/>
-      <c r="J590" s="6" t="inlineStr"/>
-      <c r="K590" s="6" t="inlineStr"/>
+      <c r="H590" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I590" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J590" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K590" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
@@ -27410,10 +28060,20 @@
       <c r="G591" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
-      <c r="K591" s="6" t="inlineStr"/>
+      <c r="H591" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I591" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J591" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K591" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -27449,10 +28109,20 @@
       <c r="G592" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H592" s="6" t="inlineStr"/>
-      <c r="I592" s="6" t="inlineStr"/>
-      <c r="J592" s="6" t="inlineStr"/>
-      <c r="K592" s="6" t="inlineStr"/>
+      <c r="H592" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I592" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J592" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K592" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
@@ -27488,10 +28158,20 @@
       <c r="G593" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="6" t="inlineStr"/>
-      <c r="J593" s="6" t="inlineStr"/>
-      <c r="K593" s="6" t="inlineStr"/>
+      <c r="H593" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I593" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J593" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K593" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -28506,10 +29186,20 @@
       <c r="G615" s="2" t="n">
         <v>1.82</v>
       </c>
-      <c r="H615" s="6" t="inlineStr"/>
-      <c r="I615" s="6" t="inlineStr"/>
-      <c r="J615" s="6" t="inlineStr"/>
-      <c r="K615" s="6" t="inlineStr"/>
+      <c r="H615" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I615" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J615" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K615" s="4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
@@ -28545,10 +29235,20 @@
       <c r="G616" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H616" s="6" t="inlineStr"/>
-      <c r="I616" s="6" t="inlineStr"/>
-      <c r="J616" s="6" t="inlineStr"/>
-      <c r="K616" s="6" t="inlineStr"/>
+      <c r="H616" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I616" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J616" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K616" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
@@ -28584,10 +29284,20 @@
       <c r="G617" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H617" s="6" t="inlineStr"/>
-      <c r="I617" s="6" t="inlineStr"/>
-      <c r="J617" s="6" t="inlineStr"/>
-      <c r="K617" s="6" t="inlineStr"/>
+      <c r="H617" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I617" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J617" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K617" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
@@ -28770,10 +29480,20 @@
       <c r="G621" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H621" s="6" t="inlineStr"/>
-      <c r="I621" s="6" t="inlineStr"/>
-      <c r="J621" s="6" t="inlineStr"/>
-      <c r="K621" s="6" t="inlineStr"/>
+      <c r="H621" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I621" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J621" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K621" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
@@ -28809,10 +29529,20 @@
       <c r="G622" s="2" t="n">
         <v>2.02</v>
       </c>
-      <c r="H622" s="6" t="inlineStr"/>
-      <c r="I622" s="6" t="inlineStr"/>
-      <c r="J622" s="6" t="inlineStr"/>
-      <c r="K622" s="6" t="inlineStr"/>
+      <c r="H622" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I622" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J622" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K622" s="4" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
@@ -28985,10 +29715,20 @@
       <c r="G626" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="H626" s="6" t="inlineStr"/>
-      <c r="I626" s="6" t="inlineStr"/>
-      <c r="J626" s="6" t="inlineStr"/>
-      <c r="K626" s="6" t="inlineStr"/>
+      <c r="H626" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I626" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J626" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K626" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -29024,10 +29764,20 @@
       <c r="G627" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H627" s="6" t="inlineStr"/>
-      <c r="I627" s="6" t="inlineStr"/>
-      <c r="J627" s="6" t="inlineStr"/>
-      <c r="K627" s="6" t="inlineStr"/>
+      <c r="H627" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I627" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J627" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K627" s="4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
@@ -29406,10 +30156,20 @@
       <c r="G635" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H635" s="6" t="inlineStr"/>
-      <c r="I635" s="6" t="inlineStr"/>
-      <c r="J635" s="6" t="inlineStr"/>
-      <c r="K635" s="6" t="inlineStr"/>
+      <c r="H635" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I635" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J635" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K635" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
@@ -29445,10 +30205,20 @@
       <c r="G636" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H636" s="6" t="inlineStr"/>
-      <c r="I636" s="6" t="inlineStr"/>
-      <c r="J636" s="6" t="inlineStr"/>
-      <c r="K636" s="6" t="inlineStr"/>
+      <c r="H636" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I636" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J636" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K636" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
@@ -29533,10 +30303,20 @@
       <c r="G638" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H638" s="6" t="inlineStr"/>
-      <c r="I638" s="6" t="inlineStr"/>
-      <c r="J638" s="6" t="inlineStr"/>
-      <c r="K638" s="6" t="inlineStr"/>
+      <c r="H638" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I638" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J638" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K638" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
@@ -29572,10 +30352,20 @@
       <c r="G639" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H639" s="6" t="inlineStr"/>
-      <c r="I639" s="6" t="inlineStr"/>
-      <c r="J639" s="6" t="inlineStr"/>
-      <c r="K639" s="6" t="inlineStr"/>
+      <c r="H639" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I639" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J639" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K639" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
@@ -29611,10 +30401,20 @@
       <c r="G640" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H640" s="6" t="inlineStr"/>
-      <c r="I640" s="6" t="inlineStr"/>
-      <c r="J640" s="6" t="inlineStr"/>
-      <c r="K640" s="6" t="inlineStr"/>
+      <c r="H640" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I640" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J640" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K640" s="5" t="n">
+        <v>-280</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -30473,10 +31273,20 @@
       <c r="G658" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H658" s="6" t="inlineStr"/>
-      <c r="I658" s="6" t="inlineStr"/>
-      <c r="J658" s="6" t="inlineStr"/>
-      <c r="K658" s="6" t="inlineStr"/>
+      <c r="H658" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I658" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J658" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K658" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
@@ -31002,10 +31812,20 @@
       <c r="G669" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H669" s="6" t="inlineStr"/>
-      <c r="I669" s="6" t="inlineStr"/>
-      <c r="J669" s="6" t="inlineStr"/>
-      <c r="K669" s="6" t="inlineStr"/>
+      <c r="H669" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I669" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J669" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K669" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="inlineStr">
@@ -33363,10 +34183,20 @@
       <c r="G718" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H718" s="6" t="inlineStr"/>
-      <c r="I718" s="6" t="inlineStr"/>
-      <c r="J718" s="6" t="inlineStr"/>
-      <c r="K718" s="6" t="inlineStr"/>
+      <c r="H718" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I718" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J718" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K718" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="inlineStr">
@@ -33402,10 +34232,20 @@
       <c r="G719" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H719" s="6" t="inlineStr"/>
-      <c r="I719" s="6" t="inlineStr"/>
-      <c r="J719" s="6" t="inlineStr"/>
-      <c r="K719" s="6" t="inlineStr"/>
+      <c r="H719" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I719" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J719" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K719" s="4" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="2" t="inlineStr">
@@ -33539,10 +34379,20 @@
       <c r="G722" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H722" s="6" t="inlineStr"/>
-      <c r="I722" s="6" t="inlineStr"/>
-      <c r="J722" s="6" t="inlineStr"/>
-      <c r="K722" s="6" t="inlineStr"/>
+      <c r="H722" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I722" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J722" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K722" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="2" t="inlineStr">
@@ -33578,10 +34428,20 @@
       <c r="G723" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H723" s="6" t="inlineStr"/>
-      <c r="I723" s="6" t="inlineStr"/>
-      <c r="J723" s="6" t="inlineStr"/>
-      <c r="K723" s="6" t="inlineStr"/>
+      <c r="H723" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I723" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J723" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K723" s="4" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="inlineStr">
@@ -33617,10 +34477,20 @@
       <c r="G724" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H724" s="6" t="inlineStr"/>
-      <c r="I724" s="6" t="inlineStr"/>
-      <c r="J724" s="6" t="inlineStr"/>
-      <c r="K724" s="6" t="inlineStr"/>
+      <c r="H724" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I724" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J724" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K724" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" s="2" t="inlineStr">
@@ -33656,10 +34526,20 @@
       <c r="G725" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="H725" s="6" t="inlineStr"/>
-      <c r="I725" s="6" t="inlineStr"/>
-      <c r="J725" s="6" t="inlineStr"/>
-      <c r="K725" s="6" t="inlineStr"/>
+      <c r="H725" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I725" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J725" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K725" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" s="2" t="inlineStr">
@@ -33793,10 +34673,20 @@
       <c r="G728" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H728" s="6" t="inlineStr"/>
-      <c r="I728" s="6" t="inlineStr"/>
-      <c r="J728" s="6" t="inlineStr"/>
-      <c r="K728" s="6" t="inlineStr"/>
+      <c r="H728" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I728" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J728" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K728" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="inlineStr">
@@ -33832,10 +34722,20 @@
       <c r="G729" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H729" s="6" t="inlineStr"/>
-      <c r="I729" s="6" t="inlineStr"/>
-      <c r="J729" s="6" t="inlineStr"/>
-      <c r="K729" s="6" t="inlineStr"/>
+      <c r="H729" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I729" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J729" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K729" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="inlineStr">
@@ -33871,10 +34771,20 @@
       <c r="G730" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="H730" s="6" t="inlineStr"/>
-      <c r="I730" s="6" t="inlineStr"/>
-      <c r="J730" s="6" t="inlineStr"/>
-      <c r="K730" s="6" t="inlineStr"/>
+      <c r="H730" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I730" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J730" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K730" s="4" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="inlineStr">
@@ -34409,10 +35319,20 @@
       <c r="G742" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H742" s="6" t="inlineStr"/>
-      <c r="I742" s="6" t="inlineStr"/>
-      <c r="J742" s="6" t="inlineStr"/>
-      <c r="K742" s="6" t="inlineStr"/>
+      <c r="H742" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I742" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J742" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K742" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="2" t="inlineStr">
@@ -34644,10 +35564,20 @@
       <c r="G747" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H747" s="6" t="inlineStr"/>
-      <c r="I747" s="6" t="inlineStr"/>
-      <c r="J747" s="6" t="inlineStr"/>
-      <c r="K747" s="6" t="inlineStr"/>
+      <c r="H747" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I747" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J747" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K747" s="5" t="n">
+        <v>-300</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="2" t="inlineStr">
@@ -34683,10 +35613,20 @@
       <c r="G748" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H748" s="6" t="inlineStr"/>
-      <c r="I748" s="6" t="inlineStr"/>
-      <c r="J748" s="6" t="inlineStr"/>
-      <c r="K748" s="6" t="inlineStr"/>
+      <c r="H748" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I748" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J748" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K748" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="inlineStr">
@@ -34722,10 +35662,20 @@
       <c r="G749" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H749" s="6" t="inlineStr"/>
-      <c r="I749" s="6" t="inlineStr"/>
-      <c r="J749" s="6" t="inlineStr"/>
-      <c r="K749" s="6" t="inlineStr"/>
+      <c r="H749" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I749" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J749" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K749" s="4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="inlineStr">
@@ -34761,10 +35711,20 @@
       <c r="G750" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H750" s="6" t="inlineStr"/>
-      <c r="I750" s="6" t="inlineStr"/>
-      <c r="J750" s="6" t="inlineStr"/>
-      <c r="K750" s="6" t="inlineStr"/>
+      <c r="H750" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I750" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J750" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K750" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="inlineStr">
@@ -34800,10 +35760,20 @@
       <c r="G751" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H751" s="6" t="inlineStr"/>
-      <c r="I751" s="6" t="inlineStr"/>
-      <c r="J751" s="6" t="inlineStr"/>
-      <c r="K751" s="6" t="inlineStr"/>
+      <c r="H751" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I751" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J751" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K751" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="inlineStr">
@@ -34986,10 +35956,20 @@
       <c r="G755" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H755" s="6" t="inlineStr"/>
-      <c r="I755" s="6" t="inlineStr"/>
-      <c r="J755" s="6" t="inlineStr"/>
-      <c r="K755" s="6" t="inlineStr"/>
+      <c r="H755" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I755" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J755" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K755" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="2" t="inlineStr">
@@ -35123,10 +36103,20 @@
       <c r="G758" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="H758" s="6" t="inlineStr"/>
-      <c r="I758" s="6" t="inlineStr"/>
-      <c r="J758" s="6" t="inlineStr"/>
-      <c r="K758" s="6" t="inlineStr"/>
+      <c r="H758" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I758" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J758" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K758" s="5" t="n">
+        <v>-138</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="inlineStr">
@@ -35309,10 +36299,20 @@
       <c r="G762" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H762" s="6" t="inlineStr"/>
-      <c r="I762" s="6" t="inlineStr"/>
-      <c r="J762" s="6" t="inlineStr"/>
-      <c r="K762" s="6" t="inlineStr"/>
+      <c r="H762" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I762" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J762" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K762" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="inlineStr">
@@ -35348,10 +36348,20 @@
       <c r="G763" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H763" s="6" t="inlineStr"/>
-      <c r="I763" s="6" t="inlineStr"/>
-      <c r="J763" s="6" t="inlineStr"/>
-      <c r="K763" s="6" t="inlineStr"/>
+      <c r="H763" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I763" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J763" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K763" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="2" t="inlineStr">
@@ -35387,10 +36397,20 @@
       <c r="G764" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H764" s="6" t="inlineStr"/>
-      <c r="I764" s="6" t="inlineStr"/>
-      <c r="J764" s="6" t="inlineStr"/>
-      <c r="K764" s="6" t="inlineStr"/>
+      <c r="H764" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I764" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J764" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K764" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765" s="2" t="inlineStr">
@@ -35426,10 +36446,20 @@
       <c r="G765" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H765" s="6" t="inlineStr"/>
-      <c r="I765" s="6" t="inlineStr"/>
-      <c r="J765" s="6" t="inlineStr"/>
-      <c r="K765" s="6" t="inlineStr"/>
+      <c r="H765" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I765" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J765" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K765" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="inlineStr">
@@ -35759,10 +36789,20 @@
       <c r="G772" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H772" s="6" t="inlineStr"/>
-      <c r="I772" s="6" t="inlineStr"/>
-      <c r="J772" s="6" t="inlineStr"/>
-      <c r="K772" s="6" t="inlineStr"/>
+      <c r="H772" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I772" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J772" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K772" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="inlineStr">
@@ -35798,10 +36838,20 @@
       <c r="G773" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H773" s="6" t="inlineStr"/>
-      <c r="I773" s="6" t="inlineStr"/>
-      <c r="J773" s="6" t="inlineStr"/>
-      <c r="K773" s="6" t="inlineStr"/>
+      <c r="H773" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I773" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J773" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K773" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="2" t="inlineStr">
@@ -36180,10 +37230,20 @@
       <c r="G781" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H781" s="6" t="inlineStr"/>
-      <c r="I781" s="6" t="inlineStr"/>
-      <c r="J781" s="6" t="inlineStr"/>
-      <c r="K781" s="6" t="inlineStr"/>
+      <c r="H781" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I781" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J781" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K781" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782" s="2" t="inlineStr">
@@ -36542,10 +37602,20 @@
       <c r="G789" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H789" s="6" t="inlineStr"/>
-      <c r="I789" s="6" t="inlineStr"/>
-      <c r="J789" s="6" t="inlineStr"/>
-      <c r="K789" s="6" t="inlineStr"/>
+      <c r="H789" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I789" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J789" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K789" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" s="2" t="inlineStr">
@@ -36630,10 +37700,20 @@
       <c r="G791" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H791" s="6" t="inlineStr"/>
-      <c r="I791" s="6" t="inlineStr"/>
-      <c r="J791" s="6" t="inlineStr"/>
-      <c r="K791" s="6" t="inlineStr"/>
+      <c r="H791" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I791" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J791" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K791" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" s="2" t="inlineStr">
@@ -36669,10 +37749,20 @@
       <c r="G792" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H792" s="6" t="inlineStr"/>
-      <c r="I792" s="6" t="inlineStr"/>
-      <c r="J792" s="6" t="inlineStr"/>
-      <c r="K792" s="6" t="inlineStr"/>
+      <c r="H792" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I792" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J792" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K792" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793" s="2" t="inlineStr">
@@ -36747,10 +37837,20 @@
       <c r="G794" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H794" s="6" t="inlineStr"/>
-      <c r="I794" s="6" t="inlineStr"/>
-      <c r="J794" s="6" t="inlineStr"/>
-      <c r="K794" s="6" t="inlineStr"/>
+      <c r="H794" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I794" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J794" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K794" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="inlineStr">
@@ -36786,10 +37886,20 @@
       <c r="G795" s="2" t="n">
         <v>1.98</v>
       </c>
-      <c r="H795" s="6" t="inlineStr"/>
-      <c r="I795" s="6" t="inlineStr"/>
-      <c r="J795" s="6" t="inlineStr"/>
-      <c r="K795" s="6" t="inlineStr"/>
+      <c r="H795" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I795" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J795" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K795" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="2" t="inlineStr">
@@ -36825,10 +37935,20 @@
       <c r="G796" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H796" s="6" t="inlineStr"/>
-      <c r="I796" s="6" t="inlineStr"/>
-      <c r="J796" s="6" t="inlineStr"/>
-      <c r="K796" s="6" t="inlineStr"/>
+      <c r="H796" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I796" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J796" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K796" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" s="2" t="inlineStr">
@@ -36864,10 +37984,20 @@
       <c r="G797" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H797" s="6" t="inlineStr"/>
-      <c r="I797" s="6" t="inlineStr"/>
-      <c r="J797" s="6" t="inlineStr"/>
-      <c r="K797" s="6" t="inlineStr"/>
+      <c r="H797" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I797" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J797" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K797" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" s="2" t="inlineStr">
@@ -36903,10 +38033,20 @@
       <c r="G798" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H798" s="6" t="inlineStr"/>
-      <c r="I798" s="6" t="inlineStr"/>
-      <c r="J798" s="6" t="inlineStr"/>
-      <c r="K798" s="6" t="inlineStr"/>
+      <c r="H798" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I798" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J798" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K798" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799" s="2" t="inlineStr">
@@ -36942,10 +38082,20 @@
       <c r="G799" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H799" s="6" t="inlineStr"/>
-      <c r="I799" s="6" t="inlineStr"/>
-      <c r="J799" s="6" t="inlineStr"/>
-      <c r="K799" s="6" t="inlineStr"/>
+      <c r="H799" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I799" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J799" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K799" s="4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800" s="2" t="inlineStr">
@@ -37226,10 +38376,20 @@
       <c r="G805" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H805" s="6" t="inlineStr"/>
-      <c r="I805" s="6" t="inlineStr"/>
-      <c r="J805" s="6" t="inlineStr"/>
-      <c r="K805" s="6" t="inlineStr"/>
+      <c r="H805" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I805" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J805" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K805" s="4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806" s="2" t="inlineStr">
@@ -37265,10 +38425,20 @@
       <c r="G806" s="2" t="n">
         <v>2.62</v>
       </c>
-      <c r="H806" s="6" t="inlineStr"/>
-      <c r="I806" s="6" t="inlineStr"/>
-      <c r="J806" s="6" t="inlineStr"/>
-      <c r="K806" s="6" t="inlineStr"/>
+      <c r="H806" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I806" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J806" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K806" s="5" t="n">
+        <v>-162</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="2" t="inlineStr">
@@ -37382,10 +38552,20 @@
       <c r="G809" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H809" s="6" t="inlineStr"/>
-      <c r="I809" s="6" t="inlineStr"/>
-      <c r="J809" s="6" t="inlineStr"/>
-      <c r="K809" s="6" t="inlineStr"/>
+      <c r="H809" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I809" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J809" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K809" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="810">
       <c r="A810" s="2" t="inlineStr">
@@ -37421,10 +38601,20 @@
       <c r="G810" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="H810" s="6" t="inlineStr"/>
-      <c r="I810" s="6" t="inlineStr"/>
-      <c r="J810" s="6" t="inlineStr"/>
-      <c r="K810" s="6" t="inlineStr"/>
+      <c r="H810" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I810" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J810" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K810" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" s="2" t="inlineStr">
@@ -37460,10 +38650,20 @@
       <c r="G811" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="H811" s="6" t="inlineStr"/>
-      <c r="I811" s="6" t="inlineStr"/>
-      <c r="J811" s="6" t="inlineStr"/>
-      <c r="K811" s="6" t="inlineStr"/>
+      <c r="H811" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I811" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J811" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K811" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812" s="2" t="inlineStr">
@@ -37499,10 +38699,20 @@
       <c r="G812" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H812" s="6" t="inlineStr"/>
-      <c r="I812" s="6" t="inlineStr"/>
-      <c r="J812" s="6" t="inlineStr"/>
-      <c r="K812" s="6" t="inlineStr"/>
+      <c r="H812" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I812" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J812" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K812" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="813">
       <c r="A813" s="2" t="inlineStr">
@@ -37538,10 +38748,20 @@
       <c r="G813" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="H813" s="6" t="inlineStr"/>
-      <c r="I813" s="6" t="inlineStr"/>
-      <c r="J813" s="6" t="inlineStr"/>
-      <c r="K813" s="6" t="inlineStr"/>
+      <c r="H813" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I813" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J813" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K813" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814" s="2" t="inlineStr">
@@ -37577,10 +38797,20 @@
       <c r="G814" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H814" s="6" t="inlineStr"/>
-      <c r="I814" s="6" t="inlineStr"/>
-      <c r="J814" s="6" t="inlineStr"/>
-      <c r="K814" s="6" t="inlineStr"/>
+      <c r="H814" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I814" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J814" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K814" s="4" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815" s="2" t="inlineStr">
@@ -37616,10 +38846,20 @@
       <c r="G815" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H815" s="6" t="inlineStr"/>
-      <c r="I815" s="6" t="inlineStr"/>
-      <c r="J815" s="6" t="inlineStr"/>
-      <c r="K815" s="6" t="inlineStr"/>
+      <c r="H815" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I815" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J815" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K815" s="5" t="n">
+        <v>-122</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816" s="2" t="inlineStr">
@@ -37655,10 +38895,20 @@
       <c r="G816" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H816" s="6" t="inlineStr"/>
-      <c r="I816" s="6" t="inlineStr"/>
-      <c r="J816" s="6" t="inlineStr"/>
-      <c r="K816" s="6" t="inlineStr"/>
+      <c r="H816" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I816" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J816" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K816" s="5" t="n">
+        <v>-295</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" s="2" t="inlineStr">
@@ -37694,10 +38944,20 @@
       <c r="G817" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H817" s="6" t="inlineStr"/>
-      <c r="I817" s="6" t="inlineStr"/>
-      <c r="J817" s="6" t="inlineStr"/>
-      <c r="K817" s="6" t="inlineStr"/>
+      <c r="H817" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I817" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J817" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K817" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818" s="2" t="inlineStr">
@@ -37880,10 +39140,20 @@
       <c r="G821" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H821" s="6" t="inlineStr"/>
-      <c r="I821" s="6" t="inlineStr"/>
-      <c r="J821" s="6" t="inlineStr"/>
-      <c r="K821" s="6" t="inlineStr"/>
+      <c r="H821" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I821" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J821" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K821" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822" s="2" t="inlineStr">
@@ -37919,10 +39189,20 @@
       <c r="G822" s="2" t="n">
         <v>1.87</v>
       </c>
-      <c r="H822" s="6" t="inlineStr"/>
-      <c r="I822" s="6" t="inlineStr"/>
-      <c r="J822" s="6" t="inlineStr"/>
-      <c r="K822" s="6" t="inlineStr"/>
+      <c r="H822" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I822" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J822" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K822" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="823">
       <c r="A823" s="2" t="inlineStr">
@@ -38193,10 +39473,20 @@
       <c r="G828" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="H828" s="6" t="inlineStr"/>
-      <c r="I828" s="6" t="inlineStr"/>
-      <c r="J828" s="6" t="inlineStr"/>
-      <c r="K828" s="6" t="inlineStr"/>
+      <c r="H828" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I828" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J828" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K828" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="829">
       <c r="A829" s="2" t="inlineStr">
@@ -38232,10 +39522,20 @@
       <c r="G829" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="H829" s="6" t="inlineStr"/>
-      <c r="I829" s="6" t="inlineStr"/>
-      <c r="J829" s="6" t="inlineStr"/>
-      <c r="K829" s="6" t="inlineStr"/>
+      <c r="H829" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I829" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J829" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K829" s="5" t="n">
+        <v>-126</v>
+      </c>
     </row>
     <row r="830">
       <c r="A830" s="2" t="inlineStr">
@@ -38692,10 +39992,20 @@
       <c r="G839" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="H839" s="6" t="inlineStr"/>
-      <c r="I839" s="6" t="inlineStr"/>
-      <c r="J839" s="6" t="inlineStr"/>
-      <c r="K839" s="6" t="inlineStr"/>
+      <c r="H839" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I839" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J839" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K839" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840" s="2" t="inlineStr">
@@ -38731,10 +40041,20 @@
       <c r="G840" s="2" t="n">
         <v>2.28</v>
       </c>
-      <c r="H840" s="6" t="inlineStr"/>
-      <c r="I840" s="6" t="inlineStr"/>
-      <c r="J840" s="6" t="inlineStr"/>
-      <c r="K840" s="6" t="inlineStr"/>
+      <c r="H840" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I840" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J840" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K840" s="4" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" s="2" t="inlineStr">
@@ -38770,10 +40090,20 @@
       <c r="G841" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="H841" s="6" t="inlineStr"/>
-      <c r="I841" s="6" t="inlineStr"/>
-      <c r="J841" s="6" t="inlineStr"/>
-      <c r="K841" s="6" t="inlineStr"/>
+      <c r="H841" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I841" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J841" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K841" s="5" t="n">
+        <v>-126</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" s="2" t="inlineStr">
@@ -38809,10 +40139,20 @@
       <c r="G842" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H842" s="6" t="inlineStr"/>
-      <c r="I842" s="6" t="inlineStr"/>
-      <c r="J842" s="6" t="inlineStr"/>
-      <c r="K842" s="6" t="inlineStr"/>
+      <c r="H842" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I842" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J842" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K842" s="5" t="n">
+        <v>-255</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" s="2" t="inlineStr">
@@ -38848,10 +40188,20 @@
       <c r="G843" s="2" t="n">
         <v>1.96</v>
       </c>
-      <c r="H843" s="6" t="inlineStr"/>
-      <c r="I843" s="6" t="inlineStr"/>
-      <c r="J843" s="6" t="inlineStr"/>
-      <c r="K843" s="6" t="inlineStr"/>
+      <c r="H843" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I843" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J843" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K843" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" s="2" t="inlineStr">
@@ -38887,10 +40237,20 @@
       <c r="G844" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H844" s="6" t="inlineStr"/>
-      <c r="I844" s="6" t="inlineStr"/>
-      <c r="J844" s="6" t="inlineStr"/>
-      <c r="K844" s="6" t="inlineStr"/>
+      <c r="H844" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I844" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J844" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K844" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="inlineStr">
@@ -38926,10 +40286,20 @@
       <c r="G845" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H845" s="6" t="inlineStr"/>
-      <c r="I845" s="6" t="inlineStr"/>
-      <c r="J845" s="6" t="inlineStr"/>
-      <c r="K845" s="6" t="inlineStr"/>
+      <c r="H845" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I845" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J845" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K845" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" s="2" t="inlineStr">
@@ -39484,10 +40854,20 @@
       <c r="G857" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H857" s="6" t="inlineStr"/>
-      <c r="I857" s="6" t="inlineStr"/>
-      <c r="J857" s="6" t="inlineStr"/>
-      <c r="K857" s="6" t="inlineStr"/>
+      <c r="H857" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I857" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J857" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K857" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858" s="2" t="inlineStr">
@@ -39523,10 +40903,20 @@
       <c r="G858" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H858" s="6" t="inlineStr"/>
-      <c r="I858" s="6" t="inlineStr"/>
-      <c r="J858" s="6" t="inlineStr"/>
-      <c r="K858" s="6" t="inlineStr"/>
+      <c r="H858" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I858" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J858" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K858" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="859">
       <c r="A859" s="2" t="inlineStr">
@@ -39875,10 +41265,20 @@
       <c r="G866" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="H866" s="6" t="inlineStr"/>
-      <c r="I866" s="6" t="inlineStr"/>
-      <c r="J866" s="6" t="inlineStr"/>
-      <c r="K866" s="6" t="inlineStr"/>
+      <c r="H866" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I866" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J866" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K866" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867" s="2" t="inlineStr">
@@ -39914,10 +41314,20 @@
       <c r="G867" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="H867" s="6" t="inlineStr"/>
-      <c r="I867" s="6" t="inlineStr"/>
-      <c r="J867" s="6" t="inlineStr"/>
-      <c r="K867" s="6" t="inlineStr"/>
+      <c r="H867" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I867" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J867" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K867" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" s="2" t="inlineStr">
@@ -40051,10 +41461,20 @@
       <c r="G870" s="2" t="n">
         <v>3.45</v>
       </c>
-      <c r="H870" s="6" t="inlineStr"/>
-      <c r="I870" s="6" t="inlineStr"/>
-      <c r="J870" s="6" t="inlineStr"/>
-      <c r="K870" s="6" t="inlineStr"/>
+      <c r="H870" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I870" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J870" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K870" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871" s="2" t="inlineStr">
@@ -40090,10 +41510,20 @@
       <c r="G871" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H871" s="6" t="inlineStr"/>
-      <c r="I871" s="6" t="inlineStr"/>
-      <c r="J871" s="6" t="inlineStr"/>
-      <c r="K871" s="6" t="inlineStr"/>
+      <c r="H871" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I871" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J871" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K871" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872" s="2" t="inlineStr">
@@ -40383,10 +41813,20 @@
       <c r="G878" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H878" s="6" t="inlineStr"/>
-      <c r="I878" s="6" t="inlineStr"/>
-      <c r="J878" s="6" t="inlineStr"/>
-      <c r="K878" s="6" t="inlineStr"/>
+      <c r="H878" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I878" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J878" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K878" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879" s="2" t="inlineStr">
@@ -40520,10 +41960,20 @@
       <c r="G881" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H881" s="6" t="inlineStr"/>
-      <c r="I881" s="6" t="inlineStr"/>
-      <c r="J881" s="6" t="inlineStr"/>
-      <c r="K881" s="6" t="inlineStr"/>
+      <c r="H881" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I881" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J881" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K881" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" s="2" t="inlineStr">
@@ -40559,10 +42009,20 @@
       <c r="G882" s="2" t="n">
         <v>2.04</v>
       </c>
-      <c r="H882" s="6" t="inlineStr"/>
-      <c r="I882" s="6" t="inlineStr"/>
-      <c r="J882" s="6" t="inlineStr"/>
-      <c r="K882" s="6" t="inlineStr"/>
+      <c r="H882" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I882" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J882" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K882" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883" s="2" t="inlineStr">
@@ -40921,10 +42381,20 @@
       <c r="G890" s="2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H890" s="6" t="inlineStr"/>
-      <c r="I890" s="6" t="inlineStr"/>
-      <c r="J890" s="6" t="inlineStr"/>
-      <c r="K890" s="6" t="inlineStr"/>
+      <c r="H890" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I890" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J890" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K890" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891" s="2" t="inlineStr">
@@ -40960,10 +42430,20 @@
       <c r="G891" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="H891" s="6" t="inlineStr"/>
-      <c r="I891" s="6" t="inlineStr"/>
-      <c r="J891" s="6" t="inlineStr"/>
-      <c r="K891" s="6" t="inlineStr"/>
+      <c r="H891" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I891" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J891" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K891" s="5" t="n">
+        <v>-240</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" s="2" t="inlineStr">
@@ -40999,10 +42479,20 @@
       <c r="G892" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="H892" s="6" t="inlineStr"/>
-      <c r="I892" s="6" t="inlineStr"/>
-      <c r="J892" s="6" t="inlineStr"/>
-      <c r="K892" s="6" t="inlineStr"/>
+      <c r="H892" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I892" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J892" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K892" s="5" t="n">
+        <v>-142</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893" s="2" t="inlineStr">
@@ -41136,10 +42626,20 @@
       <c r="G895" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H895" s="6" t="inlineStr"/>
-      <c r="I895" s="6" t="inlineStr"/>
-      <c r="J895" s="6" t="inlineStr"/>
-      <c r="K895" s="6" t="inlineStr"/>
+      <c r="H895" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I895" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J895" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K895" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="896">
       <c r="A896" s="2" t="inlineStr">
@@ -41175,10 +42675,20 @@
       <c r="G896" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="H896" s="6" t="inlineStr"/>
-      <c r="I896" s="6" t="inlineStr"/>
-      <c r="J896" s="6" t="inlineStr"/>
-      <c r="K896" s="6" t="inlineStr"/>
+      <c r="H896" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I896" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J896" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K896" s="4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897" s="2" t="inlineStr">
@@ -41684,10 +43194,20 @@
       <c r="G907" s="2" t="n">
         <v>9.6</v>
       </c>
-      <c r="H907" s="6" t="inlineStr"/>
-      <c r="I907" s="6" t="inlineStr"/>
-      <c r="J907" s="6" t="inlineStr"/>
-      <c r="K907" s="6" t="inlineStr"/>
+      <c r="H907" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I907" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J907" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K907" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="908">
       <c r="A908" s="2" t="inlineStr">
@@ -41723,10 +43243,20 @@
       <c r="G908" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="H908" s="6" t="inlineStr"/>
-      <c r="I908" s="6" t="inlineStr"/>
-      <c r="J908" s="6" t="inlineStr"/>
-      <c r="K908" s="6" t="inlineStr"/>
+      <c r="H908" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I908" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J908" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K908" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">
@@ -41762,10 +43292,20 @@
       <c r="G909" s="2" t="n">
         <v>2.48</v>
       </c>
-      <c r="H909" s="6" t="inlineStr"/>
-      <c r="I909" s="6" t="inlineStr"/>
-      <c r="J909" s="6" t="inlineStr"/>
-      <c r="K909" s="6" t="inlineStr"/>
+      <c r="H909" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I909" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J909" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K909" s="4" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910" s="2" t="inlineStr">
@@ -42046,10 +43586,20 @@
       <c r="G915" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H915" s="6" t="inlineStr"/>
-      <c r="I915" s="6" t="inlineStr"/>
-      <c r="J915" s="6" t="inlineStr"/>
-      <c r="K915" s="6" t="inlineStr"/>
+      <c r="H915" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I915" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J915" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K915" s="5" t="n">
+        <v>-250</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916" s="2" t="inlineStr">
@@ -42085,10 +43635,20 @@
       <c r="G916" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="H916" s="6" t="inlineStr"/>
-      <c r="I916" s="6" t="inlineStr"/>
-      <c r="J916" s="6" t="inlineStr"/>
-      <c r="K916" s="6" t="inlineStr"/>
+      <c r="H916" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I916" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J916" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K916" s="4" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="917">
       <c r="A917" s="2" t="inlineStr">
@@ -42124,10 +43684,20 @@
       <c r="G917" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H917" s="6" t="inlineStr"/>
-      <c r="I917" s="6" t="inlineStr"/>
-      <c r="J917" s="6" t="inlineStr"/>
-      <c r="K917" s="6" t="inlineStr"/>
+      <c r="H917" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I917" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J917" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K917" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="918">
       <c r="A918" s="2" t="inlineStr">
@@ -42163,10 +43733,20 @@
       <c r="G918" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="H918" s="6" t="inlineStr"/>
-      <c r="I918" s="6" t="inlineStr"/>
-      <c r="J918" s="6" t="inlineStr"/>
-      <c r="K918" s="6" t="inlineStr"/>
+      <c r="H918" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I918" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J918" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K918" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="919">
       <c r="A919" s="2" t="inlineStr">
@@ -42202,10 +43782,20 @@
       <c r="G919" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H919" s="6" t="inlineStr"/>
-      <c r="I919" s="6" t="inlineStr"/>
-      <c r="J919" s="6" t="inlineStr"/>
-      <c r="K919" s="6" t="inlineStr"/>
+      <c r="H919" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I919" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J919" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K919" s="4" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="920">
       <c r="A920" s="2" t="inlineStr">
@@ -42241,10 +43831,20 @@
       <c r="G920" s="2" t="n">
         <v>2.34</v>
       </c>
-      <c r="H920" s="6" t="inlineStr"/>
-      <c r="I920" s="6" t="inlineStr"/>
-      <c r="J920" s="6" t="inlineStr"/>
-      <c r="K920" s="6" t="inlineStr"/>
+      <c r="H920" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I920" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J920" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K920" s="5" t="n">
+        <v>-134</v>
+      </c>
     </row>
     <row r="921">
       <c r="A921" s="2" t="inlineStr">
@@ -42476,10 +44076,20 @@
       <c r="G925" s="2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H925" s="6" t="inlineStr"/>
-      <c r="I925" s="6" t="inlineStr"/>
-      <c r="J925" s="6" t="inlineStr"/>
-      <c r="K925" s="6" t="inlineStr"/>
+      <c r="H925" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I925" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J925" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K925" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
@@ -42515,10 +44125,20 @@
       <c r="G926" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="H926" s="6" t="inlineStr"/>
-      <c r="I926" s="6" t="inlineStr"/>
-      <c r="J926" s="6" t="inlineStr"/>
-      <c r="K926" s="6" t="inlineStr"/>
+      <c r="H926" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I926" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J926" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K926" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927" s="2" t="inlineStr">
@@ -42554,10 +44174,20 @@
       <c r="G927" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H927" s="6" t="inlineStr"/>
-      <c r="I927" s="6" t="inlineStr"/>
-      <c r="J927" s="6" t="inlineStr"/>
-      <c r="K927" s="6" t="inlineStr"/>
+      <c r="H927" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I927" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J927" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K927" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928" s="2" t="inlineStr">
@@ -42632,10 +44262,20 @@
       <c r="G929" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H929" s="6" t="inlineStr"/>
-      <c r="I929" s="6" t="inlineStr"/>
-      <c r="J929" s="6" t="inlineStr"/>
-      <c r="K929" s="6" t="inlineStr"/>
+      <c r="H929" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I929" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J929" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K929" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="930">
       <c r="A930" s="2" t="inlineStr">
@@ -42671,10 +44311,20 @@
       <c r="G930" s="2" t="n">
         <v>2.12</v>
       </c>
-      <c r="H930" s="6" t="inlineStr"/>
-      <c r="I930" s="6" t="inlineStr"/>
-      <c r="J930" s="6" t="inlineStr"/>
-      <c r="K930" s="6" t="inlineStr"/>
+      <c r="H930" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I930" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J930" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K930" s="4" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931" s="2" t="inlineStr">
@@ -43102,10 +44752,20 @@
       <c r="G939" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H939" s="6" t="inlineStr"/>
-      <c r="I939" s="6" t="inlineStr"/>
-      <c r="J939" s="6" t="inlineStr"/>
-      <c r="K939" s="6" t="inlineStr"/>
+      <c r="H939" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I939" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J939" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K939" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" s="2" t="inlineStr">
@@ -43141,10 +44801,20 @@
       <c r="G940" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="H940" s="6" t="inlineStr"/>
-      <c r="I940" s="6" t="inlineStr"/>
-      <c r="J940" s="6" t="inlineStr"/>
-      <c r="K940" s="6" t="inlineStr"/>
+      <c r="H940" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I940" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J940" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K940" s="4" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941" s="2" t="inlineStr">
@@ -43659,10 +45329,20 @@
       <c r="G952" s="2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H952" s="6" t="inlineStr"/>
-      <c r="I952" s="6" t="inlineStr"/>
-      <c r="J952" s="6" t="inlineStr"/>
-      <c r="K952" s="6" t="inlineStr"/>
+      <c r="H952" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I952" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J952" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K952" s="5" t="n">
+        <v>-820</v>
+      </c>
     </row>
     <row r="953">
       <c r="A953" s="2" t="inlineStr">
@@ -43698,10 +45378,20 @@
       <c r="G953" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H953" s="6" t="inlineStr"/>
-      <c r="I953" s="6" t="inlineStr"/>
-      <c r="J953" s="6" t="inlineStr"/>
-      <c r="K953" s="6" t="inlineStr"/>
+      <c r="H953" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I953" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J953" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K953" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="954">
       <c r="A954" s="2" t="inlineStr">
@@ -43737,10 +45427,20 @@
       <c r="G954" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="H954" s="6" t="inlineStr"/>
-      <c r="I954" s="6" t="inlineStr"/>
-      <c r="J954" s="6" t="inlineStr"/>
-      <c r="K954" s="6" t="inlineStr"/>
+      <c r="H954" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I954" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J954" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K954" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955" s="2" t="inlineStr">
@@ -43776,10 +45476,20 @@
       <c r="G955" s="2" t="n">
         <v>2.76</v>
       </c>
-      <c r="H955" s="6" t="inlineStr"/>
-      <c r="I955" s="6" t="inlineStr"/>
-      <c r="J955" s="6" t="inlineStr"/>
-      <c r="K955" s="6" t="inlineStr"/>
+      <c r="H955" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I955" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J955" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K955" s="5" t="n">
+        <v>-176</v>
+      </c>
     </row>
     <row r="956">
       <c r="A956" s="2" t="inlineStr">
@@ -43991,10 +45701,20 @@
       <c r="G960" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H960" s="6" t="inlineStr"/>
-      <c r="I960" s="6" t="inlineStr"/>
-      <c r="J960" s="6" t="inlineStr"/>
-      <c r="K960" s="6" t="inlineStr"/>
+      <c r="H960" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I960" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J960" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K960" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="961">
       <c r="A961" s="2" t="inlineStr">
@@ -44030,10 +45750,20 @@
       <c r="G961" s="2" t="n">
         <v>2.16</v>
       </c>
-      <c r="H961" s="6" t="inlineStr"/>
-      <c r="I961" s="6" t="inlineStr"/>
-      <c r="J961" s="6" t="inlineStr"/>
-      <c r="K961" s="6" t="inlineStr"/>
+      <c r="H961" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I961" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J961" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K961" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="962">
       <c r="A962" s="2" t="inlineStr">
@@ -44469,10 +46199,20 @@
       <c r="G972" s="2" t="n">
         <v>9.4</v>
       </c>
-      <c r="H972" s="6" t="inlineStr"/>
-      <c r="I972" s="6" t="inlineStr"/>
-      <c r="J972" s="6" t="inlineStr"/>
-      <c r="K972" s="6" t="inlineStr"/>
+      <c r="H972" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I972" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J972" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K972" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="973">
       <c r="A973" s="2" t="inlineStr">
@@ -44508,10 +46248,20 @@
       <c r="G973" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H973" s="6" t="inlineStr"/>
-      <c r="I973" s="6" t="inlineStr"/>
-      <c r="J973" s="6" t="inlineStr"/>
-      <c r="K973" s="6" t="inlineStr"/>
+      <c r="H973" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I973" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J973" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K973" s="5" t="n">
+        <v>-265</v>
+      </c>
     </row>
     <row r="974">
       <c r="A974" s="2" t="inlineStr">
@@ -44547,10 +46297,20 @@
       <c r="G974" s="2" t="n">
         <v>2.58</v>
       </c>
-      <c r="H974" s="6" t="inlineStr"/>
-      <c r="I974" s="6" t="inlineStr"/>
-      <c r="J974" s="6" t="inlineStr"/>
-      <c r="K974" s="6" t="inlineStr"/>
+      <c r="H974" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I974" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J974" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K974" s="5" t="n">
+        <v>-158</v>
+      </c>
     </row>
     <row r="975">
       <c r="A975" s="2" t="inlineStr">
@@ -45094,10 +46854,20 @@
       <c r="G987" s="2" t="n">
         <v>2.44</v>
       </c>
-      <c r="H987" s="6" t="inlineStr"/>
-      <c r="I987" s="6" t="inlineStr"/>
-      <c r="J987" s="6" t="inlineStr"/>
-      <c r="K987" s="6" t="inlineStr"/>
+      <c r="H987" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I987" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J987" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K987" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="988">
       <c r="A988" s="2" t="inlineStr">
@@ -45838,10 +47608,20 @@
       <c r="G1003" s="2" t="n">
         <v>3.55</v>
       </c>
-      <c r="H1003" s="6" t="inlineStr"/>
-      <c r="I1003" s="6" t="inlineStr"/>
-      <c r="J1003" s="6" t="inlineStr"/>
-      <c r="K1003" s="6" t="inlineStr"/>
+      <c r="H1003" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1003" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1003" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1003" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" s="2" t="inlineStr">
@@ -45877,10 +47657,20 @@
       <c r="G1004" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H1004" s="6" t="inlineStr"/>
-      <c r="I1004" s="6" t="inlineStr"/>
-      <c r="J1004" s="6" t="inlineStr"/>
-      <c r="K1004" s="6" t="inlineStr"/>
+      <c r="H1004" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1004" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1004" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1004" s="4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" s="2" t="inlineStr">
@@ -45916,10 +47706,20 @@
       <c r="G1005" s="2" t="n">
         <v>2.68</v>
       </c>
-      <c r="H1005" s="6" t="inlineStr"/>
-      <c r="I1005" s="6" t="inlineStr"/>
-      <c r="J1005" s="6" t="inlineStr"/>
-      <c r="K1005" s="6" t="inlineStr"/>
+      <c r="H1005" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1005" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1005" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1005" s="5" t="n">
+        <v>-168</v>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" s="2" t="inlineStr">
@@ -45955,10 +47755,20 @@
       <c r="G1006" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H1006" s="6" t="inlineStr"/>
-      <c r="I1006" s="6" t="inlineStr"/>
-      <c r="J1006" s="6" t="inlineStr"/>
-      <c r="K1006" s="6" t="inlineStr"/>
+      <c r="H1006" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1006" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1006" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1006" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="inlineStr">
@@ -45994,10 +47804,20 @@
       <c r="G1007" s="2" t="n">
         <v>3.15</v>
       </c>
-      <c r="H1007" s="6" t="inlineStr"/>
-      <c r="I1007" s="6" t="inlineStr"/>
-      <c r="J1007" s="6" t="inlineStr"/>
-      <c r="K1007" s="6" t="inlineStr"/>
+      <c r="H1007" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1007" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1007" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1007" s="5" t="n">
+        <v>-215</v>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" s="2" t="inlineStr">
@@ -46033,10 +47853,20 @@
       <c r="G1008" s="2" t="n">
         <v>9.6</v>
       </c>
-      <c r="H1008" s="6" t="inlineStr"/>
-      <c r="I1008" s="6" t="inlineStr"/>
-      <c r="J1008" s="6" t="inlineStr"/>
-      <c r="K1008" s="6" t="inlineStr"/>
+      <c r="H1008" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1008" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1008" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1008" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" s="2" t="inlineStr">
@@ -46072,10 +47902,20 @@
       <c r="G1009" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H1009" s="6" t="inlineStr"/>
-      <c r="I1009" s="6" t="inlineStr"/>
-      <c r="J1009" s="6" t="inlineStr"/>
-      <c r="K1009" s="6" t="inlineStr"/>
+      <c r="H1009" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1009" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1009" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1009" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" s="2" t="inlineStr">
@@ -46345,10 +48185,20 @@
       <c r="G1016" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H1016" s="6" t="inlineStr"/>
-      <c r="I1016" s="6" t="inlineStr"/>
-      <c r="J1016" s="6" t="inlineStr"/>
-      <c r="K1016" s="6" t="inlineStr"/>
+      <c r="H1016" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1016" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1016" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1016" s="5" t="n">
+        <v>-330</v>
+      </c>
     </row>
     <row r="1017">
       <c r="A1017" s="2" t="inlineStr">
@@ -46384,10 +48234,20 @@
       <c r="G1017" s="2" t="n">
         <v>1.84</v>
       </c>
-      <c r="H1017" s="6" t="inlineStr"/>
-      <c r="I1017" s="6" t="inlineStr"/>
-      <c r="J1017" s="6" t="inlineStr"/>
-      <c r="K1017" s="6" t="inlineStr"/>
+      <c r="H1017" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1017" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1017" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1017" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1018">
       <c r="A1018" s="2" t="inlineStr">
@@ -46423,10 +48283,20 @@
       <c r="G1018" s="2" t="n">
         <v>2.06</v>
       </c>
-      <c r="H1018" s="6" t="inlineStr"/>
-      <c r="I1018" s="6" t="inlineStr"/>
-      <c r="J1018" s="6" t="inlineStr"/>
-      <c r="K1018" s="6" t="inlineStr"/>
+      <c r="H1018" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1018" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1018" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1018" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1019">
       <c r="A1019" s="2" t="inlineStr">
@@ -46462,10 +48332,20 @@
       <c r="G1019" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="H1019" s="6" t="inlineStr"/>
-      <c r="I1019" s="6" t="inlineStr"/>
-      <c r="J1019" s="6" t="inlineStr"/>
-      <c r="K1019" s="6" t="inlineStr"/>
+      <c r="H1019" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1019" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1019" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1019" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" s="2" t="inlineStr">
@@ -46922,10 +48802,20 @@
       <c r="G1029" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H1029" s="6" t="inlineStr"/>
-      <c r="I1029" s="6" t="inlineStr"/>
-      <c r="J1029" s="6" t="inlineStr"/>
-      <c r="K1029" s="6" t="inlineStr"/>
+      <c r="H1029" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1029" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1029" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1029" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" s="2" t="inlineStr">
@@ -46961,10 +48851,20 @@
       <c r="G1030" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="H1030" s="6" t="inlineStr"/>
-      <c r="I1030" s="6" t="inlineStr"/>
-      <c r="J1030" s="6" t="inlineStr"/>
-      <c r="K1030" s="6" t="inlineStr"/>
+      <c r="H1030" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1030" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1030" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1030" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" s="2" t="inlineStr">
@@ -47000,10 +48900,20 @@
       <c r="G1031" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="H1031" s="6" t="inlineStr"/>
-      <c r="I1031" s="6" t="inlineStr"/>
-      <c r="J1031" s="6" t="inlineStr"/>
-      <c r="K1031" s="6" t="inlineStr"/>
+      <c r="H1031" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1031" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1031" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1031" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" s="2" t="inlineStr">
@@ -47039,10 +48949,20 @@
       <c r="G1032" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="H1032" s="6" t="inlineStr"/>
-      <c r="I1032" s="6" t="inlineStr"/>
-      <c r="J1032" s="6" t="inlineStr"/>
-      <c r="K1032" s="6" t="inlineStr"/>
+      <c r="H1032" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1032" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1032" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1032" s="4" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" s="2" t="inlineStr">
@@ -47254,10 +49174,20 @@
       <c r="G1037" s="2" t="n">
         <v>2.02</v>
       </c>
-      <c r="H1037" s="6" t="inlineStr"/>
-      <c r="I1037" s="6" t="inlineStr"/>
-      <c r="J1037" s="6" t="inlineStr"/>
-      <c r="K1037" s="6" t="inlineStr"/>
+      <c r="H1037" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1037" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1037" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1037" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="inlineStr">
@@ -47293,10 +49223,20 @@
       <c r="G1038" s="2" t="n">
         <v>2.58</v>
       </c>
-      <c r="H1038" s="6" t="inlineStr"/>
-      <c r="I1038" s="6" t="inlineStr"/>
-      <c r="J1038" s="6" t="inlineStr"/>
-      <c r="K1038" s="6" t="inlineStr"/>
+      <c r="H1038" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1038" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1038" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1038" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="inlineStr">
@@ -47332,10 +49272,20 @@
       <c r="G1039" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H1039" s="6" t="inlineStr"/>
-      <c r="I1039" s="6" t="inlineStr"/>
-      <c r="J1039" s="6" t="inlineStr"/>
-      <c r="K1039" s="6" t="inlineStr"/>
+      <c r="H1039" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1039" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1039" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1039" s="5" t="n">
+        <v>-330</v>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" s="2" t="inlineStr">
@@ -47371,10 +49321,20 @@
       <c r="G1040" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="H1040" s="6" t="inlineStr"/>
-      <c r="I1040" s="6" t="inlineStr"/>
-      <c r="J1040" s="6" t="inlineStr"/>
-      <c r="K1040" s="6" t="inlineStr"/>
+      <c r="H1040" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1040" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1040" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1040" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="inlineStr">
@@ -47802,10 +49762,20 @@
       <c r="G1049" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="H1049" s="6" t="inlineStr"/>
-      <c r="I1049" s="6" t="inlineStr"/>
-      <c r="J1049" s="6" t="inlineStr"/>
-      <c r="K1049" s="6" t="inlineStr"/>
+      <c r="H1049" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1049" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1049" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1049" s="5" t="n">
+        <v>-275</v>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" s="2" t="inlineStr">
@@ -47939,10 +49909,20 @@
       <c r="G1052" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H1052" s="6" t="inlineStr"/>
-      <c r="I1052" s="6" t="inlineStr"/>
-      <c r="J1052" s="6" t="inlineStr"/>
-      <c r="K1052" s="6" t="inlineStr"/>
+      <c r="H1052" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1052" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1052" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1052" s="5" t="n">
+        <v>-320</v>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" s="2" t="inlineStr">
@@ -48027,10 +50007,20 @@
       <c r="G1054" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H1054" s="6" t="inlineStr"/>
-      <c r="I1054" s="6" t="inlineStr"/>
-      <c r="J1054" s="6" t="inlineStr"/>
-      <c r="K1054" s="6" t="inlineStr"/>
+      <c r="H1054" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1054" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1054" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1054" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" s="2" t="inlineStr">
@@ -48066,10 +50056,20 @@
       <c r="G1055" s="2" t="n">
         <v>2.6</v>
       </c>
-      <c r="H1055" s="6" t="inlineStr"/>
-      <c r="I1055" s="6" t="inlineStr"/>
-      <c r="J1055" s="6" t="inlineStr"/>
-      <c r="K1055" s="6" t="inlineStr"/>
+      <c r="H1055" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1055" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1055" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1055" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" s="2" t="inlineStr">
@@ -48301,10 +50301,20 @@
       <c r="G1060" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="H1060" s="6" t="inlineStr"/>
-      <c r="I1060" s="6" t="inlineStr"/>
-      <c r="J1060" s="6" t="inlineStr"/>
-      <c r="K1060" s="6" t="inlineStr"/>
+      <c r="H1060" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1060" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1060" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1060" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="inlineStr">
@@ -48389,10 +50399,20 @@
       <c r="G1062" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="H1062" s="6" t="inlineStr"/>
-      <c r="I1062" s="6" t="inlineStr"/>
-      <c r="J1062" s="6" t="inlineStr"/>
-      <c r="K1062" s="6" t="inlineStr"/>
+      <c r="H1062" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1062" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1062" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1062" s="5" t="n">
+        <v>-350</v>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" s="2" t="inlineStr">
@@ -48428,10 +50448,20 @@
       <c r="G1063" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="H1063" s="6" t="inlineStr"/>
-      <c r="I1063" s="6" t="inlineStr"/>
-      <c r="J1063" s="6" t="inlineStr"/>
-      <c r="K1063" s="6" t="inlineStr"/>
+      <c r="H1063" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1063" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1063" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1063" s="5" t="n">
+        <v>-270</v>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
@@ -48467,10 +50497,20 @@
       <c r="G1064" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H1064" s="6" t="inlineStr"/>
-      <c r="I1064" s="6" t="inlineStr"/>
-      <c r="J1064" s="6" t="inlineStr"/>
-      <c r="K1064" s="6" t="inlineStr"/>
+      <c r="H1064" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1064" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1064" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1064" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="inlineStr">
@@ -48506,10 +50546,20 @@
       <c r="G1065" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H1065" s="6" t="inlineStr"/>
-      <c r="I1065" s="6" t="inlineStr"/>
-      <c r="J1065" s="6" t="inlineStr"/>
-      <c r="K1065" s="6" t="inlineStr"/>
+      <c r="H1065" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1065" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1065" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1065" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" s="2" t="inlineStr">
@@ -48545,10 +50595,20 @@
       <c r="G1066" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="H1066" s="6" t="inlineStr"/>
-      <c r="I1066" s="6" t="inlineStr"/>
-      <c r="J1066" s="6" t="inlineStr"/>
-      <c r="K1066" s="6" t="inlineStr"/>
+      <c r="H1066" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1066" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1066" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1066" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
@@ -48682,10 +50742,20 @@
       <c r="G1069" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="H1069" s="6" t="inlineStr"/>
-      <c r="I1069" s="6" t="inlineStr"/>
-      <c r="J1069" s="6" t="inlineStr"/>
-      <c r="K1069" s="6" t="inlineStr"/>
+      <c r="H1069" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1069" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1069" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1069" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
@@ -48721,10 +50791,20 @@
       <c r="G1070" s="2" t="n">
         <v>1.8</v>
       </c>
-      <c r="H1070" s="6" t="inlineStr"/>
-      <c r="I1070" s="6" t="inlineStr"/>
-      <c r="J1070" s="6" t="inlineStr"/>
-      <c r="K1070" s="6" t="inlineStr"/>
+      <c r="H1070" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1070" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1070" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1070" s="4" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="inlineStr">
@@ -49504,10 +51584,20 @@
       <c r="G1087" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="H1087" s="6" t="inlineStr"/>
-      <c r="I1087" s="6" t="inlineStr"/>
-      <c r="J1087" s="6" t="inlineStr"/>
-      <c r="K1087" s="6" t="inlineStr"/>
+      <c r="H1087" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1087" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1087" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1087" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1088">
       <c r="A1088" s="2" t="inlineStr">
@@ -49543,10 +51633,20 @@
       <c r="G1088" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="H1088" s="6" t="inlineStr"/>
-      <c r="I1088" s="6" t="inlineStr"/>
-      <c r="J1088" s="6" t="inlineStr"/>
-      <c r="K1088" s="6" t="inlineStr"/>
+      <c r="H1088" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1088" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1088" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1088" s="4" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
@@ -49582,10 +51682,20 @@
       <c r="G1089" s="2" t="n">
         <v>3.65</v>
       </c>
-      <c r="H1089" s="6" t="inlineStr"/>
-      <c r="I1089" s="6" t="inlineStr"/>
-      <c r="J1089" s="6" t="inlineStr"/>
-      <c r="K1089" s="6" t="inlineStr"/>
+      <c r="H1089" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1089" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1089" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1089" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" s="2" t="inlineStr">
@@ -49621,10 +51731,20 @@
       <c r="G1090" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="H1090" s="6" t="inlineStr"/>
-      <c r="I1090" s="6" t="inlineStr"/>
-      <c r="J1090" s="6" t="inlineStr"/>
-      <c r="K1090" s="6" t="inlineStr"/>
+      <c r="H1090" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1090" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1090" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1090" s="4" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" s="2" t="inlineStr">
@@ -49807,10 +51927,20 @@
       <c r="G1094" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H1094" s="6" t="inlineStr"/>
-      <c r="I1094" s="6" t="inlineStr"/>
-      <c r="J1094" s="6" t="inlineStr"/>
-      <c r="K1094" s="6" t="inlineStr"/>
+      <c r="H1094" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1094" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1094" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="K1094" s="4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="1095">
       <c r="A1095" s="2" t="inlineStr">
@@ -49846,10 +51976,20 @@
       <c r="G1095" s="2" t="n">
         <v>1.81</v>
       </c>
-      <c r="H1095" s="6" t="inlineStr"/>
-      <c r="I1095" s="6" t="inlineStr"/>
-      <c r="J1095" s="6" t="inlineStr"/>
-      <c r="K1095" s="6" t="inlineStr"/>
+      <c r="H1095" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1095" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1095" s="5" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="K1095" s="5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" s="2" t="inlineStr">
